--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -20,7 +20,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$D$4:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$D$4:$J$84</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
@@ -1806,6 +1806,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ItemData"/>
+      <sheetName val="Sheet2"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
@@ -1820,1670 +1821,1751 @@
         </row>
         <row r="5">
           <cell r="A5" t="str">
-            <v>失败的料理</v>
+            <v>失败的徒手</v>
           </cell>
           <cell r="B5">
-            <v>10</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
-            <v>传送卷轴</v>
+            <v>失败的搅拌</v>
           </cell>
           <cell r="B6">
-            <v>11</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
-            <v>鱼饵</v>
+            <v>失败的烘烤</v>
           </cell>
           <cell r="B7">
-            <v>12</v>
+            <v>22</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>牧草</v>
+            <v>失败的蒸煮</v>
           </cell>
           <cell r="B8">
-            <v>100</v>
+            <v>23</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>芜菁</v>
+            <v>失败的酿造</v>
           </cell>
           <cell r="B9">
-            <v>1001</v>
+            <v>24</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
-            <v>卷心菜</v>
+            <v>传送卷轴</v>
           </cell>
           <cell r="B10">
-            <v>1002</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>葱</v>
+            <v>鱼饵</v>
           </cell>
           <cell r="B11">
-            <v>1003</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>萝卜</v>
+            <v>牧草</v>
           </cell>
           <cell r="B12">
-            <v>1004</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
-            <v>紫甘蓝</v>
+            <v>木材</v>
           </cell>
           <cell r="B13">
-            <v>1005</v>
+            <v>101</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>黄瓜</v>
+            <v>原木</v>
           </cell>
           <cell r="B14">
-            <v>1006</v>
+            <v>102</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>西兰花</v>
+            <v>木柴</v>
           </cell>
           <cell r="B15">
-            <v>1007</v>
+            <v>103</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>番茄</v>
+            <v>木棒</v>
           </cell>
           <cell r="B16">
-            <v>1008</v>
+            <v>104</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>胡萝卜</v>
+            <v>干草</v>
           </cell>
           <cell r="B17">
-            <v>1009</v>
+            <v>105</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>西瓜</v>
+            <v>芜菁</v>
           </cell>
           <cell r="B18">
-            <v>1010</v>
+            <v>1001</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>辣椒</v>
+            <v>卷心菜</v>
           </cell>
           <cell r="B19">
-            <v>1011</v>
+            <v>1002</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>奇异果</v>
+            <v>葱</v>
           </cell>
           <cell r="B20">
-            <v>1012</v>
+            <v>1003</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>茄子</v>
+            <v>萝卜</v>
           </cell>
           <cell r="B21">
-            <v>1013</v>
+            <v>1004</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>豌豆</v>
+            <v>紫甘蓝</v>
           </cell>
           <cell r="B22">
-            <v>1014</v>
+            <v>1005</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>土豆</v>
+            <v>黄瓜</v>
           </cell>
           <cell r="B23">
-            <v>1015</v>
+            <v>1006</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>大蒜</v>
+            <v>西兰花</v>
           </cell>
           <cell r="B24">
-            <v>1016</v>
+            <v>1007</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
-            <v>芦笋</v>
+            <v>番茄</v>
           </cell>
           <cell r="B25">
-            <v>1017</v>
+            <v>1008</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>南瓜</v>
+            <v>胡萝卜</v>
           </cell>
           <cell r="B26">
-            <v>1018</v>
+            <v>1009</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>玉米</v>
+            <v>西瓜</v>
           </cell>
           <cell r="B27">
-            <v>1019</v>
+            <v>1010</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>小麦</v>
+            <v>辣椒</v>
           </cell>
           <cell r="B28">
-            <v>1020</v>
+            <v>1011</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
-            <v>啤酒花</v>
+            <v>奇异果</v>
           </cell>
           <cell r="B29">
-            <v>1021</v>
+            <v>1012</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
-            <v>葡萄</v>
+            <v>茄子</v>
           </cell>
           <cell r="B30">
-            <v>1022</v>
+            <v>1013</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
-            <v>菠萝</v>
+            <v>豌豆</v>
           </cell>
           <cell r="B31">
-            <v>1023</v>
+            <v>1014</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
-            <v>咖啡</v>
+            <v>土豆</v>
           </cell>
           <cell r="B32">
-            <v>1024</v>
+            <v>1015</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>草莓</v>
+            <v>大蒜</v>
           </cell>
           <cell r="B33">
-            <v>1025</v>
+            <v>1016</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
-            <v>蓝莓</v>
+            <v>芦笋</v>
           </cell>
           <cell r="B34">
-            <v>1026</v>
+            <v>1017</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
-            <v>红薯</v>
+            <v>南瓜</v>
           </cell>
           <cell r="B35">
-            <v>1027</v>
+            <v>1018</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
-            <v>甜菜</v>
+            <v>玉米</v>
           </cell>
           <cell r="B36">
-            <v>1028</v>
+            <v>1019</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>芜菁种子</v>
+            <v>小麦</v>
           </cell>
           <cell r="B37">
-            <v>1101</v>
+            <v>1020</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>卷心菜种子</v>
+            <v>啤酒花</v>
           </cell>
           <cell r="B38">
-            <v>1102</v>
+            <v>1021</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
-            <v>葱种子</v>
+            <v>葡萄</v>
           </cell>
           <cell r="B39">
-            <v>1103</v>
+            <v>1022</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
-            <v>萝卜种子</v>
+            <v>菠萝</v>
           </cell>
           <cell r="B40">
-            <v>1104</v>
+            <v>1023</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
-            <v>紫甘蓝种子</v>
+            <v>咖啡</v>
           </cell>
           <cell r="B41">
-            <v>1105</v>
+            <v>1024</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
-            <v>黄瓜种子</v>
+            <v>草莓</v>
           </cell>
           <cell r="B42">
-            <v>1106</v>
+            <v>1025</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>西兰花种子</v>
+            <v>蓝莓</v>
           </cell>
           <cell r="B43">
-            <v>1107</v>
+            <v>1026</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44" t="str">
-            <v>番茄种子</v>
+            <v>红薯</v>
           </cell>
           <cell r="B44">
-            <v>1108</v>
+            <v>1027</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
-            <v>胡萝卜种子</v>
+            <v>甜菜</v>
           </cell>
           <cell r="B45">
-            <v>1109</v>
+            <v>1028</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
-            <v>西瓜种子</v>
+            <v>芜菁种子</v>
           </cell>
           <cell r="B46">
-            <v>1110</v>
+            <v>1101</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
-            <v>辣椒种子</v>
+            <v>卷心菜种子</v>
           </cell>
           <cell r="B47">
-            <v>1111</v>
+            <v>1102</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48" t="str">
-            <v>奇异果种子</v>
+            <v>葱种子</v>
           </cell>
           <cell r="B48">
-            <v>1112</v>
+            <v>1103</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49" t="str">
-            <v>茄子种子</v>
+            <v>萝卜种子</v>
           </cell>
           <cell r="B49">
-            <v>1113</v>
+            <v>1104</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50" t="str">
-            <v>豌豆种子</v>
+            <v>紫甘蓝种子</v>
           </cell>
           <cell r="B50">
-            <v>1114</v>
+            <v>1105</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51" t="str">
-            <v>土豆种子</v>
+            <v>黄瓜种子</v>
           </cell>
           <cell r="B51">
-            <v>1115</v>
+            <v>1106</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52" t="str">
-            <v>大蒜种子</v>
+            <v>西兰花种子</v>
           </cell>
           <cell r="B52">
-            <v>1116</v>
+            <v>1107</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53" t="str">
-            <v>芦笋种子</v>
+            <v>番茄种子</v>
           </cell>
           <cell r="B53">
-            <v>1117</v>
+            <v>1108</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
-            <v>南瓜种子</v>
+            <v>胡萝卜种子</v>
           </cell>
           <cell r="B54">
-            <v>1118</v>
+            <v>1109</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
-            <v>玉米种子</v>
+            <v>西瓜种子</v>
           </cell>
           <cell r="B55">
-            <v>1119</v>
+            <v>1110</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
-            <v>大麦种子</v>
+            <v>辣椒种子</v>
           </cell>
           <cell r="B56">
-            <v>1120</v>
+            <v>1111</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57" t="str">
-            <v>啤酒花种子</v>
+            <v>奇异果种子</v>
           </cell>
           <cell r="B57">
-            <v>1121</v>
+            <v>1112</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
-            <v>葡萄种子</v>
+            <v>茄子种子</v>
           </cell>
           <cell r="B58">
-            <v>1122</v>
+            <v>1113</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59" t="str">
-            <v>菠萝种子</v>
+            <v>豌豆种子</v>
           </cell>
           <cell r="B59">
-            <v>1123</v>
+            <v>1114</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
-            <v>咖啡种子</v>
+            <v>土豆种子</v>
           </cell>
           <cell r="B60">
-            <v>1124</v>
+            <v>1115</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61" t="str">
-            <v>草莓种子</v>
+            <v>大蒜种子</v>
           </cell>
           <cell r="B61">
-            <v>1125</v>
+            <v>1116</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62" t="str">
-            <v>蓝莓种子</v>
+            <v>芦笋种子</v>
           </cell>
           <cell r="B62">
-            <v>1126</v>
+            <v>1117</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
-            <v>红薯种子</v>
+            <v>南瓜种子</v>
           </cell>
           <cell r="B63">
-            <v>1127</v>
+            <v>1118</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64" t="str">
-            <v>甜菜种子</v>
+            <v>玉米种子</v>
           </cell>
           <cell r="B64">
-            <v>1128</v>
+            <v>1119</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65" t="str">
-            <v>锄头</v>
+            <v>大麦种子</v>
           </cell>
           <cell r="B65">
-            <v>2000</v>
+            <v>1120</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
-            <v>洒水壶</v>
+            <v>啤酒花种子</v>
           </cell>
           <cell r="B66">
-            <v>2001</v>
+            <v>1121</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
-            <v>斧头</v>
+            <v>葡萄种子</v>
           </cell>
           <cell r="B67">
-            <v>2002</v>
+            <v>1122</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68" t="str">
-            <v>镰刀</v>
+            <v>菠萝种子</v>
           </cell>
           <cell r="B68">
-            <v>2003</v>
+            <v>1123</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69" t="str">
-            <v>鱼竿</v>
+            <v>咖啡种子</v>
           </cell>
           <cell r="B69">
-            <v>2004</v>
+            <v>1124</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70" t="str">
-            <v>纺织机</v>
+            <v>草莓种子</v>
           </cell>
           <cell r="B70">
-            <v>2100</v>
+            <v>1125</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
-            <v>锻造炉</v>
+            <v>蓝莓种子</v>
           </cell>
           <cell r="B71">
-            <v>2101</v>
+            <v>1126</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72" t="str">
-            <v>烘烤炉</v>
+            <v>红薯种子</v>
           </cell>
           <cell r="B72">
-            <v>2102</v>
+            <v>1127</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
-            <v>炖煮锅</v>
+            <v>甜菜种子</v>
           </cell>
           <cell r="B73">
-            <v>2103</v>
+            <v>1128</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
-            <v>冷餐台</v>
+            <v>长剑</v>
           </cell>
           <cell r="B74">
-            <v>2104</v>
+            <v>1600</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
-            <v>酿造桶</v>
+            <v>诅咒之剑</v>
           </cell>
           <cell r="B75">
-            <v>2105</v>
+            <v>1601</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
-            <v>绘写台</v>
+            <v>烈焰之刃</v>
           </cell>
           <cell r="B76">
-            <v>2106</v>
+            <v>1602</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
-            <v>冰箱</v>
+            <v>大地之剑</v>
           </cell>
           <cell r="B77">
-            <v>2107</v>
+            <v>1603</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
-            <v>储物箱(木)</v>
+            <v>冰之刃</v>
           </cell>
           <cell r="B78">
-            <v>2108</v>
+            <v>1604</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
-            <v>储物箱(银)</v>
+            <v>铁枪</v>
           </cell>
           <cell r="B79">
-            <v>2109</v>
+            <v>1605</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80" t="str">
-            <v>储物箱(金)</v>
+            <v>骑士长枪</v>
           </cell>
           <cell r="B80">
-            <v>2110</v>
+            <v>1606</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
-            <v>普通柜台</v>
+            <v>血腥之枪</v>
           </cell>
           <cell r="B81">
-            <v>2111</v>
+            <v>1607</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
-            <v>武器柜台</v>
+            <v>三叉戟</v>
           </cell>
           <cell r="B82">
-            <v>2112</v>
+            <v>1608</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83" t="str">
-            <v>服饰架</v>
+            <v>战斧</v>
           </cell>
           <cell r="B83">
-            <v>2113</v>
+            <v>1609</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84" t="str">
-            <v>沙发</v>
+            <v>毒蜥之牙</v>
           </cell>
           <cell r="B84">
-            <v>2200</v>
+            <v>1610</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
-            <v>双人床</v>
+            <v>恶魔之斧</v>
           </cell>
           <cell r="B85">
-            <v>2201</v>
+            <v>1611</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86" t="str">
-            <v>搅拌机</v>
+            <v>蛇皮鞭</v>
           </cell>
           <cell r="B86">
-            <v>2202</v>
+            <v>1612</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87" t="str">
-            <v>鲫鱼</v>
+            <v>藤鞭</v>
           </cell>
           <cell r="B87">
-            <v>4000</v>
+            <v>1613</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88" t="str">
-            <v>小龙虾</v>
+            <v>女王鞭</v>
           </cell>
           <cell r="B88">
-            <v>4003</v>
+            <v>1614</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89" t="str">
-            <v>鲤鱼</v>
+            <v>蛇牙鞭</v>
           </cell>
           <cell r="B89">
-            <v>4004</v>
+            <v>1615</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
-            <v>鲮鱼</v>
+            <v>暴雪斧</v>
           </cell>
           <cell r="B90">
-            <v>4006</v>
+            <v>1616</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
-            <v>手套蟹</v>
+            <v>布衣</v>
           </cell>
           <cell r="B91">
-            <v>4007</v>
+            <v>1650</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
-            <v>鲶鱼</v>
+            <v>皮铠</v>
           </cell>
           <cell r="B92">
-            <v>4008</v>
+            <v>1651</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
-            <v>丁鱼</v>
+            <v>锁子甲</v>
           </cell>
           <cell r="B93">
-            <v>4009</v>
+            <v>1652</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
-            <v>锦鲤</v>
+            <v>毛皮斗篷</v>
           </cell>
           <cell r="B94">
-            <v>4010</v>
+            <v>1653</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
-            <v>线鱼</v>
+            <v>铁铠甲</v>
           </cell>
           <cell r="B95">
-            <v>4011</v>
+            <v>1654</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96" t="str">
-            <v>梭鲈</v>
+            <v>红莲之铠</v>
           </cell>
           <cell r="B96">
-            <v>4012</v>
+            <v>1655</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97" t="str">
-            <v>兰寿金鱼</v>
+            <v>华丽背心</v>
           </cell>
           <cell r="B97">
-            <v>4013</v>
+            <v>1656</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98" t="str">
-            <v>樱桃鲑鱼</v>
+            <v>鳞铠</v>
           </cell>
           <cell r="B98">
-            <v>4014</v>
+            <v>1657</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99" t="str">
-            <v>虹鳟鱼</v>
+            <v>暗之袍</v>
           </cell>
           <cell r="B99">
-            <v>4015</v>
+            <v>1658</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
-            <v>鲷鱼</v>
+            <v>疾风背心</v>
           </cell>
           <cell r="B100">
-            <v>4016</v>
+            <v>1659</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
-            <v>金鳟鱼</v>
+            <v>魔法铠甲</v>
           </cell>
           <cell r="B101">
-            <v>4017</v>
+            <v>1660</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102" t="str">
-            <v>霓虹脂鲤</v>
+            <v>钢刃锁甲</v>
           </cell>
           <cell r="B102">
-            <v>4018</v>
+            <v>1661</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
-            <v>桃花鱼</v>
+            <v>丝织长袍</v>
           </cell>
           <cell r="B103">
-            <v>4020</v>
+            <v>1662</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104" t="str">
-            <v>鲑鱼</v>
+            <v>水之羽衣</v>
           </cell>
           <cell r="B104">
-            <v>4021</v>
+            <v>1663</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
-            <v>孔雀鱼</v>
+            <v>贵族长裙</v>
           </cell>
           <cell r="B105">
-            <v>4022</v>
+            <v>1664</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
-            <v>银龙鱼</v>
+            <v>布鞋</v>
           </cell>
           <cell r="B106">
-            <v>4023</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
-            <v>洞穴天使鱼</v>
+            <v>皮鞋</v>
           </cell>
           <cell r="B107">
-            <v>4024</v>
+            <v>1701</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108" t="str">
-            <v>沙丁鱼</v>
+            <v>士兵长靴</v>
           </cell>
           <cell r="B108">
-            <v>4100</v>
+            <v>1702</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
-            <v>竹荚鱼</v>
+            <v>登山者之靴</v>
           </cell>
           <cell r="B109">
-            <v>4101</v>
+            <v>1703</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110" t="str">
-            <v>海鳗</v>
+            <v>运动鞋</v>
           </cell>
           <cell r="B110">
-            <v>4103</v>
+            <v>1704</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
-            <v>章鱼</v>
+            <v>贵族长靴</v>
           </cell>
           <cell r="B111">
-            <v>4105</v>
+            <v>1705</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
-            <v>比目鱼</v>
+            <v>武道鞋</v>
           </cell>
           <cell r="B112">
-            <v>4106</v>
+            <v>1706</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
-            <v>河豚</v>
+            <v>骑士护胫</v>
           </cell>
           <cell r="B113">
-            <v>4109</v>
+            <v>1707</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>水母</v>
+            <v>贤者之履</v>
           </cell>
           <cell r="B114">
-            <v>4110</v>
+            <v>1708</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
-            <v>条石鲷</v>
+            <v>风神之履</v>
           </cell>
           <cell r="B115">
-            <v>4111</v>
+            <v>1709</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
-            <v>红鲷鱼</v>
+            <v>锄头</v>
           </cell>
           <cell r="B116">
-            <v>4112</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
-            <v>蓝蟹</v>
+            <v>洒水壶</v>
           </cell>
           <cell r="B117">
-            <v>4113</v>
+            <v>2001</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
-            <v>鲯鳅鱼</v>
+            <v>斧头</v>
           </cell>
           <cell r="B118">
-            <v>4114</v>
+            <v>2002</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
-            <v>龙虾</v>
+            <v>镰刀</v>
           </cell>
           <cell r="B119">
-            <v>4115</v>
+            <v>2003</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
-            <v>金枪鱼</v>
+            <v>鱼竿</v>
           </cell>
           <cell r="B120">
-            <v>4116</v>
+            <v>2004</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
-            <v>斑马狮子鱼</v>
+            <v>纺织机</v>
           </cell>
           <cell r="B121">
-            <v>4117</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122" t="str">
-            <v>米饭</v>
+            <v>锻造炉</v>
           </cell>
           <cell r="B122">
-            <v>3000</v>
+            <v>2101</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
-            <v>发酵粉</v>
+            <v>烘烤炉</v>
           </cell>
           <cell r="B123">
-            <v>3001</v>
+            <v>2102</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124" t="str">
-            <v>盐</v>
+            <v>炖煮锅</v>
           </cell>
           <cell r="B124">
-            <v>3002</v>
+            <v>2103</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
-            <v>酸味香料</v>
+            <v>冷餐台</v>
           </cell>
           <cell r="B125">
-            <v>3003</v>
+            <v>2104</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
-            <v>纯净水</v>
+            <v>酿造桶</v>
           </cell>
           <cell r="B126">
-            <v>3004</v>
+            <v>2105</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
-            <v>蜂蜜</v>
+            <v>绘写台</v>
           </cell>
           <cell r="B127">
-            <v>3005</v>
+            <v>2106</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
-            <v>牛奶</v>
+            <v>冰箱</v>
           </cell>
           <cell r="B128">
-            <v>3006</v>
+            <v>2107</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129" t="str">
-            <v>鸡蛋</v>
+            <v>储物箱(木)</v>
           </cell>
           <cell r="B129">
-            <v>3007</v>
+            <v>2108</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
-            <v>猪肉</v>
+            <v>储物箱(银)</v>
           </cell>
           <cell r="B130">
-            <v>3008</v>
+            <v>2109</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
-            <v>面粉</v>
+            <v>储物箱(金)</v>
           </cell>
           <cell r="B131">
-            <v>3009</v>
+            <v>2110</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
-            <v>咖啡粉</v>
+            <v>普通柜台</v>
           </cell>
           <cell r="B132">
-            <v>3010</v>
+            <v>2111</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133" t="str">
-            <v>海苔</v>
+            <v>武器柜台</v>
           </cell>
           <cell r="B133">
-            <v>3011</v>
+            <v>2112</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
-            <v>黄油</v>
+            <v>服饰架</v>
           </cell>
           <cell r="B134">
-            <v>3011</v>
+            <v>2113</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
-            <v>腌芜菁</v>
+            <v>沙发</v>
           </cell>
           <cell r="B135">
-            <v>3100</v>
+            <v>2200</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
-            <v>蔬菜沙拉</v>
+            <v>搅拌机</v>
           </cell>
           <cell r="B136">
-            <v>3101</v>
+            <v>2114</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
-            <v>三明治</v>
+            <v>双人床</v>
           </cell>
           <cell r="B137">
-            <v>3102</v>
+            <v>2201</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
-            <v>腌萝卜</v>
+            <v>鲫鱼</v>
           </cell>
           <cell r="B138">
-            <v>3103</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
-            <v>拉面</v>
+            <v>小龙虾</v>
           </cell>
           <cell r="B139">
-            <v>3104</v>
+            <v>4003</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
-            <v>蜂蜜蛋糕</v>
+            <v>鲤鱼</v>
           </cell>
           <cell r="B140">
-            <v>3105</v>
+            <v>4004</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141" t="str">
-            <v>披萨</v>
+            <v>鲮鱼</v>
           </cell>
           <cell r="B141">
-            <v>3106</v>
+            <v>4006</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
-            <v>腌黄瓜</v>
+            <v>手套蟹</v>
           </cell>
           <cell r="B142">
-            <v>3107</v>
+            <v>4007</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
-            <v>烤西兰花</v>
+            <v>鲶鱼</v>
           </cell>
           <cell r="B143">
-            <v>3108</v>
+            <v>4008</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
-            <v>水煮蛋</v>
+            <v>丁鱼</v>
           </cell>
           <cell r="B144">
-            <v>3109</v>
+            <v>4009</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
-            <v>烤肉串</v>
+            <v>锦鲤</v>
           </cell>
           <cell r="B145">
-            <v>3110</v>
+            <v>4010</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
-            <v>饭团</v>
+            <v>线鱼</v>
           </cell>
           <cell r="B146">
-            <v>3111</v>
+            <v>4011</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
-            <v>面包</v>
+            <v>梭鲈</v>
           </cell>
           <cell r="B147">
-            <v>3112</v>
+            <v>4012</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148" t="str">
-            <v>烤海苔</v>
+            <v>兰寿金鱼</v>
           </cell>
           <cell r="B148">
-            <v>3113</v>
+            <v>4013</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149" t="str">
-            <v>烤肉饼</v>
+            <v>樱桃鲑鱼</v>
           </cell>
           <cell r="B149">
-            <v>3114</v>
+            <v>4014</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
-            <v>汉堡</v>
+            <v>虹鳟鱼</v>
           </cell>
           <cell r="B150">
-            <v>3115</v>
+            <v>4015</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
-            <v>辣蟹堡</v>
+            <v>鲷鱼</v>
           </cell>
           <cell r="B151">
-            <v>3116</v>
+            <v>4016</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
-            <v>土豆泥</v>
+            <v>金鳟鱼</v>
           </cell>
           <cell r="B152">
-            <v>3117</v>
+            <v>4017</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
-            <v>海鲜饭</v>
+            <v>霓虹脂鲤</v>
           </cell>
           <cell r="B153">
-            <v>3118</v>
+            <v>4018</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
-            <v>烤玉米</v>
+            <v>桃花鱼</v>
           </cell>
           <cell r="B154">
-            <v>3119</v>
+            <v>4020</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
-            <v>蔬菜汁</v>
+            <v>鲑鱼</v>
           </cell>
           <cell r="B155">
-            <v>3120</v>
+            <v>4021</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
-            <v>西瓜果汁</v>
+            <v>孔雀鱼</v>
           </cell>
           <cell r="B156">
-            <v>3121</v>
+            <v>4022</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
-            <v>奇异果汁</v>
+            <v>银龙鱼</v>
           </cell>
           <cell r="B157">
-            <v>3122</v>
+            <v>4023</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158" t="str">
-            <v>葡萄汁</v>
+            <v>洞穴天使鱼</v>
           </cell>
           <cell r="B158">
-            <v>3123</v>
+            <v>4024</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159" t="str">
-            <v>菠萝汁</v>
+            <v>沙丁鱼</v>
           </cell>
           <cell r="B159">
-            <v>3124</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
-            <v>草莓汁</v>
+            <v>竹荚鱼</v>
           </cell>
           <cell r="B160">
-            <v>3125</v>
+            <v>4101</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
-            <v>蓝莓汁</v>
+            <v>海鳗</v>
           </cell>
           <cell r="B161">
-            <v>3126</v>
+            <v>4103</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
-            <v>玉米汁</v>
+            <v>章鱼</v>
           </cell>
           <cell r="B162">
-            <v>3127</v>
+            <v>4105</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
-            <v>烤蜜薯</v>
+            <v>比目鱼</v>
           </cell>
           <cell r="B163">
-            <v>3128</v>
+            <v>4106</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164" t="str">
-            <v>甜菜汁</v>
+            <v>河豚</v>
           </cell>
           <cell r="B164">
-            <v>3129</v>
+            <v>4109</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165" t="str">
-            <v>奶酪</v>
+            <v>水母</v>
           </cell>
           <cell r="B165">
-            <v>3130</v>
+            <v>4110</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
-            <v>烤茄子</v>
+            <v>条石鲷</v>
           </cell>
           <cell r="B166">
-            <v>3131</v>
+            <v>4111</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
-            <v>饺子</v>
+            <v>红鲷鱼</v>
           </cell>
           <cell r="B167">
-            <v>3132</v>
+            <v>4112</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
-            <v>炖菜</v>
+            <v>蓝蟹</v>
           </cell>
           <cell r="B168">
-            <v>3133</v>
+            <v>4113</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
-            <v>烤芦笋</v>
+            <v>鲯鳅鱼</v>
           </cell>
           <cell r="B169">
-            <v>3134</v>
+            <v>4114</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
-            <v>红菜汤</v>
+            <v>龙虾</v>
           </cell>
           <cell r="B170">
-            <v>3135</v>
+            <v>4115</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
-            <v>豌豆汤</v>
+            <v>金枪鱼</v>
           </cell>
           <cell r="B171">
-            <v>3136</v>
+            <v>4116</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172" t="str">
-            <v>草莓牛奶</v>
+            <v>斑马狮子鱼</v>
           </cell>
           <cell r="B172">
-            <v>3137</v>
+            <v>4117</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173" t="str">
-            <v>莓莓果汁</v>
+            <v>米饭</v>
           </cell>
           <cell r="B173">
-            <v>3138</v>
+            <v>3000</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174" t="str">
-            <v>鲑鱼饭团</v>
+            <v>发酵粉</v>
           </cell>
           <cell r="B174">
-            <v>3139</v>
+            <v>3001</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175" t="str">
-            <v>拿铁</v>
+            <v>盐</v>
           </cell>
           <cell r="B175">
-            <v>3140</v>
+            <v>3002</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
-            <v>黑咖啡</v>
+            <v>酸味香料</v>
           </cell>
           <cell r="B176">
-            <v>3141</v>
+            <v>3003</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
-            <v>葡萄酒</v>
+            <v>纯净水</v>
           </cell>
           <cell r="B177">
-            <v>3142</v>
+            <v>3004</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178" t="str">
-            <v>伏特加</v>
+            <v>蜂蜜</v>
           </cell>
           <cell r="B178">
-            <v>3143</v>
+            <v>3005</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179" t="str">
-            <v>啤酒</v>
+            <v>牛奶</v>
           </cell>
           <cell r="B179">
-            <v>3144</v>
+            <v>3006</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180" t="str">
-            <v>朗姆</v>
+            <v>鸡蛋</v>
           </cell>
           <cell r="B180">
-            <v>3145</v>
+            <v>3007</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181" t="str">
-            <v>野蜂拉格</v>
+            <v>猪肉</v>
           </cell>
           <cell r="B181">
-            <v>3146</v>
+            <v>3008</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
-            <v>双莓白兰地</v>
+            <v>面粉</v>
           </cell>
           <cell r="B182">
-            <v>3147</v>
+            <v>3009</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183" t="str">
-            <v>绯红之吻</v>
+            <v>咖啡粉</v>
           </cell>
           <cell r="B183">
-            <v>3148</v>
+            <v>3010</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
-            <v>阳光男孩</v>
+            <v>海苔</v>
           </cell>
           <cell r="B184">
-            <v>3149</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
-            <v>盐烤鲮鱼</v>
+            <v>黄油</v>
           </cell>
           <cell r="B185">
-            <v>3150</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
-            <v>盐烤丁鱼</v>
+            <v>腌芜菁</v>
           </cell>
           <cell r="B186">
-            <v>3151</v>
+            <v>3100</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
-            <v>盐烤虹鳟鱼</v>
+            <v>蔬菜沙拉</v>
           </cell>
           <cell r="B187">
-            <v>3152</v>
+            <v>3101</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
-            <v>烤鲷鱼</v>
+            <v>三明治</v>
           </cell>
           <cell r="B188">
-            <v>3153</v>
+            <v>3102</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189" t="str">
-            <v>盐烤金鳟鱼</v>
+            <v>腌萝卜</v>
           </cell>
           <cell r="B189">
-            <v>3154</v>
+            <v>3103</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190" t="str">
-            <v>盐烤鲑鱼</v>
+            <v>拉面</v>
           </cell>
           <cell r="B190">
-            <v>3155</v>
+            <v>3104</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
-            <v>烤沙丁鱼串</v>
+            <v>蜂蜜蛋糕</v>
           </cell>
           <cell r="B191">
-            <v>3156</v>
+            <v>3105</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
-            <v>烤竹荚鱼</v>
+            <v>披萨</v>
           </cell>
           <cell r="B192">
-            <v>3157</v>
+            <v>3106</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
-            <v>烤海鳗</v>
+            <v>腌黄瓜</v>
           </cell>
           <cell r="B193">
-            <v>3158</v>
+            <v>3107</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
-            <v>烤比目鱼</v>
+            <v>烤西兰花</v>
           </cell>
           <cell r="B194">
-            <v>3159</v>
+            <v>3108</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
-            <v>烤河豚鱼</v>
+            <v>水煮蛋</v>
           </cell>
           <cell r="B195">
-            <v>3160</v>
+            <v>3109</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196" t="str">
-            <v>烤条石鲷</v>
+            <v>烤肉串</v>
           </cell>
           <cell r="B196">
-            <v>3161</v>
+            <v>3110</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
-            <v>烤红鲷鱼</v>
+            <v>饭团</v>
           </cell>
           <cell r="B197">
-            <v>3162</v>
+            <v>3111</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
-            <v>烤蓝蟹</v>
+            <v>面包</v>
           </cell>
           <cell r="B198">
-            <v>3163</v>
+            <v>3112</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
-            <v>烤龙虾</v>
+            <v>烤海苔</v>
           </cell>
           <cell r="B199">
-            <v>3164</v>
+            <v>3113</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
-            <v>烤金枪鱼</v>
+            <v>烤肉饼</v>
           </cell>
           <cell r="B200">
-            <v>3165</v>
+            <v>3114</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
-            <v>煮蟹肉</v>
+            <v>汉堡</v>
           </cell>
           <cell r="B201">
-            <v>3166</v>
+            <v>3115</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
-            <v>海鲜浓汤</v>
+            <v>辣蟹堡</v>
           </cell>
           <cell r="B202">
-            <v>3167</v>
+            <v>3116</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
-            <v>鳗鱼饭</v>
+            <v>土豆泥</v>
           </cell>
           <cell r="B203">
-            <v>3168</v>
+            <v>3117</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
-            <v>鲫鱼蔬菜汤</v>
+            <v>海鲜饭</v>
           </cell>
           <cell r="B204">
-            <v>3169</v>
+            <v>3118</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
-            <v>鲮鱼丸</v>
+            <v>烤玉米</v>
           </cell>
           <cell r="B205">
-            <v>3170</v>
+            <v>3119</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
-            <v>鲑鱼刺身</v>
+            <v>蔬菜汁</v>
           </cell>
           <cell r="B206">
-            <v>3171</v>
+            <v>3120</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
-            <v>章鱼小丸子</v>
+            <v>西瓜果汁</v>
           </cell>
           <cell r="B207">
-            <v>3172</v>
+            <v>3121</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
-            <v>炖煮条石鲷</v>
+            <v>奇异果汁</v>
           </cell>
           <cell r="B208">
-            <v>3173</v>
+            <v>3122</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
-            <v>红鲷刺身</v>
+            <v>葡萄汁</v>
           </cell>
           <cell r="B209">
-            <v>3174</v>
+            <v>3123</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
-            <v>河豚刺身</v>
+            <v>菠萝汁</v>
           </cell>
           <cell r="B210">
-            <v>3175</v>
+            <v>3124</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
-            <v>螃蟹煲</v>
+            <v>草莓汁</v>
           </cell>
           <cell r="B211">
-            <v>3176</v>
+            <v>3125</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
-            <v>金枪鱼刺身</v>
+            <v>蓝莓汁</v>
           </cell>
           <cell r="B212">
-            <v>3177</v>
+            <v>3126</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213" t="str">
+            <v>玉米汁</v>
+          </cell>
+          <cell r="B213">
+            <v>3127</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214" t="str">
+            <v>烤蜜薯</v>
+          </cell>
+          <cell r="B214">
+            <v>3128</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215" t="str">
+            <v>甜菜汁</v>
+          </cell>
+          <cell r="B215">
+            <v>3129</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="A216" t="str">
+            <v>奶酪</v>
+          </cell>
+          <cell r="B216">
+            <v>3130</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="A217" t="str">
+            <v>烤茄子</v>
+          </cell>
+          <cell r="B217">
+            <v>3131</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="A218" t="str">
+            <v>饺子</v>
+          </cell>
+          <cell r="B218">
+            <v>3132</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="A219" t="str">
+            <v>炖菜</v>
+          </cell>
+          <cell r="B219">
+            <v>3133</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="A220" t="str">
+            <v>烤芦笋</v>
+          </cell>
+          <cell r="B220">
+            <v>3134</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="A221" t="str">
+            <v>红菜汤</v>
+          </cell>
+          <cell r="B221">
+            <v>3135</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="A222" t="str">
+            <v>豌豆汤</v>
+          </cell>
+          <cell r="B222">
+            <v>3136</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6446,19 +6528,19 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="N2" s="1">
-        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1020</v>
       </c>
       <c r="O2" s="7" t="str">
-        <f>IF(I2&lt;&gt;"",VLOOKUP(I2,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I2&lt;&gt;"",VLOOKUP(I2,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P2" s="7" t="str">
-        <f>IF(J2&lt;&gt;"",VLOOKUP(J2,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J2&lt;&gt;"",VLOOKUP(J2,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q2" s="7" t="str">
-        <f>IF(K2&lt;&gt;"",VLOOKUP(K2,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K2&lt;&gt;"",VLOOKUP(K2,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S2" s="1" t="str">
@@ -6483,19 +6565,19 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="N3" s="7">
-        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1024</v>
       </c>
       <c r="O3" s="7" t="str">
-        <f>IF(I3&lt;&gt;"",VLOOKUP(I3,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I3&lt;&gt;"",VLOOKUP(I3,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P3" s="7" t="str">
-        <f>IF(J3&lt;&gt;"",VLOOKUP(J3,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J3&lt;&gt;"",VLOOKUP(J3,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q3" s="7" t="str">
-        <f>IF(K3&lt;&gt;"",VLOOKUP(K3,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K3&lt;&gt;"",VLOOKUP(K3,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S3" s="7" t="str">
@@ -6514,19 +6596,19 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="N4" s="7" t="str">
-        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="O4" s="7" t="str">
-        <f>IF(I4&lt;&gt;"",VLOOKUP(I4,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I4&lt;&gt;"",VLOOKUP(I4,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P4" s="7" t="str">
-        <f>IF(J4&lt;&gt;"",VLOOKUP(J4,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J4&lt;&gt;"",VLOOKUP(J4,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q4" s="7" t="str">
-        <f>IF(K4&lt;&gt;"",VLOOKUP(K4,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K4&lt;&gt;"",VLOOKUP(K4,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S4" s="7" t="str">
@@ -6559,19 +6641,19 @@
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7">
-        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O5" s="7">
-        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P5" s="7" t="str">
-        <f>IF(J5&lt;&gt;"",VLOOKUP(J5,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J5&lt;&gt;"",VLOOKUP(J5,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q5" s="7" t="str">
-        <f>IF(K5&lt;&gt;"",VLOOKUP(K5,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K5&lt;&gt;"",VLOOKUP(K5,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S5" s="7" t="str">
@@ -6610,19 +6692,19 @@
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7">
-        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="O6" s="7">
-        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P6" s="7">
-        <f>IF(J6&lt;&gt;"",VLOOKUP(J6,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J6&lt;&gt;"",VLOOKUP(J6,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q6" s="7">
-        <f>IF(K6&lt;&gt;"",VLOOKUP(K6,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K6&lt;&gt;"",VLOOKUP(K6,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="S6" s="7" t="str">
@@ -6661,19 +6743,19 @@
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7">
-        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O7" s="7">
-        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="P7" s="7">
-        <f>IF(J7&lt;&gt;"",VLOOKUP(J7,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J7&lt;&gt;"",VLOOKUP(J7,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="Q7" s="7">
-        <f>IF(K7&lt;&gt;"",VLOOKUP(K7,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K7&lt;&gt;"",VLOOKUP(K7,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="S7" s="7" t="str">
@@ -6706,19 +6788,19 @@
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7">
-        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="O8" s="7">
-        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P8" s="7" t="str">
-        <f>IF(J8&lt;&gt;"",VLOOKUP(J8,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J8&lt;&gt;"",VLOOKUP(J8,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q8" s="7" t="str">
-        <f>IF(K8&lt;&gt;"",VLOOKUP(K8,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K8&lt;&gt;"",VLOOKUP(K8,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S8" s="7" t="str">
@@ -6757,19 +6839,19 @@
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7">
-        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O9" s="7">
-        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P9" s="7">
-        <f>IF(J9&lt;&gt;"",VLOOKUP(J9,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J9&lt;&gt;"",VLOOKUP(J9,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="Q9" s="7">
-        <f>IF(K9&lt;&gt;"",VLOOKUP(K9,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K9&lt;&gt;"",VLOOKUP(K9,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3109</v>
       </c>
       <c r="S9" s="7" t="str">
@@ -6804,19 +6886,19 @@
       <c r="L10" s="8"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7">
-        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O10" s="7">
-        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P10" s="7">
-        <f>IF(J10&lt;&gt;"",VLOOKUP(J10,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J10&lt;&gt;"",VLOOKUP(J10,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="Q10" s="7" t="str">
-        <f>IF(K10&lt;&gt;"",VLOOKUP(K10,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K10&lt;&gt;"",VLOOKUP(K10,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S10" s="7" t="str">
@@ -6853,19 +6935,19 @@
       <c r="L11" s="8"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7">
-        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O11" s="7">
-        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="P11" s="7">
-        <f>IF(J11&lt;&gt;"",VLOOKUP(J11,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J11&lt;&gt;"",VLOOKUP(J11,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1013</v>
       </c>
       <c r="Q11" s="7">
-        <f>IF(K11&lt;&gt;"",VLOOKUP(K11,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K11&lt;&gt;"",VLOOKUP(K11,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="S11" s="7" t="str">
@@ -6897,19 +6979,19 @@
         <v>2</v>
       </c>
       <c r="N12" s="7">
-        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="O12" s="7">
-        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P12" s="7" t="str">
-        <f>IF(J12&lt;&gt;"",VLOOKUP(J12,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J12&lt;&gt;"",VLOOKUP(J12,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q12" s="7" t="str">
-        <f>IF(K12&lt;&gt;"",VLOOKUP(K12,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K12&lt;&gt;"",VLOOKUP(K12,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S12" s="7" t="str">
@@ -6938,19 +7020,19 @@
         <v>1</v>
       </c>
       <c r="N13" s="7">
-        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1007</v>
       </c>
       <c r="O13" s="7" t="str">
-        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P13" s="7" t="str">
-        <f>IF(J13&lt;&gt;"",VLOOKUP(J13,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J13&lt;&gt;"",VLOOKUP(J13,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q13" s="7" t="str">
-        <f>IF(K13&lt;&gt;"",VLOOKUP(K13,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K13&lt;&gt;"",VLOOKUP(K13,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S13" s="7" t="str">
@@ -6980,19 +7062,19 @@
         <v>1</v>
       </c>
       <c r="N14" s="7">
-        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="O14" s="7" t="str">
-        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P14" s="7" t="str">
-        <f>IF(J14&lt;&gt;"",VLOOKUP(J14,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J14&lt;&gt;"",VLOOKUP(J14,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q14" s="7" t="str">
-        <f>IF(K14&lt;&gt;"",VLOOKUP(K14,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K14&lt;&gt;"",VLOOKUP(K14,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S14" s="7" t="str">
@@ -7028,19 +7110,19 @@
         <v>3</v>
       </c>
       <c r="N15" s="7">
-        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="O15" s="7">
-        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P15" s="7">
-        <f>IF(J15&lt;&gt;"",VLOOKUP(J15,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J15&lt;&gt;"",VLOOKUP(J15,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="Q15" s="7" t="str">
-        <f>IF(K15&lt;&gt;"",VLOOKUP(K15,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K15&lt;&gt;"",VLOOKUP(K15,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S15" s="7" t="str">
@@ -7072,19 +7154,19 @@
         <v>3</v>
       </c>
       <c r="N16" s="7">
-        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3113</v>
       </c>
       <c r="O16" s="7">
-        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P16" s="7" t="str">
-        <f>IF(J16&lt;&gt;"",VLOOKUP(J16,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J16&lt;&gt;"",VLOOKUP(J16,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q16" s="7" t="str">
-        <f>IF(K16&lt;&gt;"",VLOOKUP(K16,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K16&lt;&gt;"",VLOOKUP(K16,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S16" s="7" t="str">
@@ -7116,19 +7198,19 @@
       <c r="K17" s="7"/>
       <c r="L17" s="8"/>
       <c r="N17" s="7">
-        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O17" s="7">
-        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="P17" s="7" t="str">
-        <f>IF(J17&lt;&gt;"",VLOOKUP(J17,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J17&lt;&gt;"",VLOOKUP(J17,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q17" s="7" t="str">
-        <f>IF(K17&lt;&gt;"",VLOOKUP(K17,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K17&lt;&gt;"",VLOOKUP(K17,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S17" s="7" t="str">
@@ -7158,19 +7240,19 @@
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7">
-        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="O18" s="7" t="str">
-        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P18" s="7" t="str">
-        <f>IF(J18&lt;&gt;"",VLOOKUP(J18,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J18&lt;&gt;"",VLOOKUP(J18,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q18" s="7" t="str">
-        <f>IF(K18&lt;&gt;"",VLOOKUP(K18,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K18&lt;&gt;"",VLOOKUP(K18,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S18" s="7" t="str">
@@ -7205,19 +7287,19 @@
         <v>3</v>
       </c>
       <c r="N19" s="7">
-        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="O19" s="7">
-        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P19" s="7">
-        <f>IF(J19&lt;&gt;"",VLOOKUP(J19,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J19&lt;&gt;"",VLOOKUP(J19,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="Q19" s="7" t="str">
-        <f>IF(K19&lt;&gt;"",VLOOKUP(K19,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K19&lt;&gt;"",VLOOKUP(K19,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S19" s="7" t="str">
@@ -7253,19 +7335,19 @@
       </c>
       <c r="L20" s="8"/>
       <c r="N20" s="7">
-        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O20" s="7">
-        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="P20" s="7">
-        <f>IF(J20&lt;&gt;"",VLOOKUP(J20,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J20&lt;&gt;"",VLOOKUP(J20,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3114</v>
       </c>
       <c r="Q20" s="7">
-        <f>IF(K20&lt;&gt;"",VLOOKUP(K20,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K20&lt;&gt;"",VLOOKUP(K20,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="S20" s="7" t="str">
@@ -7302,24 +7384,24 @@
       <c r="L21" s="8"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7">
-        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3112</v>
       </c>
-      <c r="O21" s="7">
-        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
-        <v>3166</v>
+      <c r="O21" s="7" t="e">
+        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
+        <v>#N/A</v>
       </c>
       <c r="P21" s="7">
-        <f>IF(J21&lt;&gt;"",VLOOKUP(J21,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J21&lt;&gt;"",VLOOKUP(J21,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="Q21" s="7">
-        <f>IF(K21&lt;&gt;"",VLOOKUP(K21,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K21&lt;&gt;"",VLOOKUP(K21,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3130</v>
       </c>
-      <c r="S21" s="7" t="str">
+      <c r="S21" s="7" t="e">
         <f t="shared" si="0"/>
-        <v>3112,3166,1011,3130</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.2">
@@ -7345,19 +7427,19 @@
         <v>3</v>
       </c>
       <c r="N22" s="7">
-        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O22" s="7">
-        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P22" s="7" t="str">
-        <f>IF(J22&lt;&gt;"",VLOOKUP(J22,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J22&lt;&gt;"",VLOOKUP(J22,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q22" s="7" t="str">
-        <f>IF(K22&lt;&gt;"",VLOOKUP(K22,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K22&lt;&gt;"",VLOOKUP(K22,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S22" s="7" t="str">
@@ -7394,19 +7476,19 @@
       <c r="L23" s="8"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7">
-        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O23" s="7">
-        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="P23" s="7">
-        <f>IF(J23&lt;&gt;"",VLOOKUP(J23,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J23&lt;&gt;"",VLOOKUP(J23,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4115</v>
       </c>
       <c r="Q23" s="7">
-        <f>IF(K23&lt;&gt;"",VLOOKUP(K23,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K23&lt;&gt;"",VLOOKUP(K23,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="S23" s="7" t="str">
@@ -7438,19 +7520,19 @@
       <c r="K24" s="7"/>
       <c r="L24" s="8"/>
       <c r="N24" s="7">
-        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O24" s="7">
-        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P24" s="7" t="str">
-        <f>IF(J24&lt;&gt;"",VLOOKUP(J24,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J24&lt;&gt;"",VLOOKUP(J24,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q24" s="7" t="str">
-        <f>IF(K24&lt;&gt;"",VLOOKUP(K24,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K24&lt;&gt;"",VLOOKUP(K24,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S24" s="7" t="str">
@@ -7486,19 +7568,19 @@
       </c>
       <c r="L25" s="8"/>
       <c r="N25" s="7">
-        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O25" s="7">
-        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="P25" s="7">
-        <f>IF(J25&lt;&gt;"",VLOOKUP(J25,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J25&lt;&gt;"",VLOOKUP(J25,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="Q25" s="7">
-        <f>IF(K25&lt;&gt;"",VLOOKUP(K25,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K25&lt;&gt;"",VLOOKUP(K25,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="S25" s="7" t="str">
@@ -7527,19 +7609,19 @@
         <v>1</v>
       </c>
       <c r="N26" s="7">
-        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1010</v>
       </c>
       <c r="O26" s="7" t="str">
-        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P26" s="7" t="str">
-        <f>IF(J26&lt;&gt;"",VLOOKUP(J26,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J26&lt;&gt;"",VLOOKUP(J26,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q26" s="7" t="str">
-        <f>IF(K26&lt;&gt;"",VLOOKUP(K26,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K26&lt;&gt;"",VLOOKUP(K26,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S26" s="7" t="str">
@@ -7569,19 +7651,19 @@
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7">
-        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1012</v>
       </c>
       <c r="O27" s="7" t="str">
-        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P27" s="7" t="str">
-        <f>IF(J27&lt;&gt;"",VLOOKUP(J27,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J27&lt;&gt;"",VLOOKUP(J27,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q27" s="7" t="str">
-        <f>IF(K27&lt;&gt;"",VLOOKUP(K27,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K27&lt;&gt;"",VLOOKUP(K27,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S27" s="7" t="str">
@@ -7610,19 +7692,19 @@
         <v>1</v>
       </c>
       <c r="N28" s="7">
-        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1022</v>
       </c>
       <c r="O28" s="7" t="str">
-        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P28" s="7" t="str">
-        <f>IF(J28&lt;&gt;"",VLOOKUP(J28,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J28&lt;&gt;"",VLOOKUP(J28,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q28" s="7" t="str">
-        <f>IF(K28&lt;&gt;"",VLOOKUP(K28,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K28&lt;&gt;"",VLOOKUP(K28,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S28" s="7" t="str">
@@ -7651,19 +7733,19 @@
         <v>1</v>
       </c>
       <c r="N29" s="7">
-        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1023</v>
       </c>
       <c r="O29" s="7" t="str">
-        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P29" s="7" t="str">
-        <f>IF(J29&lt;&gt;"",VLOOKUP(J29,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J29&lt;&gt;"",VLOOKUP(J29,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q29" s="7" t="str">
-        <f>IF(K29&lt;&gt;"",VLOOKUP(K29,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K29&lt;&gt;"",VLOOKUP(K29,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S29" s="7" t="str">
@@ -7686,19 +7768,19 @@
         <v>1</v>
       </c>
       <c r="N30" s="7">
-        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="O30" s="7" t="str">
-        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P30" s="7" t="str">
-        <f>IF(J30&lt;&gt;"",VLOOKUP(J30,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J30&lt;&gt;"",VLOOKUP(J30,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q30" s="7" t="str">
-        <f>IF(K30&lt;&gt;"",VLOOKUP(K30,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K30&lt;&gt;"",VLOOKUP(K30,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S30" s="7" t="str">
@@ -7727,19 +7809,19 @@
         <v>1</v>
       </c>
       <c r="N31" s="7">
-        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O31" s="7" t="str">
-        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P31" s="7" t="str">
-        <f>IF(J31&lt;&gt;"",VLOOKUP(J31,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J31&lt;&gt;"",VLOOKUP(J31,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q31" s="7" t="str">
-        <f>IF(K31&lt;&gt;"",VLOOKUP(K31,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K31&lt;&gt;"",VLOOKUP(K31,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S31" s="7" t="str">
@@ -7768,19 +7850,19 @@
       <c r="K32" s="7"/>
       <c r="L32" s="8"/>
       <c r="N32" s="7">
-        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O32" s="7" t="str">
-        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P32" s="7" t="str">
-        <f>IF(J32&lt;&gt;"",VLOOKUP(J32,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J32&lt;&gt;"",VLOOKUP(J32,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q32" s="7" t="str">
-        <f>IF(K32&lt;&gt;"",VLOOKUP(K32,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K32&lt;&gt;"",VLOOKUP(K32,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S32" s="7" t="str">
@@ -7812,19 +7894,19 @@
         <v>2</v>
       </c>
       <c r="N33" s="7">
-        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="O33" s="7">
-        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="P33" s="7" t="str">
-        <f>IF(J33&lt;&gt;"",VLOOKUP(J33,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J33&lt;&gt;"",VLOOKUP(J33,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q33" s="7" t="str">
-        <f>IF(K33&lt;&gt;"",VLOOKUP(K33,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K33&lt;&gt;"",VLOOKUP(K33,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S33" s="7" t="str">
@@ -7853,19 +7935,19 @@
         <v>1</v>
       </c>
       <c r="N34" s="7">
-        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O34" s="7" t="str">
-        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P34" s="7" t="str">
-        <f>IF(J34&lt;&gt;"",VLOOKUP(J34,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J34&lt;&gt;"",VLOOKUP(J34,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q34" s="7" t="str">
-        <f>IF(K34&lt;&gt;"",VLOOKUP(K34,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K34&lt;&gt;"",VLOOKUP(K34,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S34" s="7" t="str">
@@ -7897,19 +7979,19 @@
         <v>1</v>
       </c>
       <c r="N35" s="7">
-        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O35" s="7" t="str">
-        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P35" s="7" t="str">
-        <f>IF(J35&lt;&gt;"",VLOOKUP(J35,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J35&lt;&gt;"",VLOOKUP(J35,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q35" s="7" t="str">
-        <f>IF(K35&lt;&gt;"",VLOOKUP(K35,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K35&lt;&gt;"",VLOOKUP(K35,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S35" s="7" t="str">
@@ -7936,19 +8018,19 @@
         <v>2</v>
       </c>
       <c r="N36" s="7">
-        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O36" s="7">
-        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P36" s="7" t="str">
-        <f>IF(J36&lt;&gt;"",VLOOKUP(J36,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J36&lt;&gt;"",VLOOKUP(J36,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q36" s="7" t="str">
-        <f>IF(K36&lt;&gt;"",VLOOKUP(K36,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K36&lt;&gt;"",VLOOKUP(K36,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S36" s="7" t="str">
@@ -7986,19 +8068,19 @@
         <v>4</v>
       </c>
       <c r="N37" s="7">
-        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1013</v>
       </c>
       <c r="O37" s="7">
-        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="P37" s="7">
-        <f>IF(J37&lt;&gt;"",VLOOKUP(J37,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J37&lt;&gt;"",VLOOKUP(J37,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="Q37" s="7">
-        <f>IF(K37&lt;&gt;"",VLOOKUP(K37,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K37&lt;&gt;"",VLOOKUP(K37,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="S37" s="7" t="str">
@@ -8035,19 +8117,19 @@
         <v>5</v>
       </c>
       <c r="N38" s="7">
-        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O38" s="7">
-        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P38" s="7">
-        <f>IF(J38&lt;&gt;"",VLOOKUP(J38,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J38&lt;&gt;"",VLOOKUP(J38,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="Q38" s="7">
-        <f>IF(K38&lt;&gt;"",VLOOKUP(K38,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K38&lt;&gt;"",VLOOKUP(K38,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="S38" s="7" t="str">
@@ -8084,19 +8166,19 @@
         <v>5</v>
       </c>
       <c r="N39" s="7">
-        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="O39" s="7">
-        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="P39" s="7">
-        <f>IF(J39&lt;&gt;"",VLOOKUP(J39,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J39&lt;&gt;"",VLOOKUP(J39,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="Q39" s="7">
-        <f>IF(K39&lt;&gt;"",VLOOKUP(K39,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K39&lt;&gt;"",VLOOKUP(K39,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="S39" s="7" t="str">
@@ -8125,19 +8207,19 @@
         <v>1</v>
       </c>
       <c r="N40" s="7">
-        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1017</v>
       </c>
       <c r="O40" s="7" t="str">
-        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P40" s="7" t="str">
-        <f>IF(J40&lt;&gt;"",VLOOKUP(J40,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J40&lt;&gt;"",VLOOKUP(J40,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q40" s="7" t="str">
-        <f>IF(K40&lt;&gt;"",VLOOKUP(K40,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K40&lt;&gt;"",VLOOKUP(K40,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S40" s="7" t="str">
@@ -8169,19 +8251,19 @@
         <v>4</v>
       </c>
       <c r="N41" s="7">
-        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O41" s="7">
-        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P41" s="7">
-        <f>IF(J41&lt;&gt;"",VLOOKUP(J41,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J41&lt;&gt;"",VLOOKUP(J41,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="Q41" s="7">
-        <f>IF(K41&lt;&gt;"",VLOOKUP(K41,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K41&lt;&gt;"",VLOOKUP(K41,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="S41" s="7" t="str">
@@ -8217,19 +8299,19 @@
         <v>4</v>
       </c>
       <c r="N42" s="7">
-        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="O42" s="7">
-        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P42" s="7">
-        <f>IF(J42&lt;&gt;"",VLOOKUP(J42,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J42&lt;&gt;"",VLOOKUP(J42,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q42" s="7">
-        <f>IF(K42&lt;&gt;"",VLOOKUP(K42,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K42&lt;&gt;"",VLOOKUP(K42,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="S42" s="7" t="str">
@@ -8258,19 +8340,19 @@
         <v>3</v>
       </c>
       <c r="N43" s="7">
-        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O43" s="7">
-        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P43" s="7" t="str">
-        <f>IF(J43&lt;&gt;"",VLOOKUP(J43,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J43&lt;&gt;"",VLOOKUP(J43,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q43" s="7" t="str">
-        <f>IF(K43&lt;&gt;"",VLOOKUP(K43,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K43&lt;&gt;"",VLOOKUP(K43,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S43" s="7" t="str">
@@ -8302,19 +8384,19 @@
         <v>3</v>
       </c>
       <c r="N44" s="7">
-        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O44" s="7">
-        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="P44" s="7">
-        <f>IF(J44&lt;&gt;"",VLOOKUP(J44,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J44&lt;&gt;"",VLOOKUP(J44,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="Q44" s="7" t="str">
-        <f>IF(K44&lt;&gt;"",VLOOKUP(K44,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K44&lt;&gt;"",VLOOKUP(K44,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S44" s="7" t="str">
@@ -8345,19 +8427,19 @@
         <v>4</v>
       </c>
       <c r="N45" s="7">
-        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O45" s="7">
-        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="P45" s="7">
-        <f>IF(J45&lt;&gt;"",VLOOKUP(J45,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J45&lt;&gt;"",VLOOKUP(J45,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3113</v>
       </c>
       <c r="Q45" s="7" t="str">
-        <f>IF(K45&lt;&gt;"",VLOOKUP(K45,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K45&lt;&gt;"",VLOOKUP(K45,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S45" s="7" t="str">
@@ -8388,19 +8470,19 @@
         <v>4</v>
       </c>
       <c r="N46" s="7">
-        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O46" s="7">
-        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="P46" s="7">
-        <f>IF(J46&lt;&gt;"",VLOOKUP(J46,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J46&lt;&gt;"",VLOOKUP(J46,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="Q46" s="7" t="str">
-        <f>IF(K46&lt;&gt;"",VLOOKUP(K46,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K46&lt;&gt;"",VLOOKUP(K46,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S46" s="7" t="str">
@@ -8431,19 +8513,19 @@
         <v>4</v>
       </c>
       <c r="N47" s="7">
-        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O47" s="7">
-        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="P47" s="7" t="str">
-        <f>IF(J47&lt;&gt;"",VLOOKUP(J47,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J47&lt;&gt;"",VLOOKUP(J47,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q47" s="7" t="str">
-        <f>IF(K47&lt;&gt;"",VLOOKUP(K47,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K47&lt;&gt;"",VLOOKUP(K47,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S47" s="7" t="str">
@@ -8476,19 +8558,19 @@
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7">
-        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="O48" s="7">
-        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P48" s="7" t="str">
-        <f>IF(J48&lt;&gt;"",VLOOKUP(J48,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J48&lt;&gt;"",VLOOKUP(J48,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q48" s="7" t="str">
-        <f>IF(K48&lt;&gt;"",VLOOKUP(K48,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K48&lt;&gt;"",VLOOKUP(K48,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S48" s="7" t="str">
@@ -8521,19 +8603,19 @@
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7">
-        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O49" s="7">
-        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P49" s="7" t="str">
-        <f>IF(J49&lt;&gt;"",VLOOKUP(J49,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J49&lt;&gt;"",VLOOKUP(J49,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q49" s="7" t="str">
-        <f>IF(K49&lt;&gt;"",VLOOKUP(K49,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K49&lt;&gt;"",VLOOKUP(K49,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S49" s="7" t="str">
@@ -8568,19 +8650,19 @@
         <v>3</v>
       </c>
       <c r="N50" s="7">
-        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1020</v>
       </c>
       <c r="O50" s="7">
-        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P50" s="7">
-        <f>IF(J50&lt;&gt;"",VLOOKUP(J50,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J50&lt;&gt;"",VLOOKUP(J50,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q50" s="7" t="str">
-        <f>IF(K50&lt;&gt;"",VLOOKUP(K50,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K50&lt;&gt;"",VLOOKUP(K50,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S50" s="7" t="str">
@@ -8612,19 +8694,19 @@
         <v>2</v>
       </c>
       <c r="N51" s="7">
-        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3129</v>
       </c>
       <c r="O51" s="7">
-        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P51" s="7" t="str">
-        <f>IF(J51&lt;&gt;"",VLOOKUP(J51,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J51&lt;&gt;"",VLOOKUP(J51,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q51" s="7" t="str">
-        <f>IF(K51&lt;&gt;"",VLOOKUP(K51,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K51&lt;&gt;"",VLOOKUP(K51,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S51" s="7" t="str">
@@ -8657,19 +8739,19 @@
       <c r="K52" s="7"/>
       <c r="L52" s="8"/>
       <c r="N52" s="7">
-        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="O52" s="7">
-        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P52" s="7">
-        <f>IF(J52&lt;&gt;"",VLOOKUP(J52,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J52&lt;&gt;"",VLOOKUP(J52,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q52" s="7" t="str">
-        <f>IF(K52&lt;&gt;"",VLOOKUP(K52,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K52&lt;&gt;"",VLOOKUP(K52,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S52" s="7" t="str">
@@ -8705,19 +8787,19 @@
         <v>3</v>
       </c>
       <c r="N53" s="7">
-        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3126</v>
       </c>
       <c r="O53" s="7">
-        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P53" s="7">
-        <f>IF(J53&lt;&gt;"",VLOOKUP(J53,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J53&lt;&gt;"",VLOOKUP(J53,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q53" s="7" t="str">
-        <f>IF(K53&lt;&gt;"",VLOOKUP(K53,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K53&lt;&gt;"",VLOOKUP(K53,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S53" s="7" t="str">
@@ -8755,19 +8837,19 @@
         <v>4</v>
       </c>
       <c r="N54" s="7">
-        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="O54" s="7">
-        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="P54" s="7">
-        <f>IF(J54&lt;&gt;"",VLOOKUP(J54,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J54&lt;&gt;"",VLOOKUP(J54,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3121</v>
       </c>
       <c r="Q54" s="7">
-        <f>IF(K54&lt;&gt;"",VLOOKUP(K54,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K54&lt;&gt;"",VLOOKUP(K54,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="S54" s="7" t="str">
@@ -8805,19 +8887,19 @@
         <v>4</v>
       </c>
       <c r="N55" s="7">
-        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3122</v>
       </c>
       <c r="O55" s="7">
-        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3124</v>
       </c>
       <c r="P55" s="7">
-        <f>IF(J55&lt;&gt;"",VLOOKUP(J55,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J55&lt;&gt;"",VLOOKUP(J55,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3127</v>
       </c>
       <c r="Q55" s="7">
-        <f>IF(K55&lt;&gt;"",VLOOKUP(K55,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K55&lt;&gt;"",VLOOKUP(K55,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="S55" s="7" t="str">
@@ -8849,19 +8931,19 @@
         <v>2</v>
       </c>
       <c r="N56" s="7">
-        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O56" s="7">
-        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P56" s="7" t="str">
-        <f>IF(J56&lt;&gt;"",VLOOKUP(J56,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J56&lt;&gt;"",VLOOKUP(J56,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q56" s="7" t="str">
-        <f>IF(K56&lt;&gt;"",VLOOKUP(K56,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K56&lt;&gt;"",VLOOKUP(K56,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S56" s="7" t="str">
@@ -8893,19 +8975,19 @@
         <v>2</v>
       </c>
       <c r="N57" s="7">
-        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4009</v>
       </c>
       <c r="O57" s="7">
-        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P57" s="7" t="str">
-        <f>IF(J57&lt;&gt;"",VLOOKUP(J57,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J57&lt;&gt;"",VLOOKUP(J57,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q57" s="7" t="str">
-        <f>IF(K57&lt;&gt;"",VLOOKUP(K57,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K57&lt;&gt;"",VLOOKUP(K57,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S57" s="7" t="str">
@@ -8937,19 +9019,19 @@
         <v>2</v>
       </c>
       <c r="N58" s="7">
-        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4015</v>
       </c>
       <c r="O58" s="7">
-        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P58" s="7" t="str">
-        <f>IF(J58&lt;&gt;"",VLOOKUP(J58,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J58&lt;&gt;"",VLOOKUP(J58,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q58" s="7" t="str">
-        <f>IF(K58&lt;&gt;"",VLOOKUP(K58,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K58&lt;&gt;"",VLOOKUP(K58,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S58" s="7" t="str">
@@ -8981,19 +9063,19 @@
         <v>2</v>
       </c>
       <c r="N59" s="7">
-        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4016</v>
       </c>
       <c r="O59" s="7">
-        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P59" s="7" t="str">
-        <f>IF(J59&lt;&gt;"",VLOOKUP(J59,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J59&lt;&gt;"",VLOOKUP(J59,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q59" s="7" t="str">
-        <f>IF(K59&lt;&gt;"",VLOOKUP(K59,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K59&lt;&gt;"",VLOOKUP(K59,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S59" s="7" t="str">
@@ -9025,19 +9107,19 @@
         <v>2</v>
       </c>
       <c r="N60" s="7">
-        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4017</v>
       </c>
       <c r="O60" s="7">
-        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P60" s="7" t="str">
-        <f>IF(J60&lt;&gt;"",VLOOKUP(J60,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J60&lt;&gt;"",VLOOKUP(J60,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q60" s="7" t="str">
-        <f>IF(K60&lt;&gt;"",VLOOKUP(K60,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K60&lt;&gt;"",VLOOKUP(K60,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S60" s="7" t="str">
@@ -9069,19 +9151,19 @@
         <v>2</v>
       </c>
       <c r="N61" s="7">
-        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O61" s="7">
-        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P61" s="7" t="str">
-        <f>IF(J61&lt;&gt;"",VLOOKUP(J61,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J61&lt;&gt;"",VLOOKUP(J61,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q61" s="7" t="str">
-        <f>IF(K61&lt;&gt;"",VLOOKUP(K61,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K61&lt;&gt;"",VLOOKUP(K61,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S61" s="7" t="str">
@@ -9113,19 +9195,19 @@
         <v>2</v>
       </c>
       <c r="N62" s="7">
-        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4100</v>
       </c>
       <c r="O62" s="7">
-        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P62" s="7" t="str">
-        <f>IF(J62&lt;&gt;"",VLOOKUP(J62,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J62&lt;&gt;"",VLOOKUP(J62,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q62" s="7" t="str">
-        <f>IF(K62&lt;&gt;"",VLOOKUP(K62,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K62&lt;&gt;"",VLOOKUP(K62,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S62" s="7" t="str">
@@ -9157,19 +9239,19 @@
         <v>2</v>
       </c>
       <c r="N63" s="7">
-        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4101</v>
       </c>
       <c r="O63" s="7">
-        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P63" s="7" t="str">
-        <f>IF(J63&lt;&gt;"",VLOOKUP(J63,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J63&lt;&gt;"",VLOOKUP(J63,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q63" s="7" t="str">
-        <f>IF(K63&lt;&gt;"",VLOOKUP(K63,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K63&lt;&gt;"",VLOOKUP(K63,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S63" s="7" t="str">
@@ -9201,19 +9283,19 @@
         <v>2</v>
       </c>
       <c r="N64" s="7">
-        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4103</v>
       </c>
       <c r="O64" s="7">
-        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P64" s="7" t="str">
-        <f>IF(J64&lt;&gt;"",VLOOKUP(J64,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J64&lt;&gt;"",VLOOKUP(J64,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q64" s="7" t="str">
-        <f>IF(K64&lt;&gt;"",VLOOKUP(K64,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K64&lt;&gt;"",VLOOKUP(K64,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S64" s="7" t="str">
@@ -9245,19 +9327,19 @@
         <v>2</v>
       </c>
       <c r="N65" s="7">
-        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4106</v>
       </c>
       <c r="O65" s="7">
-        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P65" s="7" t="str">
-        <f>IF(J65&lt;&gt;"",VLOOKUP(J65,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J65&lt;&gt;"",VLOOKUP(J65,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q65" s="7" t="str">
-        <f>IF(K65&lt;&gt;"",VLOOKUP(K65,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K65&lt;&gt;"",VLOOKUP(K65,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S65" s="7" t="str">
@@ -9289,19 +9371,19 @@
         <v>2</v>
       </c>
       <c r="N66" s="7">
-        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O66" s="7">
-        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P66" s="7" t="str">
-        <f>IF(J66&lt;&gt;"",VLOOKUP(J66,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J66&lt;&gt;"",VLOOKUP(J66,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q66" s="7" t="str">
-        <f>IF(K66&lt;&gt;"",VLOOKUP(K66,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K66&lt;&gt;"",VLOOKUP(K66,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S66" s="7" t="str">
@@ -9327,19 +9409,19 @@
         <v>2</v>
       </c>
       <c r="N67" s="7">
-        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O67" s="7">
-        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P67" s="7" t="str">
-        <f>IF(J67&lt;&gt;"",VLOOKUP(J67,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J67&lt;&gt;"",VLOOKUP(J67,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q67" s="7" t="str">
-        <f>IF(K67&lt;&gt;"",VLOOKUP(K67,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K67&lt;&gt;"",VLOOKUP(K67,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S67" s="7" t="str">
@@ -9366,19 +9448,19 @@
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7">
-        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O68" s="7">
-        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P68" s="7" t="str">
-        <f>IF(J68&lt;&gt;"",VLOOKUP(J68,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J68&lt;&gt;"",VLOOKUP(J68,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q68" s="7" t="str">
-        <f>IF(K68&lt;&gt;"",VLOOKUP(K68,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K68&lt;&gt;"",VLOOKUP(K68,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S68" s="7" t="str">
@@ -9404,19 +9486,19 @@
         <v>2</v>
       </c>
       <c r="N69" s="7">
-        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O69" s="7">
-        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P69" s="7" t="str">
-        <f>IF(J69&lt;&gt;"",VLOOKUP(J69,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J69&lt;&gt;"",VLOOKUP(J69,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q69" s="7" t="str">
-        <f>IF(K69&lt;&gt;"",VLOOKUP(K69,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K69&lt;&gt;"",VLOOKUP(K69,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S69" s="7" t="str">
@@ -9442,19 +9524,19 @@
         <v>2</v>
       </c>
       <c r="N70" s="7">
-        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4115</v>
       </c>
       <c r="O70" s="7">
-        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P70" s="7" t="str">
-        <f>IF(J70&lt;&gt;"",VLOOKUP(J70,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J70&lt;&gt;"",VLOOKUP(J70,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q70" s="7" t="str">
-        <f>IF(K70&lt;&gt;"",VLOOKUP(K70,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K70&lt;&gt;"",VLOOKUP(K70,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S70" s="7" t="str">
@@ -9481,19 +9563,19 @@
         <v>2</v>
       </c>
       <c r="N71" s="7">
-        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O71" s="7">
-        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P71" s="7" t="str">
-        <f>IF(J71&lt;&gt;"",VLOOKUP(J71,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J71&lt;&gt;"",VLOOKUP(J71,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q71" s="7" t="str">
-        <f>IF(K71&lt;&gt;"",VLOOKUP(K71,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K71&lt;&gt;"",VLOOKUP(K71,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S71" s="7" t="str">
@@ -9520,19 +9602,19 @@
         <v>2</v>
       </c>
       <c r="N72" s="7">
-        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4007</v>
       </c>
       <c r="O72" s="7">
-        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="P72" s="7" t="str">
-        <f>IF(J72&lt;&gt;"",VLOOKUP(J72,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J72&lt;&gt;"",VLOOKUP(J72,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q72" s="7" t="str">
-        <f>IF(K72&lt;&gt;"",VLOOKUP(K72,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K72&lt;&gt;"",VLOOKUP(K72,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S72" s="7" t="str">
@@ -9564,19 +9646,19 @@
         <v>3</v>
       </c>
       <c r="N73" s="7">
-        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="O73" s="7">
-        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="P73" s="7">
-        <f>IF(J73&lt;&gt;"",VLOOKUP(J73,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J73&lt;&gt;"",VLOOKUP(J73,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4100</v>
       </c>
       <c r="Q73" s="7">
-        <f>IF(K73&lt;&gt;"",VLOOKUP(K73,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K73&lt;&gt;"",VLOOKUP(K73,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="S73" s="7" t="str">
@@ -9601,25 +9683,25 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N74" s="7">
-        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
-        <v>3153</v>
+      <c r="N74" s="7" t="e">
+        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
+        <v>#N/A</v>
       </c>
       <c r="O74" s="7">
-        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P74" s="7" t="str">
-        <f>IF(J74&lt;&gt;"",VLOOKUP(J74,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J74&lt;&gt;"",VLOOKUP(J74,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q74" s="7" t="str">
-        <f>IF(K74&lt;&gt;"",VLOOKUP(K74,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="S74" s="7" t="str">
+        <f>IF(K74&lt;&gt;"",VLOOKUP(K74,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="S74" s="7" t="e">
         <f t="shared" si="3"/>
-        <v>3153,3000</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -9650,19 +9732,19 @@
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7">
-        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4000</v>
       </c>
       <c r="O75" s="7">
-        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="P75" s="7">
-        <f>IF(J75&lt;&gt;"",VLOOKUP(J75,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J75&lt;&gt;"",VLOOKUP(J75,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3004</v>
       </c>
       <c r="Q75" s="7">
-        <f>IF(K75&lt;&gt;"",VLOOKUP(K75,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K75&lt;&gt;"",VLOOKUP(K75,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1017</v>
       </c>
       <c r="S75" s="7" t="str">
@@ -9689,19 +9771,19 @@
         <v>2</v>
       </c>
       <c r="N76" s="7">
-        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O76" s="7">
-        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="P76" s="7" t="str">
-        <f>IF(J76&lt;&gt;"",VLOOKUP(J76,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J76&lt;&gt;"",VLOOKUP(J76,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q76" s="7" t="str">
-        <f>IF(K76&lt;&gt;"",VLOOKUP(K76,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K76&lt;&gt;"",VLOOKUP(K76,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S76" s="7" t="str">
@@ -9724,19 +9806,19 @@
         <v>1</v>
       </c>
       <c r="N77" s="7">
-        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O77" s="7" t="str">
-        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P77" s="7" t="str">
-        <f>IF(J77&lt;&gt;"",VLOOKUP(J77,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J77&lt;&gt;"",VLOOKUP(J77,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q77" s="7" t="str">
-        <f>IF(K77&lt;&gt;"",VLOOKUP(K77,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K77&lt;&gt;"",VLOOKUP(K77,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S77" s="7" t="str">
@@ -9765,19 +9847,19 @@
         <v>3</v>
       </c>
       <c r="N78" s="7">
-        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="O78" s="7">
-        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P78" s="7">
-        <f>IF(J78&lt;&gt;"",VLOOKUP(J78,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J78&lt;&gt;"",VLOOKUP(J78,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="Q78" s="7" t="str">
-        <f>IF(K78&lt;&gt;"",VLOOKUP(K78,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K78&lt;&gt;"",VLOOKUP(K78,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S78" s="7" t="str">
@@ -9804,19 +9886,19 @@
         <v>2</v>
       </c>
       <c r="N79" s="7">
-        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O79" s="7">
-        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="P79" s="7" t="str">
-        <f>IF(J79&lt;&gt;"",VLOOKUP(J79,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J79&lt;&gt;"",VLOOKUP(J79,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q79" s="7" t="str">
-        <f>IF(K79&lt;&gt;"",VLOOKUP(K79,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K79&lt;&gt;"",VLOOKUP(K79,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S79" s="7" t="str">
@@ -9838,19 +9920,19 @@
       <c r="K80" s="7"/>
       <c r="L80" s="8"/>
       <c r="N80" s="7">
-        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O80" s="7" t="str">
-        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P80" s="7" t="str">
-        <f>IF(J80&lt;&gt;"",VLOOKUP(J80,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J80&lt;&gt;"",VLOOKUP(J80,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q80" s="7" t="str">
-        <f>IF(K80&lt;&gt;"",VLOOKUP(K80,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K80&lt;&gt;"",VLOOKUP(K80,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S80" s="7" t="str">
@@ -9873,19 +9955,19 @@
         <v>1</v>
       </c>
       <c r="N81" s="7">
-        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O81" s="7" t="str">
-        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P81" s="7" t="str">
-        <f>IF(J81&lt;&gt;"",VLOOKUP(J81,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J81&lt;&gt;"",VLOOKUP(J81,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q81" s="7" t="str">
-        <f>IF(K81&lt;&gt;"",VLOOKUP(K81,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K81&lt;&gt;"",VLOOKUP(K81,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S81" s="7" t="str">
@@ -9918,19 +10000,19 @@
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="7">
-        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O82" s="7">
-        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="P82" s="7">
-        <f>IF(J82&lt;&gt;"",VLOOKUP(J82,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J82&lt;&gt;"",VLOOKUP(J82,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q82" s="7">
-        <f>IF(K82&lt;&gt;"",VLOOKUP(K82,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K82&lt;&gt;"",VLOOKUP(K82,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1007</v>
       </c>
       <c r="S82" s="7" t="str">
@@ -9953,19 +10035,19 @@
         <v>1</v>
       </c>
       <c r="N83" s="7">
-        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O83" s="7" t="str">
-        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P83" s="7" t="str">
-        <f>IF(J83&lt;&gt;"",VLOOKUP(J83,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J83&lt;&gt;"",VLOOKUP(J83,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q83" s="7" t="str">
-        <f>IF(K83&lt;&gt;"",VLOOKUP(K83,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K83&lt;&gt;"",VLOOKUP(K83,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S83" s="7" t="str">
@@ -9996,25 +10078,25 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="N84" s="7">
-        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
-        <v>3164</v>
+      <c r="N84" s="7" t="e">
+        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
+        <v>#N/A</v>
       </c>
       <c r="O84" s="7">
-        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>3134</v>
       </c>
       <c r="P84" s="7">
-        <f>IF(J84&lt;&gt;"",VLOOKUP(J84,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(J84&lt;&gt;"",VLOOKUP(J84,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="Q84" s="7">
-        <f>IF(K84&lt;&gt;"",VLOOKUP(K84,[1]ItemData!$A$4:$B$212,2,FALSE),"")</f>
+        <f>IF(K84&lt;&gt;"",VLOOKUP(K84,[1]ItemData!$A$4:$B$222,2,FALSE),"")</f>
         <v>4021</v>
       </c>
-      <c r="S84" s="7" t="str">
+      <c r="S84" s="7" t="e">
         <f t="shared" si="3"/>
-        <v>3164,3134,1006,4021</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="85" spans="5:19" x14ac:dyDescent="0.2">
@@ -10376,7 +10458,7 @@
       <c r="G203" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="D4:J4"/>
+  <autoFilter ref="D4:J84"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="491">
   <si>
     <t>芜菁</t>
   </si>
@@ -1681,6 +1681,10 @@
   </si>
   <si>
     <t>金枪鱼刺身</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯净水</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1848,7 +1852,6 @@
     <sheetNames>
       <sheetName val="ItemData"/>
       <sheetName val="Sheet2"/>
-      <sheetName val="Sheet1"/>
       <sheetName val="Sheet3"/>
     </sheetNames>
     <sheetDataSet>
@@ -1943,2920 +1946,3047 @@
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>牧草</v>
+            <v>食物配方</v>
           </cell>
           <cell r="B15">
-            <v>100</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>木材</v>
+            <v>酒水配方</v>
           </cell>
           <cell r="B16">
-            <v>101</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>原木</v>
+            <v>铸造配方</v>
           </cell>
           <cell r="B17">
-            <v>102</v>
+            <v>22</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>木柴</v>
+            <v>缝纫配方</v>
           </cell>
           <cell r="B18">
-            <v>103</v>
+            <v>23</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>木棒</v>
+            <v>书写配方</v>
           </cell>
           <cell r="B19">
-            <v>104</v>
+            <v>24</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>干草</v>
+            <v>牧草</v>
           </cell>
           <cell r="B20">
-            <v>105</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>纯净水</v>
+            <v>木材</v>
           </cell>
           <cell r="B21">
-            <v>200</v>
+            <v>101</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>石块</v>
+            <v>原木</v>
           </cell>
           <cell r="B22">
-            <v>201</v>
+            <v>102</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>龟壳</v>
+            <v>木柴</v>
           </cell>
           <cell r="B23">
-            <v>202</v>
+            <v>103</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>兽皮</v>
+            <v>木棒</v>
           </cell>
           <cell r="B24">
-            <v>203</v>
+            <v>104</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
-            <v>布片</v>
+            <v>干草</v>
           </cell>
           <cell r="B25">
-            <v>204</v>
+            <v>105</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>石英砂</v>
+            <v>纯净水</v>
           </cell>
           <cell r="B26">
-            <v>205</v>
+            <v>200</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>草药茶</v>
+            <v>石块</v>
           </cell>
           <cell r="B27">
-            <v>207</v>
+            <v>201</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>风晶石</v>
+            <v>龟壳</v>
           </cell>
           <cell r="B28">
-            <v>208</v>
+            <v>202</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
-            <v>琥珀</v>
+            <v>兽皮</v>
           </cell>
           <cell r="B29">
-            <v>210</v>
+            <v>203</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
-            <v>狼牙</v>
+            <v>布片</v>
           </cell>
           <cell r="B30">
-            <v>211</v>
+            <v>204</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
-            <v>粘土</v>
+            <v>石英砂</v>
           </cell>
           <cell r="B31">
-            <v>212</v>
+            <v>205</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
-            <v>尖刺</v>
+            <v>草药茶</v>
           </cell>
           <cell r="B32">
-            <v>213</v>
+            <v>207</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>蛛丝</v>
+            <v>风晶石</v>
           </cell>
           <cell r="B33">
-            <v>214</v>
+            <v>208</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
-            <v>铁矿</v>
+            <v>琥珀</v>
           </cell>
           <cell r="B34">
-            <v>215</v>
+            <v>210</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
-            <v>盐矿</v>
+            <v>狼牙</v>
           </cell>
           <cell r="B35">
-            <v>216</v>
+            <v>211</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
-            <v>肥皂</v>
+            <v>粘土</v>
           </cell>
           <cell r="B36">
-            <v>217</v>
+            <v>212</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>土晶石</v>
+            <v>尖刺</v>
           </cell>
           <cell r="B37">
-            <v>218</v>
+            <v>213</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>迷幻菇</v>
+            <v>蛛丝</v>
           </cell>
           <cell r="B38">
-            <v>219</v>
+            <v>214</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
-            <v>眼球</v>
+            <v>铁矿</v>
           </cell>
           <cell r="B39">
-            <v>220</v>
+            <v>215</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
-            <v>植物的藤</v>
+            <v>盐矿</v>
           </cell>
           <cell r="B40">
-            <v>221</v>
+            <v>216</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
-            <v>鹿角</v>
+            <v>肥皂</v>
           </cell>
           <cell r="B41">
-            <v>222</v>
+            <v>217</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
-            <v>魔兽皮毛</v>
+            <v>土晶石</v>
           </cell>
           <cell r="B42">
-            <v>223</v>
+            <v>218</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>奇美拉之翼</v>
+            <v>迷幻菇</v>
           </cell>
           <cell r="B43">
-            <v>224</v>
+            <v>219</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44" t="str">
-            <v>电偶瓶</v>
+            <v>眼球</v>
           </cell>
           <cell r="B44">
-            <v>225</v>
+            <v>220</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
-            <v>海胆</v>
+            <v>植物的藤</v>
           </cell>
           <cell r="B45">
-            <v>226</v>
+            <v>221</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
-            <v>珊瑚</v>
+            <v>鹿角</v>
           </cell>
           <cell r="B46">
-            <v>227</v>
+            <v>222</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
-            <v>彩色羽毛</v>
+            <v>魔兽皮毛</v>
           </cell>
           <cell r="B47">
-            <v>228</v>
+            <v>223</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48" t="str">
-            <v>火晶石</v>
+            <v>奇美拉之翼</v>
           </cell>
           <cell r="B48">
-            <v>229</v>
+            <v>224</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49" t="str">
-            <v>玻璃瓶</v>
+            <v>电偶瓶</v>
           </cell>
           <cell r="B49">
-            <v>230</v>
+            <v>225</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50" t="str">
-            <v>水晶石</v>
+            <v>海胆</v>
           </cell>
           <cell r="B50">
-            <v>232</v>
+            <v>226</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51" t="str">
-            <v>珍珠</v>
+            <v>珊瑚</v>
           </cell>
           <cell r="B51">
-            <v>234</v>
+            <v>227</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52" t="str">
-            <v>松果</v>
+            <v>彩色羽毛</v>
           </cell>
           <cell r="B52">
-            <v>235</v>
+            <v>228</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53" t="str">
-            <v>神奇泥浆</v>
+            <v>火晶石</v>
           </cell>
           <cell r="B53">
-            <v>236</v>
+            <v>229</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
-            <v>银块</v>
+            <v>玻璃瓶</v>
           </cell>
           <cell r="B54">
-            <v>237</v>
+            <v>230</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
-            <v>蛇皮</v>
+            <v>水晶石</v>
           </cell>
           <cell r="B55">
-            <v>238</v>
+            <v>232</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
-            <v>蜂刺</v>
+            <v>珍珠</v>
           </cell>
           <cell r="B56">
-            <v>239</v>
+            <v>234</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57" t="str">
-            <v>象牙</v>
+            <v>松果</v>
           </cell>
           <cell r="B57">
-            <v>240</v>
+            <v>235</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
-            <v>兽角</v>
+            <v>神奇泥浆</v>
           </cell>
           <cell r="B58">
-            <v>241</v>
+            <v>236</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59" t="str">
-            <v>水晶球</v>
+            <v>银块</v>
           </cell>
           <cell r="B59">
-            <v>242</v>
+            <v>237</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
-            <v>蝎尾</v>
+            <v>蛇皮</v>
           </cell>
           <cell r="B60">
-            <v>243</v>
+            <v>238</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61" t="str">
-            <v>仙人掌</v>
+            <v>蜂刺</v>
           </cell>
           <cell r="B61">
-            <v>244</v>
+            <v>239</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62" t="str">
-            <v>脏绷带</v>
+            <v>象牙</v>
           </cell>
           <cell r="B62">
-            <v>245</v>
+            <v>240</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
-            <v>幽魂</v>
+            <v>兽角</v>
           </cell>
           <cell r="B63">
-            <v>246</v>
+            <v>241</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64" t="str">
-            <v>金块</v>
+            <v>水晶球</v>
           </cell>
           <cell r="B64">
-            <v>247</v>
+            <v>242</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65" t="str">
-            <v>远古的硬币</v>
+            <v>蝎尾</v>
           </cell>
           <cell r="B65">
-            <v>248</v>
+            <v>243</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
-            <v>铁钉</v>
+            <v>仙人掌</v>
           </cell>
           <cell r="B66">
-            <v>249</v>
+            <v>244</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
-            <v>遗骨</v>
+            <v>脏绷带</v>
           </cell>
           <cell r="B67">
-            <v>250</v>
+            <v>245</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68" t="str">
-            <v>妖精粉</v>
+            <v>幽魂</v>
           </cell>
           <cell r="B68">
-            <v>251</v>
+            <v>246</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69" t="str">
-            <v>雪球</v>
+            <v>金块</v>
           </cell>
           <cell r="B69">
-            <v>253</v>
+            <v>247</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70" t="str">
-            <v>毒淤泥</v>
+            <v>远古的硬币</v>
           </cell>
           <cell r="B70">
-            <v>254</v>
+            <v>248</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
-            <v>亡者之土</v>
+            <v>铁钉</v>
           </cell>
           <cell r="B71">
-            <v>255</v>
+            <v>249</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72" t="str">
-            <v>咒术药水</v>
+            <v>遗骨</v>
           </cell>
           <cell r="B72">
-            <v>256</v>
+            <v>250</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
-            <v>诅咒宝珠</v>
+            <v>妖精粉</v>
           </cell>
           <cell r="B73">
-            <v>257</v>
+            <v>251</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
-            <v>人狼之证</v>
+            <v>雪球</v>
           </cell>
           <cell r="B74">
-            <v>258</v>
+            <v>253</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
-            <v>魔族之血</v>
+            <v>毒淤泥</v>
           </cell>
           <cell r="B75">
-            <v>259</v>
+            <v>254</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
-            <v>冰晶石</v>
+            <v>亡者之土</v>
           </cell>
           <cell r="B76">
-            <v>260</v>
+            <v>255</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
-            <v>冰的结晶</v>
+            <v>咒术药水</v>
           </cell>
           <cell r="B77">
-            <v>261</v>
+            <v>256</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
-            <v>石化之眼</v>
+            <v>诅咒宝珠</v>
           </cell>
           <cell r="B78">
-            <v>263</v>
+            <v>257</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
-            <v>夜之幕</v>
+            <v>人狼之证</v>
           </cell>
           <cell r="B79">
-            <v>264</v>
+            <v>258</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80" t="str">
-            <v>星的眼泪</v>
+            <v>魔族之血</v>
           </cell>
           <cell r="B80">
-            <v>265</v>
+            <v>259</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
-            <v>冰牛角</v>
+            <v>冰晶石</v>
           </cell>
           <cell r="B81">
-            <v>266</v>
+            <v>260</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
-            <v>寒冰气息</v>
+            <v>冰的结晶</v>
           </cell>
           <cell r="B82">
-            <v>267</v>
+            <v>261</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83" t="str">
-            <v>寒冰火种</v>
+            <v>石化之眼</v>
           </cell>
           <cell r="B83">
-            <v>268</v>
+            <v>263</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84" t="str">
-            <v>幻影水晶</v>
+            <v>夜之幕</v>
           </cell>
           <cell r="B84">
-            <v>269</v>
+            <v>264</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
-            <v>雷鸣宝珠</v>
+            <v>星的眼泪</v>
           </cell>
           <cell r="B85">
-            <v>270</v>
+            <v>265</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86" t="str">
-            <v>皮革</v>
+            <v>冰牛角</v>
           </cell>
           <cell r="B86">
-            <v>271</v>
+            <v>266</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87" t="str">
-            <v>彩色的布</v>
+            <v>寒冰气息</v>
           </cell>
           <cell r="B87">
-            <v>272</v>
+            <v>267</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88" t="str">
-            <v>鳞片</v>
+            <v>寒冰火种</v>
           </cell>
           <cell r="B88">
-            <v>273</v>
+            <v>268</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89" t="str">
-            <v>刀刃</v>
+            <v>幻影水晶</v>
           </cell>
           <cell r="B89">
-            <v>274</v>
+            <v>269</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
-            <v>骑士之证</v>
+            <v>雷鸣宝珠</v>
           </cell>
           <cell r="B90">
-            <v>275</v>
+            <v>270</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
-            <v>马尾</v>
+            <v>皮革</v>
           </cell>
           <cell r="B91">
-            <v>276</v>
+            <v>271</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
-            <v>毛线</v>
+            <v>彩色的布</v>
           </cell>
           <cell r="B92">
-            <v>277</v>
+            <v>272</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
-            <v>粘液</v>
+            <v>鳞片</v>
           </cell>
           <cell r="B93">
-            <v>278</v>
+            <v>273</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
-            <v>贵族徽章</v>
+            <v>刀刃</v>
           </cell>
           <cell r="B94">
-            <v>279</v>
+            <v>274</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
-            <v>武道精华</v>
+            <v>骑士之证</v>
           </cell>
           <cell r="B95">
-            <v>280</v>
+            <v>275</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96" t="str">
-            <v>贤者晶石</v>
+            <v>马尾</v>
           </cell>
           <cell r="B96">
-            <v>281</v>
+            <v>276</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97" t="str">
-            <v>防水皮革</v>
+            <v>毛线</v>
           </cell>
           <cell r="B97">
-            <v>282</v>
+            <v>277</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98" t="str">
-            <v>羊毛</v>
+            <v>粘液</v>
           </cell>
           <cell r="B98">
-            <v>283</v>
+            <v>278</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99" t="str">
-            <v>白磷粉末</v>
+            <v>贵族徽章</v>
           </cell>
           <cell r="B99">
-            <v>284</v>
+            <v>279</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
-            <v>暮光结晶</v>
+            <v>武道精华</v>
           </cell>
           <cell r="B100">
-            <v>285</v>
+            <v>280</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
-            <v>魔力之土</v>
+            <v>贤者晶石</v>
           </cell>
           <cell r="B101">
-            <v>286</v>
+            <v>281</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102" t="str">
-            <v>迷幻孢子</v>
+            <v>防水皮革</v>
           </cell>
           <cell r="B102">
-            <v>287</v>
+            <v>282</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
-            <v>力量果实</v>
+            <v>羊毛</v>
           </cell>
           <cell r="B103">
-            <v>288</v>
+            <v>283</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104" t="str">
-            <v>恶魔花瓣</v>
+            <v>白磷粉末</v>
           </cell>
           <cell r="B104">
-            <v>289</v>
+            <v>284</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
-            <v>月之光华</v>
+            <v>暮光结晶</v>
           </cell>
           <cell r="B105">
-            <v>290</v>
+            <v>285</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
-            <v>萤火树汁</v>
+            <v>魔力之土</v>
           </cell>
           <cell r="B106">
-            <v>291</v>
+            <v>286</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
-            <v>暗夜之露</v>
+            <v>迷幻孢子</v>
           </cell>
           <cell r="B107">
-            <v>292</v>
+            <v>287</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108" t="str">
-            <v>魅惑药水</v>
+            <v>力量果实</v>
           </cell>
           <cell r="B108">
-            <v>293</v>
+            <v>288</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
-            <v>图腾号角</v>
+            <v>恶魔花瓣</v>
           </cell>
           <cell r="B109">
-            <v>294</v>
+            <v>289</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110" t="str">
-            <v>空白卷轴</v>
+            <v>月之光华</v>
           </cell>
           <cell r="B110">
-            <v>295</v>
+            <v>290</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
-            <v>废铁</v>
+            <v>萤火树汁</v>
           </cell>
           <cell r="B111">
-            <v>296</v>
+            <v>291</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
-            <v>焦炭</v>
+            <v>暗夜之露</v>
           </cell>
           <cell r="B112">
-            <v>297</v>
+            <v>292</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
-            <v>铁块</v>
+            <v>魅惑药水</v>
           </cell>
           <cell r="B113">
-            <v>298</v>
+            <v>293</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>钢</v>
+            <v>图腾号角</v>
           </cell>
           <cell r="B114">
-            <v>299</v>
+            <v>294</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
-            <v>芜菁</v>
+            <v>空白卷轴</v>
           </cell>
           <cell r="B115">
-            <v>1001</v>
+            <v>295</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
-            <v>卷心菜</v>
+            <v>废铁</v>
           </cell>
           <cell r="B116">
-            <v>1002</v>
+            <v>296</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
-            <v>葱</v>
+            <v>焦炭</v>
           </cell>
           <cell r="B117">
-            <v>1003</v>
+            <v>297</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
-            <v>萝卜</v>
+            <v>铁块</v>
           </cell>
           <cell r="B118">
-            <v>1004</v>
+            <v>298</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
-            <v>紫甘蓝</v>
+            <v>钢</v>
           </cell>
           <cell r="B119">
-            <v>1005</v>
+            <v>299</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
-            <v>黄瓜</v>
+            <v>猪粪</v>
           </cell>
           <cell r="B120">
-            <v>1006</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
-            <v>西兰花</v>
+            <v>鸭绒</v>
           </cell>
           <cell r="B121">
-            <v>1007</v>
+            <v>301</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122" t="str">
-            <v>番茄</v>
+            <v>兔子脚</v>
           </cell>
           <cell r="B122">
-            <v>1008</v>
+            <v>302</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
-            <v>胡萝卜</v>
+            <v>芜菁</v>
           </cell>
           <cell r="B123">
-            <v>1009</v>
+            <v>1001</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124" t="str">
-            <v>西瓜</v>
+            <v>卷心菜</v>
           </cell>
           <cell r="B124">
-            <v>1010</v>
+            <v>1002</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
-            <v>辣椒</v>
+            <v>葱</v>
           </cell>
           <cell r="B125">
-            <v>1011</v>
+            <v>1003</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
-            <v>奇异果</v>
+            <v>萝卜</v>
           </cell>
           <cell r="B126">
-            <v>1012</v>
+            <v>1004</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
-            <v>茄子</v>
+            <v>紫甘蓝</v>
           </cell>
           <cell r="B127">
-            <v>1013</v>
+            <v>1005</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
-            <v>豌豆</v>
+            <v>黄瓜</v>
           </cell>
           <cell r="B128">
-            <v>1014</v>
+            <v>1006</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129" t="str">
-            <v>土豆</v>
+            <v>西兰花</v>
           </cell>
           <cell r="B129">
-            <v>1015</v>
+            <v>1007</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
-            <v>大蒜</v>
+            <v>番茄</v>
           </cell>
           <cell r="B130">
-            <v>1016</v>
+            <v>1008</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
-            <v>芦笋</v>
+            <v>胡萝卜</v>
           </cell>
           <cell r="B131">
-            <v>1017</v>
+            <v>1009</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
-            <v>南瓜</v>
+            <v>西瓜</v>
           </cell>
           <cell r="B132">
-            <v>1018</v>
+            <v>1010</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133" t="str">
-            <v>玉米</v>
+            <v>辣椒</v>
           </cell>
           <cell r="B133">
-            <v>1019</v>
+            <v>1011</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
-            <v>小麦</v>
+            <v>奇异果</v>
           </cell>
           <cell r="B134">
-            <v>1020</v>
+            <v>1012</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
-            <v>啤酒花</v>
+            <v>茄子</v>
           </cell>
           <cell r="B135">
-            <v>1021</v>
+            <v>1013</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
-            <v>葡萄</v>
+            <v>豌豆</v>
           </cell>
           <cell r="B136">
-            <v>1022</v>
+            <v>1014</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
-            <v>菠萝</v>
+            <v>土豆</v>
           </cell>
           <cell r="B137">
-            <v>1023</v>
+            <v>1015</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
-            <v>咖啡</v>
+            <v>大蒜</v>
           </cell>
           <cell r="B138">
-            <v>1024</v>
+            <v>1016</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
-            <v>草莓</v>
+            <v>芦笋</v>
           </cell>
           <cell r="B139">
-            <v>1025</v>
+            <v>1017</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
-            <v>蓝莓</v>
+            <v>南瓜</v>
           </cell>
           <cell r="B140">
-            <v>1026</v>
+            <v>1018</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141" t="str">
-            <v>红薯</v>
+            <v>玉米</v>
           </cell>
           <cell r="B141">
-            <v>1027</v>
+            <v>1019</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
-            <v>甜菜</v>
+            <v>小麦</v>
           </cell>
           <cell r="B142">
-            <v>1028</v>
+            <v>1020</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
-            <v>芜菁种子</v>
+            <v>啤酒花</v>
           </cell>
           <cell r="B143">
-            <v>1101</v>
+            <v>1021</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
-            <v>卷心菜种子</v>
+            <v>葡萄</v>
           </cell>
           <cell r="B144">
-            <v>1102</v>
+            <v>1022</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
-            <v>葱种子</v>
+            <v>菠萝</v>
           </cell>
           <cell r="B145">
-            <v>1103</v>
+            <v>1023</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
-            <v>萝卜种子</v>
+            <v>咖啡</v>
           </cell>
           <cell r="B146">
-            <v>1104</v>
+            <v>1024</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
-            <v>紫甘蓝种子</v>
+            <v>草莓</v>
           </cell>
           <cell r="B147">
-            <v>1105</v>
+            <v>1025</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148" t="str">
-            <v>黄瓜种子</v>
+            <v>蓝莓</v>
           </cell>
           <cell r="B148">
-            <v>1106</v>
+            <v>1026</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149" t="str">
-            <v>西兰花种子</v>
+            <v>红薯</v>
           </cell>
           <cell r="B149">
-            <v>1107</v>
+            <v>1027</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
-            <v>番茄种子</v>
+            <v>甜菜</v>
           </cell>
           <cell r="B150">
-            <v>1108</v>
+            <v>1028</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
-            <v>胡萝卜种子</v>
+            <v>芜菁种子</v>
           </cell>
           <cell r="B151">
-            <v>1109</v>
+            <v>1101</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
-            <v>西瓜种子</v>
+            <v>卷心菜种子</v>
           </cell>
           <cell r="B152">
-            <v>1110</v>
+            <v>1102</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
-            <v>辣椒种子</v>
+            <v>葱种子</v>
           </cell>
           <cell r="B153">
-            <v>1111</v>
+            <v>1103</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
-            <v>奇异果种子</v>
+            <v>萝卜种子</v>
           </cell>
           <cell r="B154">
-            <v>1112</v>
+            <v>1104</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
-            <v>茄子种子</v>
+            <v>紫甘蓝种子</v>
           </cell>
           <cell r="B155">
-            <v>1113</v>
+            <v>1105</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
-            <v>豌豆种子</v>
+            <v>黄瓜种子</v>
           </cell>
           <cell r="B156">
-            <v>1114</v>
+            <v>1106</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
-            <v>土豆种子</v>
+            <v>西兰花种子</v>
           </cell>
           <cell r="B157">
-            <v>1115</v>
+            <v>1107</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158" t="str">
-            <v>大蒜种子</v>
+            <v>番茄种子</v>
           </cell>
           <cell r="B158">
-            <v>1116</v>
+            <v>1108</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159" t="str">
-            <v>芦笋种子</v>
+            <v>胡萝卜种子</v>
           </cell>
           <cell r="B159">
-            <v>1117</v>
+            <v>1109</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
-            <v>南瓜种子</v>
+            <v>西瓜种子</v>
           </cell>
           <cell r="B160">
-            <v>1118</v>
+            <v>1110</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
-            <v>玉米种子</v>
+            <v>辣椒种子</v>
           </cell>
           <cell r="B161">
-            <v>1119</v>
+            <v>1111</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
-            <v>大麦种子</v>
+            <v>奇异果种子</v>
           </cell>
           <cell r="B162">
-            <v>1120</v>
+            <v>1112</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
-            <v>啤酒花种子</v>
+            <v>茄子种子</v>
           </cell>
           <cell r="B163">
-            <v>1121</v>
+            <v>1113</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164" t="str">
-            <v>葡萄种子</v>
+            <v>豌豆种子</v>
           </cell>
           <cell r="B164">
-            <v>1122</v>
+            <v>1114</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165" t="str">
-            <v>菠萝种子</v>
+            <v>土豆种子</v>
           </cell>
           <cell r="B165">
-            <v>1123</v>
+            <v>1115</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
-            <v>咖啡种子</v>
+            <v>大蒜种子</v>
           </cell>
           <cell r="B166">
-            <v>1124</v>
+            <v>1116</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
-            <v>草莓种子</v>
+            <v>芦笋种子</v>
           </cell>
           <cell r="B167">
-            <v>1125</v>
+            <v>1117</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
-            <v>蓝莓种子</v>
+            <v>南瓜种子</v>
           </cell>
           <cell r="B168">
-            <v>1126</v>
+            <v>1118</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
-            <v>红薯种子</v>
+            <v>玉米种子</v>
           </cell>
           <cell r="B169">
-            <v>1127</v>
+            <v>1119</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
-            <v>甜菜种子</v>
+            <v>大麦种子</v>
           </cell>
           <cell r="B170">
-            <v>1128</v>
+            <v>1120</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
-            <v>长剑</v>
+            <v>啤酒花种子</v>
           </cell>
           <cell r="B171">
-            <v>1600</v>
+            <v>1121</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172" t="str">
-            <v>诅咒之剑</v>
+            <v>葡萄种子</v>
           </cell>
           <cell r="B172">
-            <v>1601</v>
+            <v>1122</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173" t="str">
-            <v>烈焰之刃</v>
+            <v>菠萝种子</v>
           </cell>
           <cell r="B173">
-            <v>1602</v>
+            <v>1123</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174" t="str">
-            <v>大地之剑</v>
+            <v>咖啡种子</v>
           </cell>
           <cell r="B174">
-            <v>1603</v>
+            <v>1124</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175" t="str">
-            <v>冰之刃</v>
+            <v>草莓种子</v>
           </cell>
           <cell r="B175">
-            <v>1604</v>
+            <v>1125</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
-            <v>铁枪</v>
+            <v>蓝莓种子</v>
           </cell>
           <cell r="B176">
-            <v>1605</v>
+            <v>1126</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
-            <v>骑士长枪</v>
+            <v>红薯种子</v>
           </cell>
           <cell r="B177">
-            <v>1606</v>
+            <v>1127</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178" t="str">
-            <v>血腥之枪</v>
+            <v>甜菜种子</v>
           </cell>
           <cell r="B178">
-            <v>1607</v>
+            <v>1128</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179" t="str">
-            <v>三叉戟</v>
+            <v>长剑</v>
           </cell>
           <cell r="B179">
-            <v>1608</v>
+            <v>1600</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180" t="str">
-            <v>战斧</v>
+            <v>诅咒之剑</v>
           </cell>
           <cell r="B180">
-            <v>1609</v>
+            <v>1601</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181" t="str">
-            <v>毒蜥之牙</v>
+            <v>烈焰之刃</v>
           </cell>
           <cell r="B181">
-            <v>1610</v>
+            <v>1602</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
-            <v>恶魔之斧</v>
+            <v>大地之剑</v>
           </cell>
           <cell r="B182">
-            <v>1611</v>
+            <v>1603</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183" t="str">
-            <v>蛇皮鞭</v>
+            <v>冰之刃</v>
           </cell>
           <cell r="B183">
-            <v>1612</v>
+            <v>1604</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
-            <v>藤鞭</v>
+            <v>铁枪</v>
           </cell>
           <cell r="B184">
-            <v>1613</v>
+            <v>1605</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
-            <v>女王鞭</v>
+            <v>骑士长枪</v>
           </cell>
           <cell r="B185">
-            <v>1614</v>
+            <v>1606</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
-            <v>蛇牙鞭</v>
+            <v>血腥之枪</v>
           </cell>
           <cell r="B186">
-            <v>1615</v>
+            <v>1607</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
-            <v>暴雪斧</v>
+            <v>三叉戟</v>
           </cell>
           <cell r="B187">
-            <v>1616</v>
+            <v>1608</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
-            <v>秘银长剑</v>
+            <v>战斧</v>
           </cell>
           <cell r="B188">
-            <v>1617</v>
+            <v>1609</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189" t="str">
-            <v>幻影长枪</v>
+            <v>毒蜥之牙</v>
           </cell>
           <cell r="B189">
-            <v>1618</v>
+            <v>1610</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190" t="str">
-            <v>雷神之鞭</v>
+            <v>恶魔之斧</v>
           </cell>
           <cell r="B190">
-            <v>1619</v>
+            <v>1611</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
-            <v>死亡之鞭</v>
+            <v>蛇皮鞭</v>
           </cell>
           <cell r="B191">
-            <v>1620</v>
+            <v>1612</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
-            <v>布衣</v>
+            <v>藤鞭</v>
           </cell>
           <cell r="B192">
-            <v>1650</v>
+            <v>1613</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
-            <v>皮铠</v>
+            <v>女王鞭</v>
           </cell>
           <cell r="B193">
-            <v>1651</v>
+            <v>1614</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
-            <v>锁子甲</v>
+            <v>蛇牙鞭</v>
           </cell>
           <cell r="B194">
-            <v>1652</v>
+            <v>1615</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
-            <v>毛皮斗篷</v>
+            <v>暴雪斧</v>
           </cell>
           <cell r="B195">
-            <v>1653</v>
+            <v>1616</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196" t="str">
-            <v>铁铠甲</v>
+            <v>秘银长剑</v>
           </cell>
           <cell r="B196">
-            <v>1654</v>
+            <v>1617</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
-            <v>红莲之铠</v>
+            <v>幻影长枪</v>
           </cell>
           <cell r="B197">
-            <v>1655</v>
+            <v>1618</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
-            <v>铁龟铠</v>
+            <v>雷神之鞭</v>
           </cell>
           <cell r="B198">
-            <v>1656</v>
+            <v>1619</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
-            <v>华丽背心</v>
+            <v>死亡之鞭</v>
           </cell>
           <cell r="B199">
-            <v>1657</v>
+            <v>1620</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
-            <v>鳞铠</v>
+            <v>布衣</v>
           </cell>
           <cell r="B200">
-            <v>1658</v>
+            <v>1650</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
-            <v>暗之袍</v>
+            <v>皮铠</v>
           </cell>
           <cell r="B201">
-            <v>1659</v>
+            <v>1651</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
-            <v>疾风背心</v>
+            <v>锁子甲</v>
           </cell>
           <cell r="B202">
-            <v>1660</v>
+            <v>1652</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
-            <v>魔法铠甲</v>
+            <v>毛皮斗篷</v>
           </cell>
           <cell r="B203">
-            <v>1661</v>
+            <v>1653</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
-            <v>钢刃锁甲</v>
+            <v>铁铠甲</v>
           </cell>
           <cell r="B204">
-            <v>1662</v>
+            <v>1654</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
-            <v>丝织长袍</v>
+            <v>红莲之铠</v>
           </cell>
           <cell r="B205">
-            <v>1663</v>
+            <v>1655</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
-            <v>水之羽衣</v>
+            <v>铁龟铠</v>
           </cell>
           <cell r="B206">
-            <v>1664</v>
+            <v>1656</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
-            <v>贵族长裙</v>
+            <v>华丽背心</v>
           </cell>
           <cell r="B207">
-            <v>1665</v>
+            <v>1657</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
-            <v>幸运之衣</v>
+            <v>鳞铠</v>
           </cell>
           <cell r="B208">
-            <v>1666</v>
+            <v>1658</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
-            <v>布鞋</v>
+            <v>暗之袍</v>
           </cell>
           <cell r="B209">
-            <v>1700</v>
+            <v>1659</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
-            <v>皮鞋</v>
+            <v>疾风背心</v>
           </cell>
           <cell r="B210">
-            <v>1701</v>
+            <v>1660</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
-            <v>士兵长靴</v>
+            <v>魔法铠甲</v>
           </cell>
           <cell r="B211">
-            <v>1702</v>
+            <v>1661</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
-            <v>登山者之靴</v>
+            <v>钢刃锁甲</v>
           </cell>
           <cell r="B212">
-            <v>1703</v>
+            <v>1662</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213" t="str">
-            <v>运动鞋</v>
+            <v>丝织长袍</v>
           </cell>
           <cell r="B213">
-            <v>1704</v>
+            <v>1663</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214" t="str">
-            <v>贵族长靴</v>
+            <v>水之羽衣</v>
           </cell>
           <cell r="B214">
-            <v>1705</v>
+            <v>1664</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215" t="str">
-            <v>武道鞋</v>
+            <v>贵族长裙</v>
           </cell>
           <cell r="B215">
-            <v>1706</v>
+            <v>1665</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216" t="str">
-            <v>骑士护胫</v>
+            <v>幸运之衣</v>
           </cell>
           <cell r="B216">
-            <v>1707</v>
+            <v>1666</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
-            <v>贤者之履</v>
+            <v>布鞋</v>
           </cell>
           <cell r="B217">
-            <v>1708</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218" t="str">
-            <v>风神之履</v>
+            <v>皮鞋</v>
           </cell>
           <cell r="B218">
-            <v>1709</v>
+            <v>1701</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219" t="str">
-            <v>踏浪长靴</v>
+            <v>士兵长靴</v>
           </cell>
           <cell r="B219">
-            <v>1710</v>
+            <v>1702</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220" t="str">
-            <v>锄头</v>
+            <v>登山者之靴</v>
           </cell>
           <cell r="B220">
-            <v>2000</v>
+            <v>1703</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
-            <v>洒水壶</v>
+            <v>运动鞋</v>
           </cell>
           <cell r="B221">
-            <v>2001</v>
+            <v>1704</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222" t="str">
-            <v>斧头</v>
+            <v>贵族长靴</v>
           </cell>
           <cell r="B222">
-            <v>2002</v>
+            <v>1705</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223" t="str">
-            <v>镰刀</v>
+            <v>武道鞋</v>
           </cell>
           <cell r="B223">
-            <v>2003</v>
+            <v>1706</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224" t="str">
-            <v>鱼竿</v>
+            <v>骑士护胫</v>
           </cell>
           <cell r="B224">
-            <v>2004</v>
+            <v>1707</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225" t="str">
-            <v>纺织机</v>
+            <v>贤者之履</v>
           </cell>
           <cell r="B225">
-            <v>2100</v>
+            <v>1708</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
-            <v>锻造炉</v>
+            <v>风神之履</v>
           </cell>
           <cell r="B226">
-            <v>2101</v>
+            <v>1709</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
-            <v>烘烤炉</v>
+            <v>踏浪长靴</v>
           </cell>
           <cell r="B227">
-            <v>2102</v>
+            <v>1710</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
-            <v>炖煮锅</v>
+            <v>草帽</v>
           </cell>
           <cell r="B228">
-            <v>2103</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
-            <v>冷餐台</v>
+            <v>暮光草帽</v>
           </cell>
           <cell r="B229">
-            <v>2104</v>
+            <v>1801</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230" t="str">
-            <v>酿造桶</v>
+            <v>法师帽</v>
           </cell>
           <cell r="B230">
-            <v>2105</v>
+            <v>1802</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231" t="str">
-            <v>绘写台</v>
+            <v>士兵头盔</v>
           </cell>
           <cell r="B231">
-            <v>2106</v>
+            <v>1803</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232" t="str">
-            <v>冰箱</v>
+            <v>尖角头盔</v>
           </cell>
           <cell r="B232">
-            <v>2107</v>
+            <v>1804</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233" t="str">
-            <v>储物箱(木)</v>
+            <v>幸运头巾</v>
           </cell>
           <cell r="B233">
-            <v>2108</v>
+            <v>1805</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234" t="str">
-            <v>储物箱(银)</v>
+            <v>绅士礼帽</v>
           </cell>
           <cell r="B234">
-            <v>2109</v>
+            <v>1806</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
-            <v>储物箱(金)</v>
+            <v>贵族头巾</v>
           </cell>
           <cell r="B235">
-            <v>2110</v>
+            <v>1807</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
-            <v>普通柜台</v>
+            <v>战争头盔</v>
           </cell>
           <cell r="B236">
-            <v>2111</v>
+            <v>1808</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
-            <v>武器柜台</v>
+            <v>锄头</v>
           </cell>
           <cell r="B237">
-            <v>2112</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
-            <v>服饰架</v>
+            <v>洒水壶</v>
           </cell>
           <cell r="B238">
-            <v>2113</v>
+            <v>2001</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239" t="str">
-            <v>沙发</v>
+            <v>斧头</v>
           </cell>
           <cell r="B239">
-            <v>2200</v>
+            <v>2002</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240" t="str">
-            <v>搅拌机</v>
+            <v>镰刀</v>
           </cell>
           <cell r="B240">
-            <v>2114</v>
+            <v>2003</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241" t="str">
-            <v>双人床</v>
+            <v>鱼竿</v>
           </cell>
           <cell r="B241">
-            <v>2201</v>
+            <v>2004</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
-            <v>鲫鱼</v>
+            <v>缝纫机</v>
           </cell>
           <cell r="B242">
-            <v>4000</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
-            <v>小龙虾</v>
+            <v>锻造炉</v>
           </cell>
           <cell r="B243">
-            <v>4003</v>
+            <v>2101</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244" t="str">
-            <v>鲤鱼</v>
+            <v>烘烤炉</v>
           </cell>
           <cell r="B244">
-            <v>4004</v>
+            <v>2102</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
-            <v>鲮鱼</v>
+            <v>蒸煮锅</v>
           </cell>
           <cell r="B245">
-            <v>4006</v>
+            <v>2103</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246" t="str">
-            <v>手套蟹</v>
+            <v>冷餐台</v>
           </cell>
           <cell r="B246">
-            <v>4007</v>
+            <v>2104</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247" t="str">
-            <v>鲶鱼</v>
+            <v>酿造桶</v>
           </cell>
           <cell r="B247">
-            <v>4008</v>
+            <v>2105</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248" t="str">
-            <v>丁鱼</v>
+            <v>绘写台</v>
           </cell>
           <cell r="B248">
-            <v>4009</v>
+            <v>2106</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249" t="str">
-            <v>锦鲤</v>
+            <v>冰箱</v>
           </cell>
           <cell r="B249">
-            <v>4010</v>
+            <v>2107</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
-            <v>线鱼</v>
+            <v>储物箱(木)</v>
           </cell>
           <cell r="B250">
-            <v>4011</v>
+            <v>2108</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251" t="str">
-            <v>梭鲈</v>
+            <v>储物箱(银)</v>
           </cell>
           <cell r="B251">
-            <v>4012</v>
+            <v>2109</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
-            <v>兰寿金鱼</v>
+            <v>储物箱(金)</v>
           </cell>
           <cell r="B252">
-            <v>4013</v>
+            <v>2110</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
-            <v>樱桃鲑鱼</v>
+            <v>普通柜台</v>
           </cell>
           <cell r="B253">
-            <v>4014</v>
+            <v>2111</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254" t="str">
-            <v>虹鳟鱼</v>
+            <v>服饰架</v>
           </cell>
           <cell r="B254">
-            <v>4015</v>
+            <v>2113</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255" t="str">
-            <v>鲷鱼</v>
+            <v>沙发</v>
           </cell>
           <cell r="B255">
-            <v>4016</v>
+            <v>2200</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256" t="str">
-            <v>金鳟鱼</v>
+            <v>搅拌器</v>
           </cell>
           <cell r="B256">
-            <v>4017</v>
+            <v>2114</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
-            <v>霓虹脂鲤</v>
+            <v>双人床</v>
           </cell>
           <cell r="B257">
-            <v>4018</v>
+            <v>2201</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258" t="str">
-            <v>桃花鱼</v>
+            <v>鲫鱼</v>
           </cell>
           <cell r="B258">
-            <v>4020</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259" t="str">
-            <v>鲑鱼</v>
+            <v>小龙虾</v>
           </cell>
           <cell r="B259">
-            <v>4021</v>
+            <v>4003</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260" t="str">
-            <v>孔雀鱼</v>
+            <v>鲤鱼</v>
           </cell>
           <cell r="B260">
-            <v>4022</v>
+            <v>4004</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
-            <v>银龙鱼</v>
+            <v>鲮鱼</v>
           </cell>
           <cell r="B261">
-            <v>4023</v>
+            <v>4006</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
-            <v>洞穴天使鱼</v>
+            <v>手套蟹</v>
           </cell>
           <cell r="B262">
-            <v>4024</v>
+            <v>4007</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
-            <v>沙丁鱼</v>
+            <v>鲶鱼</v>
           </cell>
           <cell r="B263">
-            <v>4100</v>
+            <v>4008</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264" t="str">
-            <v>竹荚鱼</v>
+            <v>丁鱼</v>
           </cell>
           <cell r="B264">
-            <v>4101</v>
+            <v>4009</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265" t="str">
-            <v>海鳗</v>
+            <v>锦鲤</v>
           </cell>
           <cell r="B265">
-            <v>4103</v>
+            <v>4010</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266" t="str">
-            <v>章鱼</v>
+            <v>线鱼</v>
           </cell>
           <cell r="B266">
-            <v>4105</v>
+            <v>4011</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
-            <v>比目鱼</v>
+            <v>梭鲈</v>
           </cell>
           <cell r="B267">
-            <v>4106</v>
+            <v>4012</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268" t="str">
-            <v>河豚</v>
+            <v>兰寿金鱼</v>
           </cell>
           <cell r="B268">
-            <v>4109</v>
+            <v>4013</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
-            <v>水母</v>
+            <v>樱桃鲑鱼</v>
           </cell>
           <cell r="B269">
-            <v>4110</v>
+            <v>4014</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270" t="str">
-            <v>条石鲷</v>
+            <v>虹鳟鱼</v>
           </cell>
           <cell r="B270">
-            <v>4111</v>
+            <v>4015</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
-            <v>红鲷鱼</v>
+            <v>鲷鱼</v>
           </cell>
           <cell r="B271">
-            <v>4112</v>
+            <v>4016</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
-            <v>蓝蟹</v>
+            <v>金鳟鱼</v>
           </cell>
           <cell r="B272">
-            <v>4113</v>
+            <v>4017</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
-            <v>鲯鳅鱼</v>
+            <v>霓虹脂鲤</v>
           </cell>
           <cell r="B273">
-            <v>4114</v>
+            <v>4018</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
-            <v>龙虾</v>
+            <v>桃花鱼</v>
           </cell>
           <cell r="B274">
-            <v>4115</v>
+            <v>4020</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275" t="str">
-            <v>金枪鱼</v>
+            <v>鲑鱼</v>
           </cell>
           <cell r="B275">
-            <v>4116</v>
+            <v>4021</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276" t="str">
-            <v>斑马狮子鱼</v>
+            <v>孔雀鱼</v>
           </cell>
           <cell r="B276">
-            <v>4117</v>
+            <v>4022</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
-            <v>米饭</v>
+            <v>银龙鱼</v>
           </cell>
           <cell r="B277">
-            <v>3000</v>
+            <v>4023</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278" t="str">
-            <v>发酵粉</v>
+            <v>洞穴天使鱼</v>
           </cell>
           <cell r="B278">
-            <v>3001</v>
+            <v>4024</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
-            <v>盐</v>
+            <v>沙丁鱼</v>
           </cell>
           <cell r="B279">
-            <v>3002</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
-            <v>酸味香料</v>
+            <v>竹荚鱼</v>
           </cell>
           <cell r="B280">
-            <v>3003</v>
+            <v>4101</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
-            <v>蜂蜜</v>
+            <v>海鳗</v>
           </cell>
           <cell r="B281">
-            <v>3005</v>
+            <v>4103</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
-            <v>牛奶</v>
+            <v>章鱼</v>
           </cell>
           <cell r="B282">
-            <v>3006</v>
+            <v>4105</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
-            <v>鸡蛋</v>
+            <v>比目鱼</v>
           </cell>
           <cell r="B283">
-            <v>3007</v>
+            <v>4106</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284" t="str">
-            <v>猪肉</v>
+            <v>河豚</v>
           </cell>
           <cell r="B284">
-            <v>3008</v>
+            <v>4109</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
-            <v>面粉</v>
+            <v>水母</v>
           </cell>
           <cell r="B285">
-            <v>3009</v>
+            <v>4110</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
-            <v>咖啡粉</v>
+            <v>条石鲷</v>
           </cell>
           <cell r="B286">
-            <v>3010</v>
+            <v>4111</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
-            <v>海苔</v>
+            <v>红鲷鱼</v>
           </cell>
           <cell r="B287">
-            <v>3011</v>
+            <v>4112</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
-            <v>黄油</v>
+            <v>蓝蟹</v>
           </cell>
           <cell r="B288">
-            <v>3011</v>
+            <v>4113</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289" t="str">
-            <v>腌芜菁</v>
+            <v>鲯鳅鱼</v>
           </cell>
           <cell r="B289">
-            <v>3100</v>
+            <v>4114</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290" t="str">
-            <v>蔬菜沙拉</v>
+            <v>龙虾</v>
           </cell>
           <cell r="B290">
-            <v>3101</v>
+            <v>4115</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291" t="str">
-            <v>三明治</v>
+            <v>金枪鱼</v>
           </cell>
           <cell r="B291">
-            <v>3102</v>
+            <v>4116</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
-            <v>腌萝卜</v>
+            <v>斑马狮子鱼</v>
           </cell>
           <cell r="B292">
-            <v>3103</v>
+            <v>4117</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293" t="str">
-            <v>拉面</v>
+            <v>米饭</v>
           </cell>
           <cell r="B293">
-            <v>3104</v>
+            <v>3000</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
-            <v>蜂蜜蛋糕</v>
+            <v>发酵粉</v>
           </cell>
           <cell r="B294">
-            <v>3105</v>
+            <v>3001</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
-            <v>披萨</v>
+            <v>盐</v>
           </cell>
           <cell r="B295">
-            <v>3106</v>
+            <v>3002</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296" t="str">
-            <v>腌黄瓜</v>
+            <v>酸味香料</v>
           </cell>
           <cell r="B296">
-            <v>3107</v>
+            <v>3003</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297" t="str">
-            <v>烤西兰花</v>
+            <v>蜂蜜</v>
           </cell>
           <cell r="B297">
-            <v>3108</v>
+            <v>3005</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298" t="str">
-            <v>水煮蛋</v>
+            <v>牛奶</v>
           </cell>
           <cell r="B298">
-            <v>3109</v>
+            <v>3006</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299" t="str">
-            <v>烤肉串</v>
+            <v>鸡蛋</v>
           </cell>
           <cell r="B299">
-            <v>3110</v>
+            <v>3007</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300" t="str">
-            <v>饭团</v>
+            <v>猪肉</v>
           </cell>
           <cell r="B300">
-            <v>3111</v>
+            <v>3008</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
-            <v>面包</v>
+            <v>面粉</v>
           </cell>
           <cell r="B301">
-            <v>3112</v>
+            <v>3009</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302" t="str">
-            <v>烤海苔</v>
+            <v>咖啡粉</v>
           </cell>
           <cell r="B302">
-            <v>3113</v>
+            <v>3010</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303" t="str">
-            <v>烤肉饼</v>
+            <v>海苔</v>
           </cell>
           <cell r="B303">
-            <v>3114</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304" t="str">
-            <v>汉堡</v>
+            <v>黄油</v>
           </cell>
           <cell r="B304">
-            <v>3115</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305" t="str">
-            <v>辣蟹堡</v>
+            <v>腌芜菁</v>
           </cell>
           <cell r="B305">
-            <v>3116</v>
+            <v>3100</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306" t="str">
-            <v>土豆泥</v>
+            <v>蔬菜沙拉</v>
           </cell>
           <cell r="B306">
-            <v>3117</v>
+            <v>3101</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
-            <v>海鲜饭</v>
+            <v>三明治</v>
           </cell>
           <cell r="B307">
-            <v>3118</v>
+            <v>3102</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308" t="str">
-            <v>烤玉米</v>
+            <v>腌萝卜</v>
           </cell>
           <cell r="B308">
-            <v>3119</v>
+            <v>3103</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309" t="str">
-            <v>蔬菜汁</v>
+            <v>拉面</v>
           </cell>
           <cell r="B309">
-            <v>3120</v>
+            <v>3104</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
-            <v>西瓜果汁</v>
+            <v>蜂蜜蛋糕</v>
           </cell>
           <cell r="B310">
-            <v>3121</v>
+            <v>3105</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
-            <v>奇异果汁</v>
+            <v>披萨</v>
           </cell>
           <cell r="B311">
-            <v>3122</v>
+            <v>3106</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
-            <v>葡萄汁</v>
+            <v>腌黄瓜</v>
           </cell>
           <cell r="B312">
-            <v>3123</v>
+            <v>3107</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
-            <v>菠萝汁</v>
+            <v>烤西兰花</v>
           </cell>
           <cell r="B313">
-            <v>3124</v>
+            <v>3108</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314" t="str">
-            <v>草莓汁</v>
+            <v>水煮蛋</v>
           </cell>
           <cell r="B314">
-            <v>3125</v>
+            <v>3109</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315" t="str">
-            <v>蓝莓汁</v>
+            <v>烤肉串</v>
           </cell>
           <cell r="B315">
-            <v>3126</v>
+            <v>3110</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316" t="str">
-            <v>玉米汁</v>
+            <v>饭团</v>
           </cell>
           <cell r="B316">
-            <v>3127</v>
+            <v>3111</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
-            <v>烤蜜薯</v>
+            <v>面包</v>
           </cell>
           <cell r="B317">
-            <v>3128</v>
+            <v>3112</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318" t="str">
-            <v>甜菜汁</v>
+            <v>烤海苔</v>
           </cell>
           <cell r="B318">
-            <v>3129</v>
+            <v>3113</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
-            <v>奶酪</v>
+            <v>烤肉饼</v>
           </cell>
           <cell r="B319">
-            <v>3130</v>
+            <v>3114</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320" t="str">
-            <v>烤茄子</v>
+            <v>汉堡</v>
           </cell>
           <cell r="B320">
-            <v>3131</v>
+            <v>3115</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321" t="str">
-            <v>饺子</v>
+            <v>辣蟹堡</v>
           </cell>
           <cell r="B321">
-            <v>3132</v>
+            <v>3116</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322" t="str">
-            <v>炖菜</v>
+            <v>土豆泥</v>
           </cell>
           <cell r="B322">
-            <v>3133</v>
+            <v>3117</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323" t="str">
-            <v>烤芦笋</v>
+            <v>海鲜饭</v>
           </cell>
           <cell r="B323">
-            <v>3134</v>
+            <v>3118</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324" t="str">
-            <v>红菜汤</v>
+            <v>烤玉米</v>
           </cell>
           <cell r="B324">
-            <v>3135</v>
+            <v>3119</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325" t="str">
-            <v>豌豆汤</v>
+            <v>蔬菜汁</v>
           </cell>
           <cell r="B325">
-            <v>3136</v>
+            <v>3120</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
-            <v>草莓牛奶</v>
+            <v>西瓜果汁</v>
           </cell>
           <cell r="B326">
-            <v>3137</v>
+            <v>3121</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327" t="str">
-            <v>莓莓果汁</v>
+            <v>奇异果汁</v>
           </cell>
           <cell r="B327">
-            <v>3138</v>
+            <v>3122</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328" t="str">
-            <v>鲑鱼饭团</v>
+            <v>葡萄汁</v>
           </cell>
           <cell r="B328">
-            <v>3139</v>
+            <v>3123</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329" t="str">
-            <v>拿铁</v>
+            <v>菠萝汁</v>
           </cell>
           <cell r="B329">
-            <v>3140</v>
+            <v>3124</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330" t="str">
-            <v>黑咖啡</v>
+            <v>草莓汁</v>
           </cell>
           <cell r="B330">
-            <v>3141</v>
+            <v>3125</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331" t="str">
-            <v>葡萄酒</v>
+            <v>蓝莓汁</v>
           </cell>
           <cell r="B331">
-            <v>3142</v>
+            <v>3126</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
-            <v>伏特加</v>
+            <v>玉米汁</v>
           </cell>
           <cell r="B332">
-            <v>3143</v>
+            <v>3127</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333" t="str">
-            <v>啤酒</v>
+            <v>烤蜜薯</v>
           </cell>
           <cell r="B333">
-            <v>3144</v>
+            <v>3128</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334" t="str">
-            <v>朗姆</v>
+            <v>甜菜汁</v>
           </cell>
           <cell r="B334">
-            <v>3145</v>
+            <v>3129</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
-            <v>野蜂拉格</v>
+            <v>奶酪</v>
           </cell>
           <cell r="B335">
-            <v>3146</v>
+            <v>3130</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
-            <v>双莓白兰地</v>
+            <v>烤茄子</v>
           </cell>
           <cell r="B336">
-            <v>3147</v>
+            <v>3131</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
-            <v>绯红之吻</v>
+            <v>饺子</v>
           </cell>
           <cell r="B337">
-            <v>3148</v>
+            <v>3132</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
-            <v>阳光男孩</v>
+            <v>炖菜</v>
           </cell>
           <cell r="B338">
-            <v>3149</v>
+            <v>3133</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339" t="str">
-            <v>盐烤鲮鱼</v>
+            <v>烤芦笋</v>
           </cell>
           <cell r="B339">
-            <v>3150</v>
+            <v>3134</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340" t="str">
-            <v>盐烤丁鱼</v>
+            <v>红菜汤</v>
           </cell>
           <cell r="B340">
-            <v>3151</v>
+            <v>3135</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341" t="str">
-            <v>盐烤虹鳟鱼</v>
+            <v>豌豆汤</v>
           </cell>
           <cell r="B341">
-            <v>3152</v>
+            <v>3136</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342" t="str">
-            <v>烤鲷鱼</v>
+            <v>草莓牛奶</v>
           </cell>
           <cell r="B342">
-            <v>3153</v>
+            <v>3137</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343" t="str">
-            <v>盐烤金鳟鱼</v>
+            <v>莓莓果汁</v>
           </cell>
           <cell r="B343">
-            <v>3154</v>
+            <v>3138</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344" t="str">
-            <v>盐烤鲑鱼</v>
+            <v>鲑鱼饭团</v>
           </cell>
           <cell r="B344">
-            <v>3155</v>
+            <v>3139</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345" t="str">
-            <v>烤沙丁鱼串</v>
+            <v>拿铁</v>
           </cell>
           <cell r="B345">
-            <v>3156</v>
+            <v>3140</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346" t="str">
-            <v>烤竹荚鱼</v>
+            <v>黑咖啡</v>
           </cell>
           <cell r="B346">
-            <v>3157</v>
+            <v>3141</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347" t="str">
-            <v>烤海鳗</v>
+            <v>葡萄酒</v>
           </cell>
           <cell r="B347">
-            <v>3158</v>
+            <v>3142</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348" t="str">
-            <v>烤比目鱼</v>
+            <v>伏特加</v>
           </cell>
           <cell r="B348">
-            <v>3159</v>
+            <v>3143</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349" t="str">
-            <v>烤河豚鱼</v>
+            <v>啤酒</v>
           </cell>
           <cell r="B349">
-            <v>3160</v>
+            <v>3144</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350" t="str">
-            <v>烤条石鲷</v>
+            <v>朗姆</v>
           </cell>
           <cell r="B350">
-            <v>3161</v>
+            <v>3145</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351" t="str">
-            <v>烤红鲷鱼</v>
+            <v>野蜂拉格</v>
           </cell>
           <cell r="B351">
-            <v>3162</v>
+            <v>3146</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352" t="str">
-            <v>烤蓝蟹</v>
+            <v>双莓白兰地</v>
           </cell>
           <cell r="B352">
-            <v>3163</v>
+            <v>3147</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353" t="str">
-            <v>烤龙虾</v>
+            <v>绯红之吻</v>
           </cell>
           <cell r="B353">
-            <v>3164</v>
+            <v>3148</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354" t="str">
-            <v>烤金枪鱼</v>
+            <v>阳光男孩</v>
           </cell>
           <cell r="B354">
-            <v>3165</v>
+            <v>3149</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355" t="str">
-            <v>煮蟹肉</v>
+            <v>盐烤鲮鱼</v>
           </cell>
           <cell r="B355">
-            <v>3166</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356" t="str">
-            <v>海鲜浓汤</v>
+            <v>盐烤丁鱼</v>
           </cell>
           <cell r="B356">
-            <v>3167</v>
+            <v>3151</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357" t="str">
-            <v>鳗鱼饭</v>
+            <v>盐烤虹鳟鱼</v>
           </cell>
           <cell r="B357">
-            <v>3168</v>
+            <v>3152</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358" t="str">
-            <v>鲫鱼蔬菜汤</v>
+            <v>烤鲷鱼</v>
           </cell>
           <cell r="B358">
-            <v>3169</v>
+            <v>3153</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359" t="str">
-            <v>鲮鱼丸</v>
+            <v>盐烤金鳟鱼</v>
           </cell>
           <cell r="B359">
-            <v>3170</v>
+            <v>3154</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360" t="str">
-            <v>鲑鱼刺身</v>
+            <v>盐烤鲑鱼</v>
           </cell>
           <cell r="B360">
-            <v>3171</v>
+            <v>3155</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361" t="str">
-            <v>章鱼小丸子</v>
+            <v>烤沙丁鱼串</v>
           </cell>
           <cell r="B361">
-            <v>3172</v>
+            <v>3156</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362" t="str">
-            <v>炖煮条石鲷</v>
+            <v>烤竹荚鱼</v>
           </cell>
           <cell r="B362">
-            <v>3173</v>
+            <v>3157</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363" t="str">
-            <v>红鲷刺身</v>
+            <v>烤海鳗</v>
           </cell>
           <cell r="B363">
-            <v>3174</v>
+            <v>3158</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364" t="str">
-            <v>河豚刺身</v>
+            <v>烤比目鱼</v>
           </cell>
           <cell r="B364">
-            <v>3175</v>
+            <v>3159</v>
           </cell>
         </row>
         <row r="365">
           <cell r="A365" t="str">
-            <v>螃蟹煲</v>
+            <v>烤河豚鱼</v>
           </cell>
           <cell r="B365">
-            <v>3176</v>
+            <v>3160</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366" t="str">
-            <v>金枪鱼刺身</v>
+            <v>烤条石鲷</v>
           </cell>
           <cell r="B366">
-            <v>3177</v>
+            <v>3161</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367" t="str">
-            <v>龙虾鱼子酱</v>
+            <v>烤红鲷鱼</v>
           </cell>
           <cell r="B367">
-            <v>3178</v>
+            <v>3162</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368" t="str">
-            <v>回春卷轴</v>
+            <v>烤蓝蟹</v>
           </cell>
           <cell r="B368">
-            <v>4000</v>
+            <v>3163</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369" t="str">
-            <v>振奋卷轴</v>
+            <v>烤龙虾</v>
           </cell>
           <cell r="B369">
-            <v>4001</v>
+            <v>3164</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370" t="str">
-            <v>昏睡卷轴</v>
+            <v>烤金枪鱼</v>
           </cell>
           <cell r="B370">
-            <v>4002</v>
+            <v>3165</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371" t="str">
-            <v>感电卷轴</v>
+            <v>煮蟹肉</v>
           </cell>
           <cell r="B371">
-            <v>4003</v>
+            <v>3166</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372" t="str">
-            <v>冰氛卷轴</v>
+            <v>海鲜浓汤</v>
           </cell>
           <cell r="B372">
-            <v>4004</v>
+            <v>3167</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373" t="str">
-            <v>火氛卷轴</v>
+            <v>鳗鱼饭</v>
           </cell>
           <cell r="B373">
-            <v>4005</v>
+            <v>3168</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374" t="str">
-            <v>沉默卷轴</v>
+            <v>鲫鱼蔬菜汤</v>
           </cell>
           <cell r="B374">
-            <v>4006</v>
+            <v>3169</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375" t="str">
-            <v>减速卷轴</v>
+            <v>鲮鱼丸</v>
           </cell>
           <cell r="B375">
-            <v>4007</v>
+            <v>3170</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376" t="str">
-            <v>闪避卷轴</v>
+            <v>鲑鱼刺身</v>
           </cell>
           <cell r="B376">
-            <v>4008</v>
+            <v>3171</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377" t="str">
-            <v>力量卷轴</v>
+            <v>章鱼小丸子</v>
           </cell>
           <cell r="B377">
-            <v>4009</v>
+            <v>3172</v>
           </cell>
         </row>
         <row r="378">
           <cell r="A378" t="str">
+            <v>炖煮条石鲷</v>
+          </cell>
+          <cell r="B378">
+            <v>3173</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="A379" t="str">
+            <v>红鲷刺身</v>
+          </cell>
+          <cell r="B379">
+            <v>3174</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="A380" t="str">
+            <v>河豚刺身</v>
+          </cell>
+          <cell r="B380">
+            <v>3175</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="A381" t="str">
+            <v>螃蟹煲</v>
+          </cell>
+          <cell r="B381">
+            <v>3176</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="A382" t="str">
+            <v>金枪鱼刺身</v>
+          </cell>
+          <cell r="B382">
+            <v>3177</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="A383" t="str">
+            <v>龙虾鱼子酱</v>
+          </cell>
+          <cell r="B383">
+            <v>3178</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="A384" t="str">
+            <v>回春卷轴</v>
+          </cell>
+          <cell r="B384">
+            <v>4000</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="A385" t="str">
+            <v>振奋卷轴</v>
+          </cell>
+          <cell r="B385">
+            <v>4001</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="A386" t="str">
+            <v>昏睡卷轴</v>
+          </cell>
+          <cell r="B386">
+            <v>4002</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="A387" t="str">
+            <v>感电卷轴</v>
+          </cell>
+          <cell r="B387">
+            <v>4003</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="A388" t="str">
+            <v>冰氛卷轴</v>
+          </cell>
+          <cell r="B388">
+            <v>4004</v>
+          </cell>
+        </row>
+        <row r="389">
+          <cell r="A389" t="str">
+            <v>火氛卷轴</v>
+          </cell>
+          <cell r="B389">
+            <v>4005</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="A390" t="str">
+            <v>沉默卷轴</v>
+          </cell>
+          <cell r="B390">
+            <v>4006</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="A391" t="str">
+            <v>减速卷轴</v>
+          </cell>
+          <cell r="B391">
+            <v>4007</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="A392" t="str">
+            <v>闪避卷轴</v>
+          </cell>
+          <cell r="B392">
+            <v>4008</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="A393" t="str">
+            <v>力量卷轴</v>
+          </cell>
+          <cell r="B393">
+            <v>4009</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="A394" t="str">
             <v>魅惑卷轴</v>
           </cell>
-          <cell r="B378">
+          <cell r="B394">
             <v>4010</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4897,7 +5027,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -7785,19 +7915,19 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="N2" s="1">
-        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1020</v>
       </c>
       <c r="O2" s="7" t="str">
-        <f>IF(I2&lt;&gt;"",VLOOKUP(I2,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(I2&lt;&gt;"",VLOOKUP(I2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P2" s="7" t="str">
-        <f>IF(J2&lt;&gt;"",VLOOKUP(J2,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J2&lt;&gt;"",VLOOKUP(J2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q2" s="7" t="str">
-        <f>IF(K2&lt;&gt;"",VLOOKUP(K2,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K2&lt;&gt;"",VLOOKUP(K2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S2" s="1" t="str">
@@ -7822,19 +7952,19 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="N3" s="7">
-        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1024</v>
       </c>
       <c r="O3" s="7" t="str">
-        <f>IF(I3&lt;&gt;"",VLOOKUP(I3,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(I3&lt;&gt;"",VLOOKUP(I3,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P3" s="7" t="str">
-        <f>IF(J3&lt;&gt;"",VLOOKUP(J3,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J3&lt;&gt;"",VLOOKUP(J3,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q3" s="7" t="str">
-        <f>IF(K3&lt;&gt;"",VLOOKUP(K3,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K3&lt;&gt;"",VLOOKUP(K3,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S3" s="7" t="str">
@@ -7853,19 +7983,19 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="N4" s="7" t="str">
-        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="O4" s="7" t="str">
-        <f>IF(I4&lt;&gt;"",VLOOKUP(I4,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(I4&lt;&gt;"",VLOOKUP(I4,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P4" s="7" t="str">
-        <f>IF(J4&lt;&gt;"",VLOOKUP(J4,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J4&lt;&gt;"",VLOOKUP(J4,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q4" s="7" t="str">
-        <f>IF(K4&lt;&gt;"",VLOOKUP(K4,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K4&lt;&gt;"",VLOOKUP(K4,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S4" s="7" t="str">
@@ -7898,19 +8028,19 @@
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7">
-        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O5" s="7">
-        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P5" s="7" t="str">
-        <f>IF(J5&lt;&gt;"",VLOOKUP(J5,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J5&lt;&gt;"",VLOOKUP(J5,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q5" s="7" t="str">
-        <f>IF(K5&lt;&gt;"",VLOOKUP(K5,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K5&lt;&gt;"",VLOOKUP(K5,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S5" s="7" t="str">
@@ -7949,19 +8079,19 @@
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7">
-        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="O6" s="7">
-        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P6" s="7">
-        <f>IF(J6&lt;&gt;"",VLOOKUP(J6,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J6&lt;&gt;"",VLOOKUP(J6,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q6" s="7">
-        <f>IF(K6&lt;&gt;"",VLOOKUP(K6,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K6&lt;&gt;"",VLOOKUP(K6,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="S6" s="7" t="str">
@@ -8000,19 +8130,19 @@
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7">
-        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O7" s="7">
-        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="P7" s="7">
-        <f>IF(J7&lt;&gt;"",VLOOKUP(J7,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J7&lt;&gt;"",VLOOKUP(J7,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="Q7" s="7">
-        <f>IF(K7&lt;&gt;"",VLOOKUP(K7,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K7&lt;&gt;"",VLOOKUP(K7,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="S7" s="7" t="str">
@@ -8045,19 +8175,19 @@
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7">
-        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="O8" s="7">
-        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P8" s="7" t="str">
-        <f>IF(J8&lt;&gt;"",VLOOKUP(J8,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J8&lt;&gt;"",VLOOKUP(J8,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q8" s="7" t="str">
-        <f>IF(K8&lt;&gt;"",VLOOKUP(K8,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K8&lt;&gt;"",VLOOKUP(K8,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S8" s="7" t="str">
@@ -8099,19 +8229,19 @@
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7">
-        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O9" s="7">
-        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P9" s="7">
-        <f>IF(J9&lt;&gt;"",VLOOKUP(J9,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J9&lt;&gt;"",VLOOKUP(J9,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="Q9" s="7">
-        <f>IF(K9&lt;&gt;"",VLOOKUP(K9,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K9&lt;&gt;"",VLOOKUP(K9,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3109</v>
       </c>
       <c r="S9" s="7" t="str">
@@ -8148,19 +8278,19 @@
       <c r="L10" s="8"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7">
-        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O10" s="7">
-        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P10" s="7">
-        <f>IF(J10&lt;&gt;"",VLOOKUP(J10,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J10&lt;&gt;"",VLOOKUP(J10,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="Q10" s="7" t="str">
-        <f>IF(K10&lt;&gt;"",VLOOKUP(K10,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K10&lt;&gt;"",VLOOKUP(K10,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S10" s="7" t="str">
@@ -8199,19 +8329,19 @@
       <c r="L11" s="8"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7">
-        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O11" s="7">
-        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="P11" s="7">
-        <f>IF(J11&lt;&gt;"",VLOOKUP(J11,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J11&lt;&gt;"",VLOOKUP(J11,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1013</v>
       </c>
       <c r="Q11" s="7">
-        <f>IF(K11&lt;&gt;"",VLOOKUP(K11,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K11&lt;&gt;"",VLOOKUP(K11,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="S11" s="7" t="str">
@@ -8243,19 +8373,19 @@
         <v>2</v>
       </c>
       <c r="N12" s="7">
-        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="O12" s="7">
-        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P12" s="7" t="str">
-        <f>IF(J12&lt;&gt;"",VLOOKUP(J12,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J12&lt;&gt;"",VLOOKUP(J12,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q12" s="7" t="str">
-        <f>IF(K12&lt;&gt;"",VLOOKUP(K12,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K12&lt;&gt;"",VLOOKUP(K12,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S12" s="7" t="str">
@@ -8287,19 +8417,19 @@
         <v>1</v>
       </c>
       <c r="N13" s="7">
-        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1007</v>
       </c>
       <c r="O13" s="7" t="str">
-        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P13" s="7" t="str">
-        <f>IF(J13&lt;&gt;"",VLOOKUP(J13,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J13&lt;&gt;"",VLOOKUP(J13,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q13" s="7" t="str">
-        <f>IF(K13&lt;&gt;"",VLOOKUP(K13,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K13&lt;&gt;"",VLOOKUP(K13,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S13" s="7" t="str">
@@ -8331,19 +8461,19 @@
         <v>1</v>
       </c>
       <c r="N14" s="7">
-        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="O14" s="7" t="str">
-        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P14" s="7" t="str">
-        <f>IF(J14&lt;&gt;"",VLOOKUP(J14,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J14&lt;&gt;"",VLOOKUP(J14,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q14" s="7" t="str">
-        <f>IF(K14&lt;&gt;"",VLOOKUP(K14,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K14&lt;&gt;"",VLOOKUP(K14,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S14" s="7" t="str">
@@ -8381,19 +8511,19 @@
         <v>3</v>
       </c>
       <c r="N15" s="7">
-        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="O15" s="7">
-        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P15" s="7">
-        <f>IF(J15&lt;&gt;"",VLOOKUP(J15,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J15&lt;&gt;"",VLOOKUP(J15,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="Q15" s="7" t="str">
-        <f>IF(K15&lt;&gt;"",VLOOKUP(K15,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K15&lt;&gt;"",VLOOKUP(K15,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S15" s="7" t="str">
@@ -8425,19 +8555,19 @@
         <v>3</v>
       </c>
       <c r="N16" s="7">
-        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3113</v>
       </c>
       <c r="O16" s="7">
-        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P16" s="7" t="str">
-        <f>IF(J16&lt;&gt;"",VLOOKUP(J16,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J16&lt;&gt;"",VLOOKUP(J16,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q16" s="7" t="str">
-        <f>IF(K16&lt;&gt;"",VLOOKUP(K16,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K16&lt;&gt;"",VLOOKUP(K16,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S16" s="7" t="str">
@@ -8471,19 +8601,19 @@
       <c r="K17" s="7"/>
       <c r="L17" s="8"/>
       <c r="N17" s="7">
-        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O17" s="7">
-        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P17" s="7" t="str">
-        <f>IF(J17&lt;&gt;"",VLOOKUP(J17,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J17&lt;&gt;"",VLOOKUP(J17,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q17" s="7" t="str">
-        <f>IF(K17&lt;&gt;"",VLOOKUP(K17,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K17&lt;&gt;"",VLOOKUP(K17,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S17" s="7" t="str">
@@ -8516,19 +8646,19 @@
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7">
-        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="O18" s="7" t="str">
-        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P18" s="7" t="str">
-        <f>IF(J18&lt;&gt;"",VLOOKUP(J18,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J18&lt;&gt;"",VLOOKUP(J18,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q18" s="7" t="str">
-        <f>IF(K18&lt;&gt;"",VLOOKUP(K18,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K18&lt;&gt;"",VLOOKUP(K18,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S18" s="7" t="str">
@@ -8566,19 +8696,19 @@
         <v>3</v>
       </c>
       <c r="N19" s="7">
-        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="O19" s="7">
-        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P19" s="7">
-        <f>IF(J19&lt;&gt;"",VLOOKUP(J19,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J19&lt;&gt;"",VLOOKUP(J19,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="Q19" s="7" t="str">
-        <f>IF(K19&lt;&gt;"",VLOOKUP(K19,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K19&lt;&gt;"",VLOOKUP(K19,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S19" s="7" t="str">
@@ -8614,19 +8744,19 @@
       </c>
       <c r="L20" s="8"/>
       <c r="N20" s="7">
-        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O20" s="7">
-        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="P20" s="7">
-        <f>IF(J20&lt;&gt;"",VLOOKUP(J20,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J20&lt;&gt;"",VLOOKUP(J20,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3114</v>
       </c>
       <c r="Q20" s="7">
-        <f>IF(K20&lt;&gt;"",VLOOKUP(K20,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K20&lt;&gt;"",VLOOKUP(K20,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="S20" s="7" t="str">
@@ -8663,19 +8793,19 @@
       <c r="L21" s="8"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7">
-        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O21" s="7">
-        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3166</v>
       </c>
       <c r="P21" s="7">
-        <f>IF(J21&lt;&gt;"",VLOOKUP(J21,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J21&lt;&gt;"",VLOOKUP(J21,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="Q21" s="7">
-        <f>IF(K21&lt;&gt;"",VLOOKUP(K21,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K21&lt;&gt;"",VLOOKUP(K21,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="S21" s="7" t="str">
@@ -8709,19 +8839,19 @@
         <v>3</v>
       </c>
       <c r="N22" s="7">
-        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O22" s="7">
-        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P22" s="7" t="str">
-        <f>IF(J22&lt;&gt;"",VLOOKUP(J22,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J22&lt;&gt;"",VLOOKUP(J22,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q22" s="7" t="str">
-        <f>IF(K22&lt;&gt;"",VLOOKUP(K22,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K22&lt;&gt;"",VLOOKUP(K22,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S22" s="7" t="str">
@@ -8760,19 +8890,19 @@
       <c r="L23" s="8"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7">
-        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O23" s="7">
-        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="P23" s="7">
-        <f>IF(J23&lt;&gt;"",VLOOKUP(J23,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J23&lt;&gt;"",VLOOKUP(J23,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>4115</v>
       </c>
       <c r="Q23" s="7">
-        <f>IF(K23&lt;&gt;"",VLOOKUP(K23,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K23&lt;&gt;"",VLOOKUP(K23,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="S23" s="7" t="str">
@@ -8806,19 +8936,19 @@
       <c r="K24" s="7"/>
       <c r="L24" s="8"/>
       <c r="N24" s="7">
-        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O24" s="7">
-        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P24" s="7" t="str">
-        <f>IF(J24&lt;&gt;"",VLOOKUP(J24,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J24&lt;&gt;"",VLOOKUP(J24,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q24" s="7" t="str">
-        <f>IF(K24&lt;&gt;"",VLOOKUP(K24,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K24&lt;&gt;"",VLOOKUP(K24,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S24" s="7" t="str">
@@ -8854,19 +8984,19 @@
       </c>
       <c r="L25" s="8"/>
       <c r="N25" s="7">
-        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O25" s="7">
-        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="P25" s="7">
-        <f>IF(J25&lt;&gt;"",VLOOKUP(J25,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J25&lt;&gt;"",VLOOKUP(J25,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="Q25" s="7">
-        <f>IF(K25&lt;&gt;"",VLOOKUP(K25,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K25&lt;&gt;"",VLOOKUP(K25,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="S25" s="7" t="str">
@@ -8895,19 +9025,19 @@
         <v>1</v>
       </c>
       <c r="N26" s="7">
-        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1010</v>
       </c>
       <c r="O26" s="7" t="str">
-        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P26" s="7" t="str">
-        <f>IF(J26&lt;&gt;"",VLOOKUP(J26,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J26&lt;&gt;"",VLOOKUP(J26,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q26" s="7" t="str">
-        <f>IF(K26&lt;&gt;"",VLOOKUP(K26,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K26&lt;&gt;"",VLOOKUP(K26,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S26" s="7" t="str">
@@ -8937,19 +9067,19 @@
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7">
-        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1012</v>
       </c>
       <c r="O27" s="7" t="str">
-        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P27" s="7" t="str">
-        <f>IF(J27&lt;&gt;"",VLOOKUP(J27,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J27&lt;&gt;"",VLOOKUP(J27,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q27" s="7" t="str">
-        <f>IF(K27&lt;&gt;"",VLOOKUP(K27,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K27&lt;&gt;"",VLOOKUP(K27,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S27" s="7" t="str">
@@ -8978,19 +9108,19 @@
         <v>1</v>
       </c>
       <c r="N28" s="7">
-        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1022</v>
       </c>
       <c r="O28" s="7" t="str">
-        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P28" s="7" t="str">
-        <f>IF(J28&lt;&gt;"",VLOOKUP(J28,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J28&lt;&gt;"",VLOOKUP(J28,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q28" s="7" t="str">
-        <f>IF(K28&lt;&gt;"",VLOOKUP(K28,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K28&lt;&gt;"",VLOOKUP(K28,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S28" s="7" t="str">
@@ -9019,19 +9149,19 @@
         <v>1</v>
       </c>
       <c r="N29" s="7">
-        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1023</v>
       </c>
       <c r="O29" s="7" t="str">
-        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P29" s="7" t="str">
-        <f>IF(J29&lt;&gt;"",VLOOKUP(J29,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J29&lt;&gt;"",VLOOKUP(J29,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q29" s="7" t="str">
-        <f>IF(K29&lt;&gt;"",VLOOKUP(K29,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K29&lt;&gt;"",VLOOKUP(K29,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S29" s="7" t="str">
@@ -9054,19 +9184,19 @@
         <v>1</v>
       </c>
       <c r="N30" s="7">
-        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="O30" s="7" t="str">
-        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P30" s="7" t="str">
-        <f>IF(J30&lt;&gt;"",VLOOKUP(J30,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J30&lt;&gt;"",VLOOKUP(J30,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q30" s="7" t="str">
-        <f>IF(K30&lt;&gt;"",VLOOKUP(K30,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K30&lt;&gt;"",VLOOKUP(K30,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S30" s="7" t="str">
@@ -9095,19 +9225,19 @@
         <v>1</v>
       </c>
       <c r="N31" s="7">
-        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O31" s="7" t="str">
-        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P31" s="7" t="str">
-        <f>IF(J31&lt;&gt;"",VLOOKUP(J31,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J31&lt;&gt;"",VLOOKUP(J31,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q31" s="7" t="str">
-        <f>IF(K31&lt;&gt;"",VLOOKUP(K31,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K31&lt;&gt;"",VLOOKUP(K31,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S31" s="7" t="str">
@@ -9136,19 +9266,19 @@
       <c r="K32" s="7"/>
       <c r="L32" s="8"/>
       <c r="N32" s="7">
-        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O32" s="7" t="str">
-        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P32" s="7" t="str">
-        <f>IF(J32&lt;&gt;"",VLOOKUP(J32,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J32&lt;&gt;"",VLOOKUP(J32,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q32" s="7" t="str">
-        <f>IF(K32&lt;&gt;"",VLOOKUP(K32,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K32&lt;&gt;"",VLOOKUP(K32,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S32" s="7" t="str">
@@ -9183,19 +9313,19 @@
         <v>2</v>
       </c>
       <c r="N33" s="7">
-        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="O33" s="7">
-        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="P33" s="7" t="str">
-        <f>IF(J33&lt;&gt;"",VLOOKUP(J33,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J33&lt;&gt;"",VLOOKUP(J33,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q33" s="7" t="str">
-        <f>IF(K33&lt;&gt;"",VLOOKUP(K33,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K33&lt;&gt;"",VLOOKUP(K33,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S33" s="7" t="str">
@@ -9224,19 +9354,19 @@
         <v>1</v>
       </c>
       <c r="N34" s="7">
-        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O34" s="7" t="str">
-        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P34" s="7" t="str">
-        <f>IF(J34&lt;&gt;"",VLOOKUP(J34,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J34&lt;&gt;"",VLOOKUP(J34,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q34" s="7" t="str">
-        <f>IF(K34&lt;&gt;"",VLOOKUP(K34,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K34&lt;&gt;"",VLOOKUP(K34,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S34" s="7" t="str">
@@ -9268,19 +9398,19 @@
         <v>1</v>
       </c>
       <c r="N35" s="7">
-        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O35" s="7" t="str">
-        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P35" s="7" t="str">
-        <f>IF(J35&lt;&gt;"",VLOOKUP(J35,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J35&lt;&gt;"",VLOOKUP(J35,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q35" s="7" t="str">
-        <f>IF(K35&lt;&gt;"",VLOOKUP(K35,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K35&lt;&gt;"",VLOOKUP(K35,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S35" s="7" t="str">
@@ -9307,19 +9437,19 @@
         <v>2</v>
       </c>
       <c r="N36" s="7">
-        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O36" s="7">
-        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P36" s="7" t="str">
-        <f>IF(J36&lt;&gt;"",VLOOKUP(J36,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J36&lt;&gt;"",VLOOKUP(J36,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q36" s="7" t="str">
-        <f>IF(K36&lt;&gt;"",VLOOKUP(K36,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K36&lt;&gt;"",VLOOKUP(K36,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S36" s="7" t="str">
@@ -9357,19 +9487,19 @@
         <v>4</v>
       </c>
       <c r="N37" s="7">
-        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1013</v>
       </c>
       <c r="O37" s="7">
-        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="P37" s="7">
-        <f>IF(J37&lt;&gt;"",VLOOKUP(J37,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J37&lt;&gt;"",VLOOKUP(J37,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="Q37" s="7">
-        <f>IF(K37&lt;&gt;"",VLOOKUP(K37,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K37&lt;&gt;"",VLOOKUP(K37,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="S37" s="7" t="str">
@@ -9409,19 +9539,19 @@
         <v>5</v>
       </c>
       <c r="N38" s="7">
-        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O38" s="7">
-        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P38" s="7">
-        <f>IF(J38&lt;&gt;"",VLOOKUP(J38,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J38&lt;&gt;"",VLOOKUP(J38,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="Q38" s="7">
-        <f>IF(K38&lt;&gt;"",VLOOKUP(K38,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K38&lt;&gt;"",VLOOKUP(K38,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="S38" s="7" t="str">
@@ -9461,19 +9591,19 @@
         <v>5</v>
       </c>
       <c r="N39" s="7">
-        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="O39" s="7">
-        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="P39" s="7">
-        <f>IF(J39&lt;&gt;"",VLOOKUP(J39,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J39&lt;&gt;"",VLOOKUP(J39,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="Q39" s="7">
-        <f>IF(K39&lt;&gt;"",VLOOKUP(K39,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K39&lt;&gt;"",VLOOKUP(K39,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="S39" s="7" t="str">
@@ -9505,19 +9635,19 @@
         <v>1</v>
       </c>
       <c r="N40" s="7">
-        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1017</v>
       </c>
       <c r="O40" s="7" t="str">
-        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P40" s="7" t="str">
-        <f>IF(J40&lt;&gt;"",VLOOKUP(J40,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J40&lt;&gt;"",VLOOKUP(J40,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q40" s="7" t="str">
-        <f>IF(K40&lt;&gt;"",VLOOKUP(K40,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K40&lt;&gt;"",VLOOKUP(K40,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S40" s="7" t="str">
@@ -9545,26 +9675,26 @@
         <v>55</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>170</v>
+        <v>490</v>
       </c>
       <c r="L41" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N41" s="7">
-        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O41" s="7">
-        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P41" s="7">
-        <f>IF(J41&lt;&gt;"",VLOOKUP(J41,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J41&lt;&gt;"",VLOOKUP(J41,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="Q41" s="7">
-        <f>IF(K41&lt;&gt;"",VLOOKUP(K41,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K41&lt;&gt;"",VLOOKUP(K41,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="S41" s="7" t="str">
@@ -9602,19 +9732,19 @@
         <v>4</v>
       </c>
       <c r="N42" s="7">
-        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="O42" s="7">
-        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P42" s="7">
-        <f>IF(J42&lt;&gt;"",VLOOKUP(J42,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J42&lt;&gt;"",VLOOKUP(J42,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q42" s="7">
-        <f>IF(K42&lt;&gt;"",VLOOKUP(K42,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K42&lt;&gt;"",VLOOKUP(K42,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="S42" s="7" t="str">
@@ -9643,19 +9773,19 @@
         <v>3</v>
       </c>
       <c r="N43" s="7">
-        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O43" s="7">
-        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P43" s="7" t="str">
-        <f>IF(J43&lt;&gt;"",VLOOKUP(J43,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J43&lt;&gt;"",VLOOKUP(J43,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q43" s="7" t="str">
-        <f>IF(K43&lt;&gt;"",VLOOKUP(K43,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K43&lt;&gt;"",VLOOKUP(K43,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S43" s="7" t="str">
@@ -9687,19 +9817,19 @@
         <v>3</v>
       </c>
       <c r="N44" s="7">
-        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O44" s="7">
-        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="P44" s="7">
-        <f>IF(J44&lt;&gt;"",VLOOKUP(J44,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J44&lt;&gt;"",VLOOKUP(J44,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="Q44" s="7" t="str">
-        <f>IF(K44&lt;&gt;"",VLOOKUP(K44,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K44&lt;&gt;"",VLOOKUP(K44,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S44" s="7" t="str">
@@ -9730,19 +9860,19 @@
         <v>4</v>
       </c>
       <c r="N45" s="7">
-        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O45" s="7">
-        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="P45" s="7">
-        <f>IF(J45&lt;&gt;"",VLOOKUP(J45,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J45&lt;&gt;"",VLOOKUP(J45,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3113</v>
       </c>
       <c r="Q45" s="7" t="str">
-        <f>IF(K45&lt;&gt;"",VLOOKUP(K45,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K45&lt;&gt;"",VLOOKUP(K45,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S45" s="7" t="str">
@@ -9773,19 +9903,19 @@
         <v>4</v>
       </c>
       <c r="N46" s="7">
-        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O46" s="7">
-        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="P46" s="7">
-        <f>IF(J46&lt;&gt;"",VLOOKUP(J46,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J46&lt;&gt;"",VLOOKUP(J46,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="Q46" s="7" t="str">
-        <f>IF(K46&lt;&gt;"",VLOOKUP(K46,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K46&lt;&gt;"",VLOOKUP(K46,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S46" s="7" t="str">
@@ -9816,19 +9946,19 @@
         <v>4</v>
       </c>
       <c r="N47" s="7">
-        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O47" s="7">
-        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P47" s="7" t="str">
-        <f>IF(J47&lt;&gt;"",VLOOKUP(J47,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J47&lt;&gt;"",VLOOKUP(J47,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q47" s="7" t="str">
-        <f>IF(K47&lt;&gt;"",VLOOKUP(K47,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K47&lt;&gt;"",VLOOKUP(K47,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S47" s="7" t="str">
@@ -9864,19 +9994,19 @@
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7">
-        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="O48" s="7">
-        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P48" s="7" t="str">
-        <f>IF(J48&lt;&gt;"",VLOOKUP(J48,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J48&lt;&gt;"",VLOOKUP(J48,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q48" s="7" t="str">
-        <f>IF(K48&lt;&gt;"",VLOOKUP(K48,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K48&lt;&gt;"",VLOOKUP(K48,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S48" s="7" t="str">
@@ -9912,19 +10042,19 @@
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7">
-        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O49" s="7">
-        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P49" s="7" t="str">
-        <f>IF(J49&lt;&gt;"",VLOOKUP(J49,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J49&lt;&gt;"",VLOOKUP(J49,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q49" s="7" t="str">
-        <f>IF(K49&lt;&gt;"",VLOOKUP(K49,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K49&lt;&gt;"",VLOOKUP(K49,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S49" s="7" t="str">
@@ -9962,19 +10092,19 @@
         <v>3</v>
       </c>
       <c r="N50" s="7">
-        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1020</v>
       </c>
       <c r="O50" s="7">
-        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P50" s="7">
-        <f>IF(J50&lt;&gt;"",VLOOKUP(J50,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J50&lt;&gt;"",VLOOKUP(J50,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q50" s="7" t="str">
-        <f>IF(K50&lt;&gt;"",VLOOKUP(K50,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K50&lt;&gt;"",VLOOKUP(K50,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S50" s="7" t="str">
@@ -10009,19 +10139,19 @@
         <v>2</v>
       </c>
       <c r="N51" s="7">
-        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3129</v>
       </c>
       <c r="O51" s="7">
-        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P51" s="7" t="str">
-        <f>IF(J51&lt;&gt;"",VLOOKUP(J51,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J51&lt;&gt;"",VLOOKUP(J51,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q51" s="7" t="str">
-        <f>IF(K51&lt;&gt;"",VLOOKUP(K51,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K51&lt;&gt;"",VLOOKUP(K51,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S51" s="7" t="str">
@@ -10057,19 +10187,19 @@
       <c r="K52" s="7"/>
       <c r="L52" s="8"/>
       <c r="N52" s="7">
-        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="O52" s="7">
-        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P52" s="7">
-        <f>IF(J52&lt;&gt;"",VLOOKUP(J52,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J52&lt;&gt;"",VLOOKUP(J52,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q52" s="7" t="str">
-        <f>IF(K52&lt;&gt;"",VLOOKUP(K52,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K52&lt;&gt;"",VLOOKUP(K52,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S52" s="7" t="str">
@@ -10107,19 +10237,19 @@
         <v>3</v>
       </c>
       <c r="N53" s="7">
-        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3126</v>
       </c>
       <c r="O53" s="7">
-        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P53" s="7">
-        <f>IF(J53&lt;&gt;"",VLOOKUP(J53,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J53&lt;&gt;"",VLOOKUP(J53,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="Q53" s="7" t="str">
-        <f>IF(K53&lt;&gt;"",VLOOKUP(K53,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K53&lt;&gt;"",VLOOKUP(K53,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S53" s="7" t="str">
@@ -10160,19 +10290,19 @@
         <v>4</v>
       </c>
       <c r="N54" s="7">
-        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="O54" s="7">
-        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="P54" s="7">
-        <f>IF(J54&lt;&gt;"",VLOOKUP(J54,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J54&lt;&gt;"",VLOOKUP(J54,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3121</v>
       </c>
       <c r="Q54" s="7">
-        <f>IF(K54&lt;&gt;"",VLOOKUP(K54,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K54&lt;&gt;"",VLOOKUP(K54,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="S54" s="7" t="str">
@@ -10213,19 +10343,19 @@
         <v>4</v>
       </c>
       <c r="N55" s="7">
-        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3122</v>
       </c>
       <c r="O55" s="7">
-        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3124</v>
       </c>
       <c r="P55" s="7">
-        <f>IF(J55&lt;&gt;"",VLOOKUP(J55,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J55&lt;&gt;"",VLOOKUP(J55,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3127</v>
       </c>
       <c r="Q55" s="7">
-        <f>IF(K55&lt;&gt;"",VLOOKUP(K55,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K55&lt;&gt;"",VLOOKUP(K55,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="S55" s="7" t="str">
@@ -10260,19 +10390,19 @@
         <v>2</v>
       </c>
       <c r="N56" s="7">
-        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O56" s="7">
-        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P56" s="7" t="str">
-        <f>IF(J56&lt;&gt;"",VLOOKUP(J56,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J56&lt;&gt;"",VLOOKUP(J56,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q56" s="7" t="str">
-        <f>IF(K56&lt;&gt;"",VLOOKUP(K56,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K56&lt;&gt;"",VLOOKUP(K56,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S56" s="7" t="str">
@@ -10307,19 +10437,19 @@
         <v>2</v>
       </c>
       <c r="N57" s="7">
-        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4009</v>
       </c>
       <c r="O57" s="7">
-        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P57" s="7" t="str">
-        <f>IF(J57&lt;&gt;"",VLOOKUP(J57,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J57&lt;&gt;"",VLOOKUP(J57,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q57" s="7" t="str">
-        <f>IF(K57&lt;&gt;"",VLOOKUP(K57,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K57&lt;&gt;"",VLOOKUP(K57,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S57" s="7" t="str">
@@ -10354,19 +10484,19 @@
         <v>2</v>
       </c>
       <c r="N58" s="7">
-        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4015</v>
       </c>
       <c r="O58" s="7">
-        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P58" s="7" t="str">
-        <f>IF(J58&lt;&gt;"",VLOOKUP(J58,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J58&lt;&gt;"",VLOOKUP(J58,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q58" s="7" t="str">
-        <f>IF(K58&lt;&gt;"",VLOOKUP(K58,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K58&lt;&gt;"",VLOOKUP(K58,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S58" s="7" t="str">
@@ -10401,19 +10531,19 @@
         <v>2</v>
       </c>
       <c r="N59" s="7">
-        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4016</v>
       </c>
       <c r="O59" s="7">
-        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P59" s="7" t="str">
-        <f>IF(J59&lt;&gt;"",VLOOKUP(J59,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J59&lt;&gt;"",VLOOKUP(J59,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q59" s="7" t="str">
-        <f>IF(K59&lt;&gt;"",VLOOKUP(K59,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K59&lt;&gt;"",VLOOKUP(K59,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S59" s="7" t="str">
@@ -10448,19 +10578,19 @@
         <v>2</v>
       </c>
       <c r="N60" s="7">
-        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4017</v>
       </c>
       <c r="O60" s="7">
-        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P60" s="7" t="str">
-        <f>IF(J60&lt;&gt;"",VLOOKUP(J60,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J60&lt;&gt;"",VLOOKUP(J60,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q60" s="7" t="str">
-        <f>IF(K60&lt;&gt;"",VLOOKUP(K60,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K60&lt;&gt;"",VLOOKUP(K60,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S60" s="7" t="str">
@@ -10495,19 +10625,19 @@
         <v>2</v>
       </c>
       <c r="N61" s="7">
-        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O61" s="7">
-        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P61" s="7" t="str">
-        <f>IF(J61&lt;&gt;"",VLOOKUP(J61,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J61&lt;&gt;"",VLOOKUP(J61,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q61" s="7" t="str">
-        <f>IF(K61&lt;&gt;"",VLOOKUP(K61,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K61&lt;&gt;"",VLOOKUP(K61,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S61" s="7" t="str">
@@ -10542,19 +10672,19 @@
         <v>2</v>
       </c>
       <c r="N62" s="7">
-        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4100</v>
       </c>
       <c r="O62" s="7">
-        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P62" s="7" t="str">
-        <f>IF(J62&lt;&gt;"",VLOOKUP(J62,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J62&lt;&gt;"",VLOOKUP(J62,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q62" s="7" t="str">
-        <f>IF(K62&lt;&gt;"",VLOOKUP(K62,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K62&lt;&gt;"",VLOOKUP(K62,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S62" s="7" t="str">
@@ -10589,19 +10719,19 @@
         <v>2</v>
       </c>
       <c r="N63" s="7">
-        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4101</v>
       </c>
       <c r="O63" s="7">
-        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P63" s="7" t="str">
-        <f>IF(J63&lt;&gt;"",VLOOKUP(J63,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J63&lt;&gt;"",VLOOKUP(J63,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q63" s="7" t="str">
-        <f>IF(K63&lt;&gt;"",VLOOKUP(K63,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K63&lt;&gt;"",VLOOKUP(K63,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S63" s="7" t="str">
@@ -10636,19 +10766,19 @@
         <v>2</v>
       </c>
       <c r="N64" s="7">
-        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4103</v>
       </c>
       <c r="O64" s="7">
-        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P64" s="7" t="str">
-        <f>IF(J64&lt;&gt;"",VLOOKUP(J64,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J64&lt;&gt;"",VLOOKUP(J64,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q64" s="7" t="str">
-        <f>IF(K64&lt;&gt;"",VLOOKUP(K64,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K64&lt;&gt;"",VLOOKUP(K64,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S64" s="7" t="str">
@@ -10683,19 +10813,19 @@
         <v>2</v>
       </c>
       <c r="N65" s="7">
-        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4106</v>
       </c>
       <c r="O65" s="7">
-        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P65" s="7" t="str">
-        <f>IF(J65&lt;&gt;"",VLOOKUP(J65,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J65&lt;&gt;"",VLOOKUP(J65,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q65" s="7" t="str">
-        <f>IF(K65&lt;&gt;"",VLOOKUP(K65,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K65&lt;&gt;"",VLOOKUP(K65,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S65" s="7" t="str">
@@ -10730,19 +10860,19 @@
         <v>2</v>
       </c>
       <c r="N66" s="7">
-        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O66" s="7">
-        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P66" s="7" t="str">
-        <f>IF(J66&lt;&gt;"",VLOOKUP(J66,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J66&lt;&gt;"",VLOOKUP(J66,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q66" s="7" t="str">
-        <f>IF(K66&lt;&gt;"",VLOOKUP(K66,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K66&lt;&gt;"",VLOOKUP(K66,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S66" s="7" t="str">
@@ -10771,19 +10901,19 @@
         <v>2</v>
       </c>
       <c r="N67" s="7">
-        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O67" s="7">
-        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P67" s="7" t="str">
-        <f>IF(J67&lt;&gt;"",VLOOKUP(J67,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J67&lt;&gt;"",VLOOKUP(J67,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q67" s="7" t="str">
-        <f>IF(K67&lt;&gt;"",VLOOKUP(K67,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K67&lt;&gt;"",VLOOKUP(K67,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S67" s="7" t="str">
@@ -10813,19 +10943,19 @@
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7">
-        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O68" s="7">
-        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P68" s="7" t="str">
-        <f>IF(J68&lt;&gt;"",VLOOKUP(J68,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J68&lt;&gt;"",VLOOKUP(J68,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q68" s="7" t="str">
-        <f>IF(K68&lt;&gt;"",VLOOKUP(K68,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K68&lt;&gt;"",VLOOKUP(K68,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S68" s="7" t="str">
@@ -10854,19 +10984,19 @@
         <v>2</v>
       </c>
       <c r="N69" s="7">
-        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O69" s="7">
-        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P69" s="7" t="str">
-        <f>IF(J69&lt;&gt;"",VLOOKUP(J69,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J69&lt;&gt;"",VLOOKUP(J69,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q69" s="7" t="str">
-        <f>IF(K69&lt;&gt;"",VLOOKUP(K69,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K69&lt;&gt;"",VLOOKUP(K69,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S69" s="7" t="str">
@@ -10895,19 +11025,19 @@
         <v>2</v>
       </c>
       <c r="N70" s="7">
-        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4115</v>
       </c>
       <c r="O70" s="7">
-        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P70" s="7" t="str">
-        <f>IF(J70&lt;&gt;"",VLOOKUP(J70,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J70&lt;&gt;"",VLOOKUP(J70,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q70" s="7" t="str">
-        <f>IF(K70&lt;&gt;"",VLOOKUP(K70,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K70&lt;&gt;"",VLOOKUP(K70,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S70" s="7" t="str">
@@ -10936,19 +11066,19 @@
         <v>2</v>
       </c>
       <c r="N71" s="7">
-        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O71" s="7">
-        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P71" s="7" t="str">
-        <f>IF(J71&lt;&gt;"",VLOOKUP(J71,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J71&lt;&gt;"",VLOOKUP(J71,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q71" s="7" t="str">
-        <f>IF(K71&lt;&gt;"",VLOOKUP(K71,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K71&lt;&gt;"",VLOOKUP(K71,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S71" s="7" t="str">
@@ -10978,19 +11108,19 @@
         <v>2</v>
       </c>
       <c r="N72" s="7">
-        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4007</v>
       </c>
       <c r="O72" s="7">
-        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P72" s="7" t="str">
-        <f>IF(J72&lt;&gt;"",VLOOKUP(J72,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J72&lt;&gt;"",VLOOKUP(J72,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q72" s="7" t="str">
-        <f>IF(K72&lt;&gt;"",VLOOKUP(K72,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K72&lt;&gt;"",VLOOKUP(K72,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S72" s="7" t="str">
@@ -11025,19 +11155,19 @@
         <v>3</v>
       </c>
       <c r="N73" s="7">
-        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="O73" s="7">
-        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P73" s="7">
-        <f>IF(J73&lt;&gt;"",VLOOKUP(J73,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J73&lt;&gt;"",VLOOKUP(J73,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>4100</v>
       </c>
       <c r="Q73" s="7">
-        <f>IF(K73&lt;&gt;"",VLOOKUP(K73,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K73&lt;&gt;"",VLOOKUP(K73,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="S73" s="7" t="str">
@@ -11063,19 +11193,19 @@
         <v>2</v>
       </c>
       <c r="N74" s="7">
-        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3158</v>
       </c>
       <c r="O74" s="7">
-        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P74" s="7" t="str">
-        <f>IF(J74&lt;&gt;"",VLOOKUP(J74,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J74&lt;&gt;"",VLOOKUP(J74,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q74" s="7" t="str">
-        <f>IF(K74&lt;&gt;"",VLOOKUP(K74,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K74&lt;&gt;"",VLOOKUP(K74,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S74" s="7" t="str">
@@ -11113,19 +11243,19 @@
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7">
-        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4000</v>
       </c>
       <c r="O75" s="7">
-        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="P75" s="7">
-        <f>IF(J75&lt;&gt;"",VLOOKUP(J75,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J75&lt;&gt;"",VLOOKUP(J75,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="Q75" s="7">
-        <f>IF(K75&lt;&gt;"",VLOOKUP(K75,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K75&lt;&gt;"",VLOOKUP(K75,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1017</v>
       </c>
       <c r="S75" s="7" t="str">
@@ -11155,19 +11285,19 @@
         <v>2</v>
       </c>
       <c r="N76" s="7">
-        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O76" s="7">
-        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="P76" s="7" t="str">
-        <f>IF(J76&lt;&gt;"",VLOOKUP(J76,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J76&lt;&gt;"",VLOOKUP(J76,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q76" s="7" t="str">
-        <f>IF(K76&lt;&gt;"",VLOOKUP(K76,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K76&lt;&gt;"",VLOOKUP(K76,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S76" s="7" t="str">
@@ -11190,19 +11320,19 @@
         <v>1</v>
       </c>
       <c r="N77" s="7">
-        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O77" s="7" t="str">
-        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P77" s="7" t="str">
-        <f>IF(J77&lt;&gt;"",VLOOKUP(J77,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J77&lt;&gt;"",VLOOKUP(J77,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q77" s="7" t="str">
-        <f>IF(K77&lt;&gt;"",VLOOKUP(K77,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K77&lt;&gt;"",VLOOKUP(K77,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S77" s="7" t="str">
@@ -11234,19 +11364,19 @@
         <v>3</v>
       </c>
       <c r="N78" s="7">
-        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="O78" s="7">
-        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P78" s="7">
-        <f>IF(J78&lt;&gt;"",VLOOKUP(J78,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J78&lt;&gt;"",VLOOKUP(J78,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="Q78" s="7" t="str">
-        <f>IF(K78&lt;&gt;"",VLOOKUP(K78,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K78&lt;&gt;"",VLOOKUP(K78,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S78" s="7" t="str">
@@ -11275,19 +11405,19 @@
         <v>2</v>
       </c>
       <c r="N79" s="7">
-        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O79" s="7">
-        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="P79" s="7" t="str">
-        <f>IF(J79&lt;&gt;"",VLOOKUP(J79,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J79&lt;&gt;"",VLOOKUP(J79,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q79" s="7" t="str">
-        <f>IF(K79&lt;&gt;"",VLOOKUP(K79,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K79&lt;&gt;"",VLOOKUP(K79,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S79" s="7" t="str">
@@ -11309,19 +11439,19 @@
       <c r="K80" s="7"/>
       <c r="L80" s="8"/>
       <c r="N80" s="7">
-        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O80" s="7" t="str">
-        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P80" s="7" t="str">
-        <f>IF(J80&lt;&gt;"",VLOOKUP(J80,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J80&lt;&gt;"",VLOOKUP(J80,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q80" s="7" t="str">
-        <f>IF(K80&lt;&gt;"",VLOOKUP(K80,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K80&lt;&gt;"",VLOOKUP(K80,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S80" s="7" t="str">
@@ -11344,19 +11474,19 @@
         <v>1</v>
       </c>
       <c r="N81" s="7">
-        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O81" s="7" t="str">
-        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P81" s="7" t="str">
-        <f>IF(J81&lt;&gt;"",VLOOKUP(J81,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J81&lt;&gt;"",VLOOKUP(J81,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q81" s="7" t="str">
-        <f>IF(K81&lt;&gt;"",VLOOKUP(K81,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K81&lt;&gt;"",VLOOKUP(K81,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S81" s="7" t="str">
@@ -11392,19 +11522,19 @@
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="7">
-        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O82" s="7">
-        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="P82" s="7">
-        <f>IF(J82&lt;&gt;"",VLOOKUP(J82,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J82&lt;&gt;"",VLOOKUP(J82,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1009</v>
       </c>
       <c r="Q82" s="7">
-        <f>IF(K82&lt;&gt;"",VLOOKUP(K82,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K82&lt;&gt;"",VLOOKUP(K82,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1007</v>
       </c>
       <c r="S82" s="7" t="str">
@@ -11427,19 +11557,19 @@
         <v>1</v>
       </c>
       <c r="N83" s="7">
-        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O83" s="7" t="str">
-        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P83" s="7" t="str">
-        <f>IF(J83&lt;&gt;"",VLOOKUP(J83,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J83&lt;&gt;"",VLOOKUP(J83,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q83" s="7" t="str">
-        <f>IF(K83&lt;&gt;"",VLOOKUP(K83,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K83&lt;&gt;"",VLOOKUP(K83,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="S83" s="7" t="str">
@@ -11471,19 +11601,19 @@
         <v>4</v>
       </c>
       <c r="N84" s="7">
-        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3164</v>
       </c>
       <c r="O84" s="7">
-        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$531,2,FALSE),"")</f>
+        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
         <v>3134</v>
       </c>
       <c r="P84" s="7">
-        <f>IF(J84&lt;&gt;"",VLOOKUP(J84,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(J84&lt;&gt;"",VLOOKUP(J84,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="Q84" s="7">
-        <f>IF(K84&lt;&gt;"",VLOOKUP(K84,[1]ItemData!$A$4:$B$331,2,FALSE),"")</f>
+        <f>IF(K84&lt;&gt;"",VLOOKUP(K84,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="S84" s="7" t="str">

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -5,11 +5,11 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="6" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2962,7 +2962,7 @@
         </row>
         <row r="142">
           <cell r="A142" t="str">
-            <v>小麦</v>
+            <v>大麦</v>
           </cell>
           <cell r="B142">
             <v>1020</v>
@@ -3314,7 +3314,7 @@
         </row>
         <row r="186">
           <cell r="A186" t="str">
-            <v>血腥之枪</v>
+            <v>血腥之矛</v>
           </cell>
           <cell r="B186">
             <v>1607</v>
@@ -3362,7 +3362,7 @@
         </row>
         <row r="192">
           <cell r="A192" t="str">
-            <v>藤鞭</v>
+            <v>荆棘鞭</v>
           </cell>
           <cell r="B192">
             <v>1613</v>
@@ -3370,7 +3370,7 @@
         </row>
         <row r="193">
           <cell r="A193" t="str">
-            <v>女王鞭</v>
+            <v>女王之鞭</v>
           </cell>
           <cell r="B193">
             <v>1614</v>
@@ -3658,7 +3658,7 @@
         </row>
         <row r="229">
           <cell r="A229" t="str">
-            <v>暮光草帽</v>
+            <v>阳光草帽</v>
           </cell>
           <cell r="B229">
             <v>1801</v>
@@ -3786,7 +3786,7 @@
         </row>
         <row r="245">
           <cell r="A245" t="str">
-            <v>蒸煮锅</v>
+            <v>炖煮锅</v>
           </cell>
           <cell r="B245">
             <v>2103</v>
@@ -4985,8 +4985,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5027,7 +5027,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -7914,9 +7914,9 @@
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="N2" s="1">
+      <c r="N2" s="1" t="e">
         <f>IF(H2&lt;&gt;"",VLOOKUP(H2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
-        <v>1020</v>
+        <v>#N/A</v>
       </c>
       <c r="O2" s="7" t="str">
         <f>IF(I2&lt;&gt;"",VLOOKUP(I2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
@@ -7930,9 +7930,9 @@
         <f>IF(K2&lt;&gt;"",VLOOKUP(K2,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="S2" s="1" t="str">
+      <c r="S2" s="1" t="e">
         <f>IF(N2&lt;&gt;"",N2&amp;IF(O2&lt;&gt;"",","&amp;O2,"")&amp;IF(P2&lt;&gt;"",","&amp;P2,"")&amp;IF(Q2&lt;&gt;"",","&amp;Q2,""),"")</f>
-        <v>1020</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
@@ -10091,9 +10091,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="7" t="e">
         <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
-        <v>1020</v>
+        <v>#N/A</v>
       </c>
       <c r="O50" s="7">
         <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
@@ -10107,9 +10107,9 @@
         <f>IF(K50&lt;&gt;"",VLOOKUP(K50,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="S50" s="7" t="str">
+      <c r="S50" s="7" t="e">
         <f t="shared" si="0"/>
-        <v>1020,1021,3001</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.2">

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -9,21 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="6" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$D$4:$J$84</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="574">
   <si>
     <t>芜菁</t>
   </si>
@@ -1685,6 +1686,285 @@
   </si>
   <si>
     <t>纯净水</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+  </si>
+  <si>
+    <t>拉面</t>
+  </si>
+  <si>
+    <t>蜂蜜蛋糕</t>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+  </si>
+  <si>
+    <t>烤肉串</t>
+  </si>
+  <si>
+    <t>烤海苔</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+  </si>
+  <si>
+    <t>烤茄子</t>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>炖菜</t>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+  </si>
+  <si>
+    <t>红菜汤</t>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+  </si>
+  <si>
+    <t>拿铁</t>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+  </si>
+  <si>
+    <t>伏特加</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>朗姆</t>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+  </si>
+  <si>
+    <t>凉茶</t>
+  </si>
+  <si>
+    <t>主食</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>汤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>果汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接触流血</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解毒，解除燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海鲜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸运buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸运buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解毒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解失明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解厄运</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解流血</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗冰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗晕眩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗火</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗毒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -11997,6 +12277,1085 @@
   <autoFilter ref="D4:J84"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:AD83"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="9" style="7"/>
+    <col min="7" max="7" width="9" style="7"/>
+    <col min="9" max="9" width="9" style="7"/>
+    <col min="11" max="19" width="9" style="7"/>
+    <col min="20" max="22" width="9.125" style="7" customWidth="1"/>
+    <col min="23" max="28" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F2" t="s">
+        <v>549</v>
+      </c>
+      <c r="H2" t="s">
+        <v>559</v>
+      </c>
+      <c r="J2" t="s">
+        <v>560</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>15</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>544</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
+        <v>15</v>
+      </c>
+      <c r="U4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>545</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>10</v>
+      </c>
+      <c r="N5" s="7">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>548</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="6" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>550</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>492</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7">
+        <v>20</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>552</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>493</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7">
+        <v>20</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>556</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="9" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>553</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>495</v>
+      </c>
+      <c r="L13" s="7">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>496</v>
+      </c>
+      <c r="N16" s="7">
+        <v>1</v>
+      </c>
+      <c r="O16" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="L17" s="7">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>497</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="I18" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>498</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>20</v>
+      </c>
+      <c r="R19" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>499</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>222</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>215</v>
+      </c>
+      <c r="N23" s="7">
+        <v>1</v>
+      </c>
+      <c r="O23" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>500</v>
+      </c>
+      <c r="P24" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="P25" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="P29" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>191</v>
+      </c>
+      <c r="N30" s="7">
+        <v>1</v>
+      </c>
+      <c r="O30" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>501</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="N32" s="7">
+        <v>1</v>
+      </c>
+      <c r="O32" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C33" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C34" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>502</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>503</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7">
+        <v>80</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7">
+        <v>30</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>504</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7">
+        <v>100</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1</v>
+      </c>
+      <c r="G37" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>505</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>506</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>507</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
+        <v>70</v>
+      </c>
+      <c r="P41" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>508</v>
+      </c>
+      <c r="N42" s="7">
+        <v>1</v>
+      </c>
+      <c r="O42" s="7">
+        <v>20</v>
+      </c>
+      <c r="P42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>509</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>510</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7">
+        <v>80</v>
+      </c>
+      <c r="P44" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>40</v>
+      </c>
+      <c r="S44" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>511</v>
+      </c>
+      <c r="N45" s="7">
+        <v>1</v>
+      </c>
+      <c r="O45" s="7">
+        <v>30</v>
+      </c>
+      <c r="S45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>512</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>513</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>514</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>515</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>516</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C52" t="s">
+        <v>517</v>
+      </c>
+      <c r="J52" s="7">
+        <v>1</v>
+      </c>
+      <c r="K52" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>518</v>
+      </c>
+      <c r="J53" s="7">
+        <v>1</v>
+      </c>
+      <c r="K53" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>519</v>
+      </c>
+      <c r="L54" s="7">
+        <v>1</v>
+      </c>
+      <c r="M54" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C55" t="s">
+        <v>520</v>
+      </c>
+      <c r="L55" s="7">
+        <v>1</v>
+      </c>
+      <c r="M55" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>521</v>
+      </c>
+      <c r="L56" s="7">
+        <v>1</v>
+      </c>
+      <c r="M56" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>522</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C58" t="s">
+        <v>523</v>
+      </c>
+      <c r="L58" s="7">
+        <v>1</v>
+      </c>
+      <c r="M58" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C59" t="s">
+        <v>200</v>
+      </c>
+      <c r="L59" s="7">
+        <v>1</v>
+      </c>
+      <c r="M59" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C60" t="s">
+        <v>524</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C61" t="s">
+        <v>525</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" s="7">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>476</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C63" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" s="7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C64" t="s">
+        <v>526</v>
+      </c>
+      <c r="D64" s="7">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>527</v>
+      </c>
+      <c r="D65" s="7">
+        <v>1</v>
+      </c>
+      <c r="E65" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>528</v>
+      </c>
+      <c r="D66" s="7">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7">
+        <v>200</v>
+      </c>
+      <c r="J66" s="7"/>
+    </row>
+    <row r="67" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>529</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C68" t="s">
+        <v>530</v>
+      </c>
+      <c r="J68" s="7">
+        <v>1</v>
+      </c>
+      <c r="K68" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C69" t="s">
+        <v>531</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C70" t="s">
+        <v>186</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7">
+        <v>150</v>
+      </c>
+      <c r="L70" s="7">
+        <v>1</v>
+      </c>
+      <c r="M70" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C71" t="s">
+        <v>532</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" s="7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C72" t="s">
+        <v>533</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" s="7">
+        <v>150</v>
+      </c>
+      <c r="L72" s="7">
+        <v>1</v>
+      </c>
+      <c r="M72" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C73" t="s">
+        <v>534</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7">
+        <v>140</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C74" t="s">
+        <v>535</v>
+      </c>
+      <c r="L74" s="7">
+        <v>1</v>
+      </c>
+      <c r="M74" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C75" t="s">
+        <v>536</v>
+      </c>
+      <c r="N75" s="7">
+        <v>1</v>
+      </c>
+      <c r="O75" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C76" t="s">
+        <v>537</v>
+      </c>
+      <c r="L76" s="7">
+        <v>1</v>
+      </c>
+      <c r="M76" s="7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C78" t="s">
+        <v>539</v>
+      </c>
+      <c r="N78" s="7">
+        <v>1</v>
+      </c>
+      <c r="O78" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C79" t="s">
+        <v>540</v>
+      </c>
+      <c r="N79" s="7">
+        <v>1</v>
+      </c>
+      <c r="O79" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C80" t="s">
+        <v>571</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" s="7">
+        <v>170</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="C81" t="s">
+        <v>541</v>
+      </c>
+      <c r="N81" s="7">
+        <v>1</v>
+      </c>
+      <c r="O81" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="C82" t="s">
+        <v>542</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="C83" t="s">
+        <v>543</v>
+      </c>
+      <c r="N83" s="7">
+        <v>1</v>
+      </c>
+      <c r="O83" s="7">
+        <v>50</v>
+      </c>
+      <c r="P83" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>50</v>
+      </c>
+      <c r="T83" s="7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="575">
   <si>
     <t>芜菁</t>
   </si>
@@ -1966,6 +1966,10 @@
   <si>
     <t>抗毒</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2133,6 +2137,7 @@
       <sheetName val="ItemData"/>
       <sheetName val="Sheet2"/>
       <sheetName val="Sheet3"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5267,6 +5272,7 @@
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -12289,9 +12295,11 @@
     <col min="5" max="5" width="9" style="7"/>
     <col min="7" max="7" width="9" style="7"/>
     <col min="9" max="9" width="9" style="7"/>
-    <col min="11" max="19" width="9" style="7"/>
-    <col min="20" max="22" width="9.125" style="7" customWidth="1"/>
-    <col min="23" max="28" width="9" style="7"/>
+    <col min="11" max="17" width="9" style="7"/>
+    <col min="18" max="19" width="0" style="7" hidden="1" customWidth="1"/>
+    <col min="20" max="22" width="9.125" style="7" hidden="1" customWidth="1"/>
+    <col min="23" max="26" width="0" style="7" hidden="1" customWidth="1"/>
+    <col min="27" max="28" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:30" x14ac:dyDescent="0.2">
@@ -12531,8 +12539,8 @@
       <c r="C15" t="s">
         <v>58</v>
       </c>
-      <c r="H15">
-        <v>1</v>
+      <c r="H15" t="s">
+        <v>574</v>
       </c>
       <c r="I15" s="7">
         <v>40</v>

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -9,22 +9,26 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="6" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$D$4:$J$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$B$2:$AD$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet3!$B$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="601">
   <si>
     <t>芜菁</t>
   </si>
@@ -1968,14 +1972,106 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>4,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>虹鳟鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉茶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>线鱼</t>
+  </si>
+  <si>
+    <t>河豚鱼</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2009,7 +2105,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2031,6 +2127,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2064,7 +2166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2113,11 +2215,44 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2135,12 +2270,26 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ItemData"/>
+      <sheetName val="Sheet13"/>
       <sheetName val="Sheet2"/>
       <sheetName val="Sheet3"/>
       <sheetName val="Sheet1"/>
+      <sheetName val="Sheet5"/>
+      <sheetName val="植物"/>
+      <sheetName val="动物"/>
+      <sheetName val="装备"/>
+      <sheetName val="Sheet8"/>
+      <sheetName val="材料"/>
+      <sheetName val="食物"/>
+      <sheetName val="鱼"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>string</v>
+          </cell>
+        </row>
         <row r="4">
           <cell r="A4" t="str">
             <v>未知的物品</v>
@@ -5183,89 +5332,97 @@
         </row>
         <row r="384">
           <cell r="A384" t="str">
-            <v>回春卷轴</v>
+            <v>凉茶</v>
           </cell>
           <cell r="B384">
-            <v>4000</v>
+            <v>3179</v>
           </cell>
         </row>
         <row r="385">
           <cell r="A385" t="str">
-            <v>振奋卷轴</v>
+            <v>回春卷轴</v>
           </cell>
           <cell r="B385">
-            <v>4001</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="386">
           <cell r="A386" t="str">
-            <v>昏睡卷轴</v>
+            <v>振奋卷轴</v>
           </cell>
           <cell r="B386">
-            <v>4002</v>
+            <v>4001</v>
           </cell>
         </row>
         <row r="387">
           <cell r="A387" t="str">
-            <v>感电卷轴</v>
+            <v>昏睡卷轴</v>
           </cell>
           <cell r="B387">
-            <v>4003</v>
+            <v>4002</v>
           </cell>
         </row>
         <row r="388">
           <cell r="A388" t="str">
-            <v>冰氛卷轴</v>
+            <v>感电卷轴</v>
           </cell>
           <cell r="B388">
-            <v>4004</v>
+            <v>4003</v>
           </cell>
         </row>
         <row r="389">
           <cell r="A389" t="str">
-            <v>火氛卷轴</v>
+            <v>冰氛卷轴</v>
           </cell>
           <cell r="B389">
-            <v>4005</v>
+            <v>4004</v>
           </cell>
         </row>
         <row r="390">
           <cell r="A390" t="str">
-            <v>沉默卷轴</v>
+            <v>火氛卷轴</v>
           </cell>
           <cell r="B390">
-            <v>4006</v>
+            <v>4005</v>
           </cell>
         </row>
         <row r="391">
           <cell r="A391" t="str">
-            <v>减速卷轴</v>
+            <v>沉默卷轴</v>
           </cell>
           <cell r="B391">
-            <v>4007</v>
+            <v>4006</v>
           </cell>
         </row>
         <row r="392">
           <cell r="A392" t="str">
-            <v>闪避卷轴</v>
+            <v>减速卷轴</v>
           </cell>
           <cell r="B392">
-            <v>4008</v>
+            <v>4007</v>
           </cell>
         </row>
         <row r="393">
           <cell r="A393" t="str">
-            <v>力量卷轴</v>
+            <v>闪避卷轴</v>
           </cell>
           <cell r="B393">
-            <v>4009</v>
+            <v>4008</v>
           </cell>
         </row>
         <row r="394">
           <cell r="A394" t="str">
+            <v>力量卷轴</v>
+          </cell>
+          <cell r="B394">
+            <v>4009</v>
+          </cell>
+        </row>
+        <row r="395">
+          <cell r="A395" t="str">
             <v>魅惑卷轴</v>
           </cell>
-          <cell r="B394">
+          <cell r="B395">
             <v>4010</v>
           </cell>
         </row>
@@ -5273,6 +5430,15 @@
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8314,11 +8480,11 @@
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7">
-        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O5" s="7">
-        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I5&lt;&gt;"",VLOOKUP(I5,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P5" s="7" t="str">
@@ -8365,11 +8531,11 @@
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7">
-        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="O6" s="7">
-        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I6&lt;&gt;"",VLOOKUP(I6,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P6" s="7">
@@ -8416,11 +8582,11 @@
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7">
-        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O7" s="7">
-        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I7&lt;&gt;"",VLOOKUP(I7,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1002</v>
       </c>
       <c r="P7" s="7">
@@ -8461,11 +8627,11 @@
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7">
-        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="O8" s="7">
-        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I8&lt;&gt;"",VLOOKUP(I8,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P8" s="7" t="str">
@@ -8515,11 +8681,11 @@
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7">
-        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O9" s="7">
-        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I9&lt;&gt;"",VLOOKUP(I9,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P9" s="7">
@@ -8564,11 +8730,11 @@
       <c r="L10" s="8"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7">
-        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O10" s="7">
-        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I10&lt;&gt;"",VLOOKUP(I10,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P10" s="7">
@@ -8615,11 +8781,11 @@
       <c r="L11" s="8"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7">
-        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O11" s="7">
-        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I11&lt;&gt;"",VLOOKUP(I11,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3130</v>
       </c>
       <c r="P11" s="7">
@@ -8659,11 +8825,11 @@
         <v>2</v>
       </c>
       <c r="N12" s="7">
-        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="O12" s="7">
-        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I12&lt;&gt;"",VLOOKUP(I12,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P12" s="7" t="str">
@@ -8703,11 +8869,11 @@
         <v>1</v>
       </c>
       <c r="N13" s="7">
-        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1007</v>
       </c>
       <c r="O13" s="7" t="str">
-        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I13&lt;&gt;"",VLOOKUP(I13,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P13" s="7" t="str">
@@ -8747,11 +8913,11 @@
         <v>1</v>
       </c>
       <c r="N14" s="7">
-        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="O14" s="7" t="str">
-        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I14&lt;&gt;"",VLOOKUP(I14,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P14" s="7" t="str">
@@ -8797,11 +8963,11 @@
         <v>3</v>
       </c>
       <c r="N15" s="7">
-        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1003</v>
       </c>
       <c r="O15" s="7">
-        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I15&lt;&gt;"",VLOOKUP(I15,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P15" s="7">
@@ -8841,11 +9007,11 @@
         <v>3</v>
       </c>
       <c r="N16" s="7">
-        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3113</v>
       </c>
       <c r="O16" s="7">
-        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I16&lt;&gt;"",VLOOKUP(I16,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P16" s="7" t="str">
@@ -8887,11 +9053,11 @@
       <c r="K17" s="7"/>
       <c r="L17" s="8"/>
       <c r="N17" s="7">
-        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O17" s="7">
-        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I17&lt;&gt;"",VLOOKUP(I17,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P17" s="7" t="str">
@@ -8932,11 +9098,11 @@
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7">
-        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="O18" s="7" t="str">
-        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I18&lt;&gt;"",VLOOKUP(I18,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P18" s="7" t="str">
@@ -8982,11 +9148,11 @@
         <v>3</v>
       </c>
       <c r="N19" s="7">
-        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="O19" s="7">
-        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I19&lt;&gt;"",VLOOKUP(I19,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P19" s="7">
@@ -9030,11 +9196,11 @@
       </c>
       <c r="L20" s="8"/>
       <c r="N20" s="7">
-        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O20" s="7">
-        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I20&lt;&gt;"",VLOOKUP(I20,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1008</v>
       </c>
       <c r="P20" s="7">
@@ -9079,11 +9245,11 @@
       <c r="L21" s="8"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7">
-        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3112</v>
       </c>
       <c r="O21" s="7">
-        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I21&lt;&gt;"",VLOOKUP(I21,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3166</v>
       </c>
       <c r="P21" s="7">
@@ -9125,11 +9291,11 @@
         <v>3</v>
       </c>
       <c r="N22" s="7">
-        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O22" s="7">
-        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I22&lt;&gt;"",VLOOKUP(I22,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P22" s="7" t="str">
@@ -9176,11 +9342,11 @@
       <c r="L23" s="8"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7">
-        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O23" s="7">
-        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I23&lt;&gt;"",VLOOKUP(I23,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="P23" s="7">
@@ -9222,11 +9388,11 @@
       <c r="K24" s="7"/>
       <c r="L24" s="8"/>
       <c r="N24" s="7">
-        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O24" s="7">
-        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I24&lt;&gt;"",VLOOKUP(I24,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3011</v>
       </c>
       <c r="P24" s="7" t="str">
@@ -9270,11 +9436,11 @@
       </c>
       <c r="L25" s="8"/>
       <c r="N25" s="7">
-        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1001</v>
       </c>
       <c r="O25" s="7">
-        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I25&lt;&gt;"",VLOOKUP(I25,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1006</v>
       </c>
       <c r="P25" s="7">
@@ -9311,11 +9477,11 @@
         <v>1</v>
       </c>
       <c r="N26" s="7">
-        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1010</v>
       </c>
       <c r="O26" s="7" t="str">
-        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I26&lt;&gt;"",VLOOKUP(I26,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P26" s="7" t="str">
@@ -9353,11 +9519,11 @@
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7">
-        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1012</v>
       </c>
       <c r="O27" s="7" t="str">
-        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I27&lt;&gt;"",VLOOKUP(I27,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P27" s="7" t="str">
@@ -9394,11 +9560,11 @@
         <v>1</v>
       </c>
       <c r="N28" s="7">
-        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1022</v>
       </c>
       <c r="O28" s="7" t="str">
-        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I28&lt;&gt;"",VLOOKUP(I28,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P28" s="7" t="str">
@@ -9435,11 +9601,11 @@
         <v>1</v>
       </c>
       <c r="N29" s="7">
-        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1023</v>
       </c>
       <c r="O29" s="7" t="str">
-        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I29&lt;&gt;"",VLOOKUP(I29,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P29" s="7" t="str">
@@ -9470,11 +9636,11 @@
         <v>1</v>
       </c>
       <c r="N30" s="7">
-        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="O30" s="7" t="str">
-        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I30&lt;&gt;"",VLOOKUP(I30,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P30" s="7" t="str">
@@ -9511,11 +9677,11 @@
         <v>1</v>
       </c>
       <c r="N31" s="7">
-        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H31&lt;&gt;"",VLOOKUP(H31,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O31" s="7" t="str">
-        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I31&lt;&gt;"",VLOOKUP(I31,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P31" s="7" t="str">
@@ -9552,11 +9718,11 @@
       <c r="K32" s="7"/>
       <c r="L32" s="8"/>
       <c r="N32" s="7">
-        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1019</v>
       </c>
       <c r="O32" s="7" t="str">
-        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I32&lt;&gt;"",VLOOKUP(I32,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P32" s="7" t="str">
@@ -9599,11 +9765,11 @@
         <v>2</v>
       </c>
       <c r="N33" s="7">
-        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="O33" s="7">
-        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I33&lt;&gt;"",VLOOKUP(I33,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="P33" s="7" t="str">
@@ -9640,11 +9806,11 @@
         <v>1</v>
       </c>
       <c r="N34" s="7">
-        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O34" s="7" t="str">
-        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I34&lt;&gt;"",VLOOKUP(I34,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P34" s="7" t="str">
@@ -9684,11 +9850,11 @@
         <v>1</v>
       </c>
       <c r="N35" s="7">
-        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H35&lt;&gt;"",VLOOKUP(H35,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O35" s="7" t="str">
-        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I35&lt;&gt;"",VLOOKUP(I35,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P35" s="7" t="str">
@@ -9723,11 +9889,11 @@
         <v>2</v>
       </c>
       <c r="N36" s="7">
-        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H36&lt;&gt;"",VLOOKUP(H36,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O36" s="7">
-        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I36&lt;&gt;"",VLOOKUP(I36,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P36" s="7" t="str">
@@ -9773,11 +9939,11 @@
         <v>4</v>
       </c>
       <c r="N37" s="7">
-        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H37&lt;&gt;"",VLOOKUP(H37,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1013</v>
       </c>
       <c r="O37" s="7">
-        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I37&lt;&gt;"",VLOOKUP(I37,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1016</v>
       </c>
       <c r="P37" s="7">
@@ -9825,11 +9991,11 @@
         <v>5</v>
       </c>
       <c r="N38" s="7">
-        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H38&lt;&gt;"",VLOOKUP(H38,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3009</v>
       </c>
       <c r="O38" s="7">
-        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I38&lt;&gt;"",VLOOKUP(I38,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P38" s="7">
@@ -9877,11 +10043,11 @@
         <v>5</v>
       </c>
       <c r="N39" s="7">
-        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H39&lt;&gt;"",VLOOKUP(H39,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="O39" s="7">
-        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I39&lt;&gt;"",VLOOKUP(I39,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="P39" s="7">
@@ -9921,11 +10087,11 @@
         <v>1</v>
       </c>
       <c r="N40" s="7">
-        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H40&lt;&gt;"",VLOOKUP(H40,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1017</v>
       </c>
       <c r="O40" s="7" t="str">
-        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I40&lt;&gt;"",VLOOKUP(I40,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P40" s="7" t="str">
@@ -9968,11 +10134,11 @@
         <v>4</v>
       </c>
       <c r="N41" s="7">
-        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H41&lt;&gt;"",VLOOKUP(H41,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1028</v>
       </c>
       <c r="O41" s="7">
-        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I41&lt;&gt;"",VLOOKUP(I41,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1005</v>
       </c>
       <c r="P41" s="7">
@@ -10018,11 +10184,11 @@
         <v>4</v>
       </c>
       <c r="N42" s="7">
-        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H42&lt;&gt;"",VLOOKUP(H42,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="O42" s="7">
-        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I42&lt;&gt;"",VLOOKUP(I42,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3008</v>
       </c>
       <c r="P42" s="7">
@@ -10059,11 +10225,11 @@
         <v>3</v>
       </c>
       <c r="N43" s="7">
-        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H43&lt;&gt;"",VLOOKUP(H43,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="O43" s="7">
-        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I43&lt;&gt;"",VLOOKUP(I43,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P43" s="7" t="str">
@@ -10103,11 +10269,11 @@
         <v>3</v>
       </c>
       <c r="N44" s="7">
-        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H44&lt;&gt;"",VLOOKUP(H44,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1026</v>
       </c>
       <c r="O44" s="7">
-        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I44&lt;&gt;"",VLOOKUP(I44,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1025</v>
       </c>
       <c r="P44" s="7">
@@ -10146,11 +10312,11 @@
         <v>4</v>
       </c>
       <c r="N45" s="7">
-        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H45&lt;&gt;"",VLOOKUP(H45,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="O45" s="7">
-        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I45&lt;&gt;"",VLOOKUP(I45,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="P45" s="7">
@@ -10189,11 +10355,11 @@
         <v>4</v>
       </c>
       <c r="N46" s="7">
-        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H46&lt;&gt;"",VLOOKUP(H46,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O46" s="7">
-        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I46&lt;&gt;"",VLOOKUP(I46,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3006</v>
       </c>
       <c r="P46" s="7">
@@ -10232,11 +10398,11 @@
         <v>4</v>
       </c>
       <c r="N47" s="7">
-        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H47&lt;&gt;"",VLOOKUP(H47,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3010</v>
       </c>
       <c r="O47" s="7">
-        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I47&lt;&gt;"",VLOOKUP(I47,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P47" s="7" t="str">
@@ -10280,11 +10446,11 @@
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7">
-        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H48&lt;&gt;"",VLOOKUP(H48,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="O48" s="7">
-        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I48&lt;&gt;"",VLOOKUP(I48,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P48" s="7" t="str">
@@ -10328,11 +10494,11 @@
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7">
-        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H49&lt;&gt;"",VLOOKUP(H49,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1015</v>
       </c>
       <c r="O49" s="7">
-        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I49&lt;&gt;"",VLOOKUP(I49,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P49" s="7" t="str">
@@ -10378,11 +10544,11 @@
         <v>3</v>
       </c>
       <c r="N50" s="7" t="e">
-        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H50&lt;&gt;"",VLOOKUP(H50,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
       <c r="O50" s="7">
-        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I50&lt;&gt;"",VLOOKUP(I50,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P50" s="7">
@@ -10425,11 +10591,11 @@
         <v>2</v>
       </c>
       <c r="N51" s="7">
-        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H51&lt;&gt;"",VLOOKUP(H51,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3129</v>
       </c>
       <c r="O51" s="7">
-        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I51&lt;&gt;"",VLOOKUP(I51,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3001</v>
       </c>
       <c r="P51" s="7" t="str">
@@ -10473,11 +10639,11 @@
       <c r="K52" s="7"/>
       <c r="L52" s="8"/>
       <c r="N52" s="7">
-        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H52&lt;&gt;"",VLOOKUP(H52,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3005</v>
       </c>
       <c r="O52" s="7">
-        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I52&lt;&gt;"",VLOOKUP(I52,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1021</v>
       </c>
       <c r="P52" s="7">
@@ -10523,11 +10689,11 @@
         <v>3</v>
       </c>
       <c r="N53" s="7">
-        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H53&lt;&gt;"",VLOOKUP(H53,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3126</v>
       </c>
       <c r="O53" s="7">
-        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I53&lt;&gt;"",VLOOKUP(I53,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="P53" s="7">
@@ -10576,11 +10742,11 @@
         <v>4</v>
       </c>
       <c r="N54" s="7">
-        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H54&lt;&gt;"",VLOOKUP(H54,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3125</v>
       </c>
       <c r="O54" s="7">
-        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I54&lt;&gt;"",VLOOKUP(I54,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3123</v>
       </c>
       <c r="P54" s="7">
@@ -10629,11 +10795,11 @@
         <v>4</v>
       </c>
       <c r="N55" s="7">
-        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H55&lt;&gt;"",VLOOKUP(H55,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3122</v>
       </c>
       <c r="O55" s="7">
-        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I55&lt;&gt;"",VLOOKUP(I55,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3124</v>
       </c>
       <c r="P55" s="7">
@@ -10676,11 +10842,11 @@
         <v>2</v>
       </c>
       <c r="N56" s="7">
-        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H56&lt;&gt;"",VLOOKUP(H56,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O56" s="7">
-        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I56&lt;&gt;"",VLOOKUP(I56,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P56" s="7" t="str">
@@ -10723,11 +10889,11 @@
         <v>2</v>
       </c>
       <c r="N57" s="7">
-        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H57&lt;&gt;"",VLOOKUP(H57,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4009</v>
       </c>
       <c r="O57" s="7">
-        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I57&lt;&gt;"",VLOOKUP(I57,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P57" s="7" t="str">
@@ -10760,7 +10926,7 @@
         <v>202</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>107</v>
+        <v>574</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>28</v>
@@ -10770,11 +10936,11 @@
         <v>2</v>
       </c>
       <c r="N58" s="7">
-        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H58&lt;&gt;"",VLOOKUP(H58,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4015</v>
       </c>
       <c r="O58" s="7">
-        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I58&lt;&gt;"",VLOOKUP(I58,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P58" s="7" t="str">
@@ -10817,11 +10983,11 @@
         <v>2</v>
       </c>
       <c r="N59" s="7">
-        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H59&lt;&gt;"",VLOOKUP(H59,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4016</v>
       </c>
       <c r="O59" s="7">
-        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I59&lt;&gt;"",VLOOKUP(I59,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P59" s="7" t="str">
@@ -10864,11 +11030,11 @@
         <v>2</v>
       </c>
       <c r="N60" s="7">
-        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H60&lt;&gt;"",VLOOKUP(H60,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4017</v>
       </c>
       <c r="O60" s="7">
-        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I60&lt;&gt;"",VLOOKUP(I60,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P60" s="7" t="str">
@@ -10911,11 +11077,11 @@
         <v>2</v>
       </c>
       <c r="N61" s="7">
-        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H61&lt;&gt;"",VLOOKUP(H61,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O61" s="7">
-        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I61&lt;&gt;"",VLOOKUP(I61,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3002</v>
       </c>
       <c r="P61" s="7" t="str">
@@ -10958,11 +11124,11 @@
         <v>2</v>
       </c>
       <c r="N62" s="7">
-        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H62&lt;&gt;"",VLOOKUP(H62,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4100</v>
       </c>
       <c r="O62" s="7">
-        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I62&lt;&gt;"",VLOOKUP(I62,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P62" s="7" t="str">
@@ -11005,11 +11171,11 @@
         <v>2</v>
       </c>
       <c r="N63" s="7">
-        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H63&lt;&gt;"",VLOOKUP(H63,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4101</v>
       </c>
       <c r="O63" s="7">
-        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I63&lt;&gt;"",VLOOKUP(I63,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P63" s="7" t="str">
@@ -11052,11 +11218,11 @@
         <v>2</v>
       </c>
       <c r="N64" s="7">
-        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H64&lt;&gt;"",VLOOKUP(H64,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4103</v>
       </c>
       <c r="O64" s="7">
-        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I64&lt;&gt;"",VLOOKUP(I64,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P64" s="7" t="str">
@@ -11099,11 +11265,11 @@
         <v>2</v>
       </c>
       <c r="N65" s="7">
-        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H65&lt;&gt;"",VLOOKUP(H65,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4106</v>
       </c>
       <c r="O65" s="7">
-        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I65&lt;&gt;"",VLOOKUP(I65,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P65" s="7" t="str">
@@ -11146,11 +11312,11 @@
         <v>2</v>
       </c>
       <c r="N66" s="7">
-        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H66&lt;&gt;"",VLOOKUP(H66,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O66" s="7">
-        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I66&lt;&gt;"",VLOOKUP(I66,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P66" s="7" t="str">
@@ -11187,11 +11353,11 @@
         <v>2</v>
       </c>
       <c r="N67" s="7">
-        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H67&lt;&gt;"",VLOOKUP(H67,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O67" s="7">
-        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I67&lt;&gt;"",VLOOKUP(I67,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P67" s="7" t="str">
@@ -11229,11 +11395,11 @@
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7">
-        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H68&lt;&gt;"",VLOOKUP(H68,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O68" s="7">
-        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I68&lt;&gt;"",VLOOKUP(I68,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P68" s="7" t="str">
@@ -11270,11 +11436,11 @@
         <v>2</v>
       </c>
       <c r="N69" s="7">
-        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H69&lt;&gt;"",VLOOKUP(H69,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O69" s="7">
-        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I69&lt;&gt;"",VLOOKUP(I69,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P69" s="7" t="str">
@@ -11311,11 +11477,11 @@
         <v>2</v>
       </c>
       <c r="N70" s="7">
-        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H70&lt;&gt;"",VLOOKUP(H70,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4115</v>
       </c>
       <c r="O70" s="7">
-        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I70&lt;&gt;"",VLOOKUP(I70,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P70" s="7" t="str">
@@ -11352,11 +11518,11 @@
         <v>2</v>
       </c>
       <c r="N71" s="7">
-        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H71&lt;&gt;"",VLOOKUP(H71,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O71" s="7">
-        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I71&lt;&gt;"",VLOOKUP(I71,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3003</v>
       </c>
       <c r="P71" s="7" t="str">
@@ -11394,11 +11560,11 @@
         <v>2</v>
       </c>
       <c r="N72" s="7">
-        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H72&lt;&gt;"",VLOOKUP(H72,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4007</v>
       </c>
       <c r="O72" s="7">
-        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I72&lt;&gt;"",VLOOKUP(I72,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P72" s="7" t="str">
@@ -11441,11 +11607,11 @@
         <v>3</v>
       </c>
       <c r="N73" s="7">
-        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H73&lt;&gt;"",VLOOKUP(H73,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1018</v>
       </c>
       <c r="O73" s="7">
-        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I73&lt;&gt;"",VLOOKUP(I73,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>200</v>
       </c>
       <c r="P73" s="7">
@@ -11479,11 +11645,11 @@
         <v>2</v>
       </c>
       <c r="N74" s="7">
-        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H74&lt;&gt;"",VLOOKUP(H74,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3158</v>
       </c>
       <c r="O74" s="7">
-        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I74&lt;&gt;"",VLOOKUP(I74,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3000</v>
       </c>
       <c r="P74" s="7" t="str">
@@ -11529,11 +11695,11 @@
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7">
-        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H75&lt;&gt;"",VLOOKUP(H75,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4000</v>
       </c>
       <c r="O75" s="7">
-        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I75&lt;&gt;"",VLOOKUP(I75,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1014</v>
       </c>
       <c r="P75" s="7">
@@ -11571,11 +11737,11 @@
         <v>2</v>
       </c>
       <c r="N76" s="7">
-        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H76&lt;&gt;"",VLOOKUP(H76,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4006</v>
       </c>
       <c r="O76" s="7">
-        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I76&lt;&gt;"",VLOOKUP(I76,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1027</v>
       </c>
       <c r="P76" s="7" t="str">
@@ -11606,11 +11772,11 @@
         <v>1</v>
       </c>
       <c r="N77" s="7">
-        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H77&lt;&gt;"",VLOOKUP(H77,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4021</v>
       </c>
       <c r="O77" s="7" t="str">
-        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I77&lt;&gt;"",VLOOKUP(I77,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P77" s="7" t="str">
@@ -11650,11 +11816,11 @@
         <v>3</v>
       </c>
       <c r="N78" s="7">
-        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H78&lt;&gt;"",VLOOKUP(H78,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4105</v>
       </c>
       <c r="O78" s="7">
-        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I78&lt;&gt;"",VLOOKUP(I78,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3007</v>
       </c>
       <c r="P78" s="7">
@@ -11691,11 +11857,11 @@
         <v>2</v>
       </c>
       <c r="N79" s="7">
-        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H79&lt;&gt;"",VLOOKUP(H79,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4111</v>
       </c>
       <c r="O79" s="7">
-        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I79&lt;&gt;"",VLOOKUP(I79,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1004</v>
       </c>
       <c r="P79" s="7" t="str">
@@ -11725,11 +11891,11 @@
       <c r="K80" s="7"/>
       <c r="L80" s="8"/>
       <c r="N80" s="7">
-        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H80&lt;&gt;"",VLOOKUP(H80,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4112</v>
       </c>
       <c r="O80" s="7" t="str">
-        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I80&lt;&gt;"",VLOOKUP(I80,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P80" s="7" t="str">
@@ -11760,11 +11926,11 @@
         <v>1</v>
       </c>
       <c r="N81" s="7">
-        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H81&lt;&gt;"",VLOOKUP(H81,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4109</v>
       </c>
       <c r="O81" s="7" t="str">
-        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I81&lt;&gt;"",VLOOKUP(I81,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P81" s="7" t="str">
@@ -11808,11 +11974,11 @@
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="7">
-        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H82&lt;&gt;"",VLOOKUP(H82,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4113</v>
       </c>
       <c r="O82" s="7">
-        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I82&lt;&gt;"",VLOOKUP(I82,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>1011</v>
       </c>
       <c r="P82" s="7">
@@ -11843,11 +12009,11 @@
         <v>1</v>
       </c>
       <c r="N83" s="7">
-        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H83&lt;&gt;"",VLOOKUP(H83,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>4116</v>
       </c>
       <c r="O83" s="7" t="str">
-        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I83&lt;&gt;"",VLOOKUP(I83,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="P83" s="7" t="str">
@@ -11879,19 +12045,19 @@
       <c r="J84" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>110</v>
+      <c r="K84" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="L84" s="8">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N84" s="7">
-        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(H84&lt;&gt;"",VLOOKUP(H84,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3164</v>
       </c>
       <c r="O84" s="7">
-        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$536,2,FALSE),"")</f>
+        <f>IF(I84&lt;&gt;"",VLOOKUP(I84,[1]ItemData!$A$4:$B$537,2,FALSE),"")</f>
         <v>3134</v>
       </c>
       <c r="P84" s="7">
@@ -11900,11 +12066,11 @@
       </c>
       <c r="Q84" s="7">
         <f>IF(K84&lt;&gt;"",VLOOKUP(K84,[1]ItemData!$A$4:$B$336,2,FALSE),"")</f>
-        <v>4021</v>
+        <v>4015</v>
       </c>
       <c r="S84" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>3164,3134,1006,4021</v>
+        <v>3164,3134,1006,4015</v>
       </c>
     </row>
     <row r="85" spans="5:19" x14ac:dyDescent="0.2">
@@ -12289,7 +12455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:AD83"/>
+  <dimension ref="B2:AD82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="9" style="7"/>
@@ -12302,7 +12468,10 @@
     <col min="27" max="28" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>578</v>
+      </c>
       <c r="D2" t="s">
         <v>558</v>
       </c>
@@ -12351,8 +12520,15 @@
       <c r="AA2" s="7" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="3" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AB2" s="7" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <f>VLOOKUP(C3,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3100</v>
+      </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
@@ -12362,6 +12538,9 @@
       <c r="E3" s="7">
         <v>15</v>
       </c>
+      <c r="AB3" s="7">
+        <v>66</v>
+      </c>
       <c r="AC3" t="s">
         <v>544</v>
       </c>
@@ -12369,7 +12548,11 @@
         <v>546</v>
       </c>
     </row>
-    <row r="4" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B4" s="7">
+        <f>VLOOKUP(C4,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3101</v>
+      </c>
       <c r="C4" t="s">
         <v>491</v>
       </c>
@@ -12377,11 +12560,14 @@
         <v>1</v>
       </c>
       <c r="E4" s="7">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="U4" s="7">
         <v>1</v>
       </c>
+      <c r="AB4" s="7">
+        <v>425.42500000000001</v>
+      </c>
       <c r="AC4" t="s">
         <v>545</v>
       </c>
@@ -12389,7 +12575,11 @@
         <v>547</v>
       </c>
     </row>
-    <row r="5" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B5" s="7">
+        <f>VLOOKUP(C5,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3102</v>
+      </c>
       <c r="C5" t="s">
         <v>56</v>
       </c>
@@ -12397,13 +12587,16 @@
         <v>1</v>
       </c>
       <c r="I5" s="7">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="N5" s="7">
         <v>1</v>
       </c>
       <c r="O5" s="7">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>609.578125</v>
       </c>
       <c r="AC5" t="s">
         <v>548</v>
@@ -12412,7 +12605,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="6" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B6" s="7">
+        <f>VLOOKUP(C6,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3103</v>
+      </c>
       <c r="C6" t="s">
         <v>49</v>
       </c>
@@ -12422,6 +12619,9 @@
       <c r="E6" s="7">
         <v>20</v>
       </c>
+      <c r="AB6" s="7">
+        <v>111.5</v>
+      </c>
       <c r="AC6" t="s">
         <v>550</v>
       </c>
@@ -12429,7 +12629,11 @@
         <v>551</v>
       </c>
     </row>
-    <row r="7" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B7" s="7">
+        <f>VLOOKUP(C7,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3104</v>
+      </c>
       <c r="C7" t="s">
         <v>492</v>
       </c>
@@ -12437,7 +12641,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="7">
-        <v>20</v>
+        <v>120</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>947.578125</v>
       </c>
       <c r="AC7" t="s">
         <v>552</v>
@@ -12446,7 +12653,11 @@
         <v>555</v>
       </c>
     </row>
-    <row r="8" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B8" s="7">
+        <f>VLOOKUP(C8,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3105</v>
+      </c>
       <c r="C8" t="s">
         <v>493</v>
       </c>
@@ -12454,7 +12665,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="7">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>678.453125</v>
       </c>
       <c r="AC8" t="s">
         <v>556</v>
@@ -12463,7 +12677,11 @@
         <v>557</v>
       </c>
     </row>
-    <row r="9" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B9" s="7">
+        <f>VLOOKUP(C9,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3106</v>
+      </c>
       <c r="C9" t="s">
         <v>213</v>
       </c>
@@ -12471,7 +12689,10 @@
         <v>1</v>
       </c>
       <c r="I9" s="7">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1365.0531249999999</v>
       </c>
       <c r="AC9" t="s">
         <v>553</v>
@@ -12480,7 +12701,11 @@
         <v>554</v>
       </c>
     </row>
-    <row r="10" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B10" s="7">
+        <f>VLOOKUP(C10,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3107</v>
+      </c>
       <c r="C10" t="s">
         <v>50</v>
       </c>
@@ -12490,8 +12715,15 @@
       <c r="E10" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AB10" s="7">
+        <v>111.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B11" s="7">
+        <f>VLOOKUP(C11,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3108</v>
+      </c>
       <c r="C11" t="s">
         <v>494</v>
       </c>
@@ -12501,8 +12733,15 @@
       <c r="E11" s="7">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AB11" s="7">
+        <v>121.94999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B12" s="7">
+        <f>VLOOKUP(C12,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3109</v>
+      </c>
       <c r="C12" t="s">
         <v>59</v>
       </c>
@@ -12512,8 +12751,15 @@
       <c r="G12" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AB12" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B13" s="7">
+        <f>VLOOKUP(C13,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3110</v>
+      </c>
       <c r="C13" t="s">
         <v>495</v>
       </c>
@@ -12521,10 +12767,17 @@
         <v>1</v>
       </c>
       <c r="M13" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="3:30" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>554.125</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B14" s="7">
+        <f>VLOOKUP(C14,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3111</v>
+      </c>
       <c r="C14" t="s">
         <v>68</v>
       </c>
@@ -12532,21 +12785,35 @@
         <v>1</v>
       </c>
       <c r="I14" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="3:30" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>151.94999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B15" s="7">
+        <f>VLOOKUP(C15,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3112</v>
+      </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
-      <c r="H15" t="s">
-        <v>574</v>
+      <c r="H15">
+        <v>1</v>
       </c>
       <c r="I15" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="3:30" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>344.45312499999994</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B16" s="7">
+        <f>VLOOKUP(C16,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3113</v>
+      </c>
       <c r="C16" t="s">
         <v>496</v>
       </c>
@@ -12554,10 +12821,17 @@
         <v>1</v>
       </c>
       <c r="O16" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>121.94999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B17" s="7">
+        <f>VLOOKUP(C17,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3114</v>
+      </c>
       <c r="C17" t="s">
         <v>74</v>
       </c>
@@ -12566,10 +12840,17 @@
         <v>1</v>
       </c>
       <c r="M17" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>859.75</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B18" s="7">
+        <f>VLOOKUP(C18,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3115</v>
+      </c>
       <c r="C18" t="s">
         <v>497</v>
       </c>
@@ -12577,10 +12858,17 @@
         <v>1</v>
       </c>
       <c r="I18" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>1786.203125</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B19" s="7">
+        <f>VLOOKUP(C19,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3116</v>
+      </c>
       <c r="C19" t="s">
         <v>498</v>
       </c>
@@ -12588,13 +12876,20 @@
         <v>1</v>
       </c>
       <c r="G19" s="7">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="R19" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="AB19" s="7">
+        <v>896.953125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B20" s="7">
+        <f>VLOOKUP(C20,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3117</v>
+      </c>
       <c r="C20" t="s">
         <v>499</v>
       </c>
@@ -12602,10 +12897,17 @@
         <v>1</v>
       </c>
       <c r="E20" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>586.45000000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B21" s="7">
+        <f>VLOOKUP(C21,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3118</v>
+      </c>
       <c r="C21" t="s">
         <v>222</v>
       </c>
@@ -12613,10 +12915,17 @@
         <v>1</v>
       </c>
       <c r="I21" s="7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>2650.4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B22" s="7">
+        <f>VLOOKUP(C22,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3119</v>
+      </c>
       <c r="C22" t="s">
         <v>205</v>
       </c>
@@ -12624,10 +12933,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="7">
+        <v>768.9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B23" s="7">
+        <f>VLOOKUP(C23,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3120</v>
+      </c>
       <c r="C23" t="s">
         <v>215</v>
       </c>
@@ -12635,10 +12951,17 @@
         <v>1</v>
       </c>
       <c r="O23" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>265.89999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B24" s="7">
+        <f>VLOOKUP(C24,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3121</v>
+      </c>
       <c r="C24" t="s">
         <v>500</v>
       </c>
@@ -12648,8 +12971,15 @@
       <c r="Q24" s="7">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="AB24" s="7">
+        <v>127.2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B25" s="7">
+        <f>VLOOKUP(C25,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3122</v>
+      </c>
       <c r="C25" t="s">
         <v>37</v>
       </c>
@@ -12657,10 +12987,17 @@
         <v>1</v>
       </c>
       <c r="Q25" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>275.59999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B26" s="7">
+        <f>VLOOKUP(C26,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3123</v>
+      </c>
       <c r="C26" t="s">
         <v>32</v>
       </c>
@@ -12668,21 +13005,35 @@
         <v>1</v>
       </c>
       <c r="Q26" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB26" s="7">
+        <v>754.4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B27" s="7">
+        <f>VLOOKUP(C27,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3124</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P27" s="7">
         <v>1</v>
       </c>
       <c r="Q27" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="AB27" s="7">
+        <v>589.37499999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B28" s="7">
+        <f>VLOOKUP(C28,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3125</v>
+      </c>
       <c r="C28" t="s">
         <v>34</v>
       </c>
@@ -12690,10 +13041,17 @@
         <v>1</v>
       </c>
       <c r="Q28" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="AB28" s="7">
+        <v>761.69999999999993</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B29" s="7">
+        <f>VLOOKUP(C29,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3126</v>
+      </c>
       <c r="C29" t="s">
         <v>35</v>
       </c>
@@ -12701,10 +13059,17 @@
         <v>1</v>
       </c>
       <c r="Q29" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="AB29" s="7">
+        <v>761.7</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B30" s="7">
+        <f>VLOOKUP(C30,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3127</v>
+      </c>
       <c r="C30" t="s">
         <v>191</v>
       </c>
@@ -12714,8 +13079,15 @@
       <c r="O30" s="7">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="AB30" s="7">
+        <v>408.9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B31" s="7">
+        <f>VLOOKUP(C31,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3128</v>
+      </c>
       <c r="C31" t="s">
         <v>501</v>
       </c>
@@ -12723,10 +13095,17 @@
         <v>1</v>
       </c>
       <c r="E31" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="AB31" s="7">
+        <v>940.7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B32" s="7">
+        <f>VLOOKUP(C32,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3129</v>
+      </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
@@ -12734,185 +13113,289 @@
         <v>1</v>
       </c>
       <c r="O32" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="AB32" s="7">
+        <v>761.7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B33" s="7">
+        <f>VLOOKUP(C33,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3130</v>
+      </c>
       <c r="C33" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C34" s="14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="AB33" s="7">
+        <v>446.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B34" s="7">
+        <f>VLOOKUP(C34,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3131</v>
+      </c>
+      <c r="C34" t="s">
+        <v>502</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7">
+        <v>90</v>
+      </c>
+      <c r="AB34" s="7">
+        <v>691.97500000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B35" s="7">
+        <f>VLOOKUP(C35,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3132</v>
+      </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" s="7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7">
+        <v>30</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" s="7">
+        <v>80</v>
+      </c>
+      <c r="AB35" s="7">
+        <v>810.703125</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B36" s="7">
+        <f>VLOOKUP(C36,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3133</v>
+      </c>
       <c r="C36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" s="7">
+        <v>140</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7">
         <v>80</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7">
-        <v>30</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" s="7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="AB36" s="7">
+        <v>1531.7249999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B37" s="7">
+        <f>VLOOKUP(C37,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3134</v>
+      </c>
       <c r="C37" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" s="7">
-        <v>100</v>
-      </c>
-      <c r="F37" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B38" s="7">
+        <f>VLOOKUP(C38,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>506</v>
+      </c>
+      <c r="F38">
         <v>1</v>
       </c>
-      <c r="G37" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>505</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="G38" s="7">
+        <v>70</v>
+      </c>
+      <c r="AB38" s="7">
+        <v>974.1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B39" s="7">
+        <f>VLOOKUP(C39,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3136</v>
+      </c>
       <c r="C39" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="3:19" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>1013.5749999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B40" s="7">
+        <f>VLOOKUP(C40,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3137</v>
+      </c>
       <c r="C40" t="s">
-        <v>507</v>
+        <v>101</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="3:19" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>35</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>1121.6999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B41" s="7">
+        <f>VLOOKUP(C41,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3138</v>
+      </c>
       <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="F41">
+        <v>508</v>
+      </c>
+      <c r="N41" s="7">
         <v>1</v>
       </c>
-      <c r="G41" s="7">
-        <v>70</v>
+      <c r="O41" s="7">
+        <v>30</v>
       </c>
       <c r="P41" s="7">
         <v>1</v>
       </c>
       <c r="Q41" s="7">
+        <v>35</v>
+      </c>
+      <c r="AB41" s="7">
+        <v>1702.4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B42" s="7">
+        <f>VLOOKUP(C42,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>509</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="7">
+        <v>170</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>1933.2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B43" s="7">
+        <f>VLOOKUP(C43,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>510</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="7">
+        <v>80</v>
+      </c>
+      <c r="P43" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>508</v>
-      </c>
-      <c r="N42" s="7">
+      <c r="S43" s="7">
         <v>1</v>
       </c>
-      <c r="O42" s="7">
-        <v>20</v>
-      </c>
-      <c r="P42" s="7">
+      <c r="AB43" s="7">
+        <v>1045.0999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B44" s="7">
+        <f>VLOOKUP(C44,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>511</v>
+      </c>
+      <c r="N44" s="7">
         <v>1</v>
       </c>
-      <c r="Q42" s="7">
+      <c r="O44" s="7">
         <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
-        <v>509</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C44" t="s">
-        <v>510</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7">
-        <v>80</v>
-      </c>
-      <c r="P44" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="7">
-        <v>40</v>
       </c>
       <c r="S44" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="AB44" s="7">
+        <v>685.09999999999991</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B45" s="7">
+        <f>VLOOKUP(C45,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3142</v>
+      </c>
       <c r="C45" t="s">
-        <v>511</v>
-      </c>
-      <c r="N45" s="7">
+        <v>172</v>
+      </c>
+      <c r="J45">
         <v>1</v>
       </c>
-      <c r="O45" s="7">
+      <c r="K45" s="7">
         <v>30</v>
       </c>
-      <c r="S45" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="AB45" s="7">
+        <v>840.9</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B46" s="7">
+        <f>VLOOKUP(C46,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3143</v>
+      </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>512</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -12920,65 +13403,107 @@
       <c r="K46" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="AB46" s="7">
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B47" s="7">
+        <f>VLOOKUP(C47,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3144</v>
+      </c>
       <c r="C47" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="3:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="AB47" s="7">
+        <v>746.70312499999989</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B48" s="7">
+        <f>VLOOKUP(C48,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3145</v>
+      </c>
       <c r="C48" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="K48" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="AB48" s="7">
+        <v>848.2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B49" s="7">
+        <f>VLOOKUP(C49,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3146</v>
+      </c>
       <c r="C49" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="K49" s="7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>606.25</v>
+      </c>
+    </row>
+    <row r="50" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B50" s="7">
+        <f>VLOOKUP(C50,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3147</v>
+      </c>
       <c r="C50" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="K50" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="AB50" s="7">
+        <v>1609.9</v>
+      </c>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B51" s="7">
+        <f>VLOOKUP(C51,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3148</v>
+      </c>
       <c r="C51" t="s">
-        <v>516</v>
-      </c>
-      <c r="J51">
+        <v>517</v>
+      </c>
+      <c r="J51" s="7">
         <v>1</v>
       </c>
       <c r="K51" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1729.8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B52" s="7">
+        <f>VLOOKUP(C52,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3149</v>
+      </c>
       <c r="C52" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J52" s="7">
         <v>1</v>
@@ -12986,142 +13511,233 @@
       <c r="K52" s="7">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="AB52" s="7">
+        <v>1360.375</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B53" s="7">
+        <f>VLOOKUP(C53,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3150</v>
+      </c>
       <c r="C53" t="s">
-        <v>518</v>
-      </c>
-      <c r="J53" s="7">
+        <v>519</v>
+      </c>
+      <c r="L53" s="7">
         <v>1</v>
       </c>
-      <c r="K53" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>234.2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B54" s="7">
+        <f>VLOOKUP(C54,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3151</v>
+      </c>
       <c r="C54" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L54" s="7">
         <v>1</v>
       </c>
       <c r="M54" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="AB54" s="7">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B55" s="7">
+        <f>VLOOKUP(C55,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3152</v>
+      </c>
       <c r="C55" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L55" s="7">
         <v>1</v>
       </c>
       <c r="M55" s="7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B56" s="7">
+        <f>VLOOKUP(C56,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3153</v>
+      </c>
       <c r="C56" t="s">
-        <v>521</v>
-      </c>
-      <c r="L56" s="7">
+        <v>522</v>
+      </c>
+      <c r="F56">
         <v>1</v>
       </c>
-      <c r="M56" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G56" s="7">
+        <v>70</v>
+      </c>
+      <c r="AB56" s="7">
+        <v>968.30000000000007</v>
+      </c>
+    </row>
+    <row r="57" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B57" s="7">
+        <f>VLOOKUP(C57,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3154</v>
+      </c>
       <c r="C57" t="s">
-        <v>522</v>
-      </c>
-      <c r="F57">
+        <v>523</v>
+      </c>
+      <c r="L57" s="7">
         <v>1</v>
       </c>
-      <c r="G57" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="7">
+        <v>65</v>
+      </c>
+      <c r="AB57" s="7">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="58" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B58" s="7">
+        <f>VLOOKUP(C58,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3155</v>
+      </c>
       <c r="C58" t="s">
-        <v>523</v>
+        <v>200</v>
       </c>
       <c r="L58" s="7">
         <v>1</v>
       </c>
       <c r="M58" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="AB58" s="7">
+        <v>1806.25</v>
+      </c>
+    </row>
+    <row r="59" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B59" s="7">
+        <f>VLOOKUP(C59,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3156</v>
+      </c>
       <c r="C59" t="s">
-        <v>200</v>
-      </c>
-      <c r="L59" s="7">
+        <v>524</v>
+      </c>
+      <c r="H59">
         <v>1</v>
       </c>
-      <c r="M59" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="I59" s="7">
+        <v>30</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>270.05</v>
+      </c>
+    </row>
+    <row r="60" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B60" s="7">
+        <f>VLOOKUP(C60,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3157</v>
+      </c>
       <c r="C60" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" s="7">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="AB60" s="7">
+        <v>298.14999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B61" s="7">
+        <f>VLOOKUP(C61,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3158</v>
+      </c>
       <c r="C61" t="s">
-        <v>525</v>
-      </c>
-      <c r="H61">
+        <v>476</v>
+      </c>
+      <c r="F61">
         <v>1</v>
       </c>
-      <c r="I61" s="7">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="G61" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB61" s="7">
+        <v>341.84999999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B62" s="7">
+        <f>VLOOKUP(C62,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3159</v>
+      </c>
       <c r="C62" t="s">
-        <v>476</v>
-      </c>
-      <c r="F62">
+        <v>136</v>
+      </c>
+      <c r="D62">
         <v>1</v>
       </c>
-      <c r="G62" s="7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="E62" s="7">
+        <v>70</v>
+      </c>
+      <c r="AB62" s="7">
+        <v>535.1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B63" s="7">
+        <f>VLOOKUP(C63,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3160</v>
+      </c>
       <c r="C63" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63">
+        <v>526</v>
+      </c>
+      <c r="D63" s="7">
         <v>1</v>
       </c>
       <c r="E63" s="7">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>485.65</v>
+      </c>
+    </row>
+    <row r="64" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B64" s="7">
+        <f>VLOOKUP(C64,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3161</v>
+      </c>
       <c r="C64" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D64" s="7">
         <v>1</v>
       </c>
       <c r="E64" s="7">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65" spans="3:15" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="AB64" s="7">
+        <v>878.35</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B65" s="7">
+        <f>VLOOKUP(C65,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3162</v>
+      </c>
       <c r="C65" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D65" s="7">
         <v>1</v>
@@ -13129,240 +13745,1611 @@
       <c r="E65" s="7">
         <v>180</v>
       </c>
-    </row>
-    <row r="66" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="J65" s="7"/>
+      <c r="AB65" s="7">
+        <v>1066.0500000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B66" s="7">
+        <f>VLOOKUP(C66,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3163</v>
+      </c>
       <c r="C66" t="s">
-        <v>528</v>
-      </c>
-      <c r="D66" s="7">
+        <v>529</v>
+      </c>
+      <c r="J66">
         <v>1</v>
       </c>
-      <c r="E66" s="7">
-        <v>200</v>
-      </c>
-      <c r="J66" s="7"/>
-    </row>
-    <row r="67" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="K66" s="7">
+        <v>45</v>
+      </c>
+      <c r="AB66" s="7">
+        <v>1409.1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B67" s="7">
+        <f>VLOOKUP(C67,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3164</v>
+      </c>
       <c r="C67" t="s">
-        <v>529</v>
-      </c>
-      <c r="J67">
+        <v>530</v>
+      </c>
+      <c r="J67" s="7">
         <v>1</v>
       </c>
       <c r="K67" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="68" spans="3:15" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="AB67" s="7">
+        <v>1993.9</v>
+      </c>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B68" s="7">
+        <f>VLOOKUP(C68,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3165</v>
+      </c>
       <c r="C68" t="s">
-        <v>530</v>
-      </c>
-      <c r="J68" s="7">
+        <v>531</v>
+      </c>
+      <c r="J68">
         <v>1</v>
       </c>
       <c r="K68" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="3:15" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="AB68" s="7">
+        <v>2538.5500000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B69" s="7">
+        <f>VLOOKUP(C69,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3166</v>
+      </c>
       <c r="C69" t="s">
-        <v>531</v>
-      </c>
-      <c r="J69">
+        <v>186</v>
+      </c>
+      <c r="F69">
         <v>1</v>
       </c>
-      <c r="K69" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="G69" s="7">
+        <v>20</v>
+      </c>
+      <c r="L69" s="7">
+        <v>1</v>
+      </c>
+      <c r="M69" s="7">
+        <v>15</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>255.4</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B70" s="7">
+        <f>VLOOKUP(C70,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3167</v>
+      </c>
       <c r="C70" t="s">
-        <v>186</v>
+        <v>532</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" s="7">
-        <v>150</v>
-      </c>
-      <c r="L70" s="7">
+        <v>160</v>
+      </c>
+      <c r="AB70" s="7">
+        <v>1958.4749999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B71" s="7">
+        <f>VLOOKUP(C71,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3168</v>
+      </c>
+      <c r="C71" t="s">
+        <v>533</v>
+      </c>
+      <c r="H71">
         <v>1</v>
       </c>
-      <c r="M70" s="7">
+      <c r="I71" s="7">
+        <v>50</v>
+      </c>
+      <c r="L71" s="7">
+        <v>1</v>
+      </c>
+      <c r="M71" s="7">
+        <v>30</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>371.84999999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B72" s="7">
+        <f>VLOOKUP(C72,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3169</v>
+      </c>
+      <c r="C72" t="s">
+        <v>534</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7">
+        <v>120</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB72" s="7">
+        <v>949.92499999999995</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B73" s="7">
+        <f>VLOOKUP(C73,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3170</v>
+      </c>
+      <c r="C73" t="s">
+        <v>535</v>
+      </c>
+      <c r="L73" s="7">
+        <v>1</v>
+      </c>
+      <c r="M73" s="7">
+        <v>60</v>
+      </c>
+      <c r="AB73" s="7">
+        <v>970.90000000000009</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B74" s="7">
+        <f>VLOOKUP(C74,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3171</v>
+      </c>
+      <c r="C74" t="s">
+        <v>536</v>
+      </c>
+      <c r="N74" s="7">
+        <v>1</v>
+      </c>
+      <c r="O74" s="7">
         <v>45</v>
       </c>
-    </row>
-    <row r="71" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C71" t="s">
-        <v>532</v>
-      </c>
-      <c r="F71">
+      <c r="AB74" s="7">
+        <v>1781.25</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B75" s="7">
+        <f>VLOOKUP(C75,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3172</v>
+      </c>
+      <c r="C75" t="s">
+        <v>537</v>
+      </c>
+      <c r="L75" s="7">
         <v>1</v>
       </c>
-      <c r="G71" s="7">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C72" t="s">
-        <v>533</v>
-      </c>
-      <c r="H72">
+      <c r="M75" s="7">
+        <v>45</v>
+      </c>
+      <c r="AB75" s="7">
+        <v>620.34999999999991</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B76" s="7">
+        <f>VLOOKUP(C76,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3173</v>
+      </c>
+      <c r="C76" t="s">
+        <v>538</v>
+      </c>
+      <c r="F76">
         <v>1</v>
       </c>
-      <c r="I72" s="7">
-        <v>150</v>
-      </c>
-      <c r="L72" s="7">
+      <c r="G76" s="7">
+        <v>60</v>
+      </c>
+      <c r="AB76" s="7">
+        <v>912.95</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B77" s="7">
+        <f>VLOOKUP(C77,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3174</v>
+      </c>
+      <c r="C77" t="s">
+        <v>539</v>
+      </c>
+      <c r="N77" s="7">
         <v>1</v>
       </c>
-      <c r="M72" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C73" t="s">
-        <v>534</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" s="7">
-        <v>140</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="G73" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C74" t="s">
-        <v>535</v>
-      </c>
-      <c r="L74" s="7">
-        <v>1</v>
-      </c>
-      <c r="M74" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="75" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C75" t="s">
-        <v>536</v>
-      </c>
-      <c r="N75" s="7">
-        <v>1</v>
-      </c>
-      <c r="O75" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C76" t="s">
-        <v>537</v>
-      </c>
-      <c r="L76" s="7">
-        <v>1</v>
-      </c>
-      <c r="M76" s="7">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C77" t="s">
-        <v>538</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77" s="7">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="78" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>1014.1500000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B78" s="7">
+        <f>VLOOKUP(C78,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3175</v>
+      </c>
       <c r="C78" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N78" s="7">
         <v>1</v>
       </c>
       <c r="O78" s="7">
+        <v>20</v>
+      </c>
+      <c r="AB78" s="7">
+        <v>433.75</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B79" s="7">
+        <f>VLOOKUP(C79,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3176</v>
+      </c>
+      <c r="C79" t="s">
+        <v>571</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" s="7">
+        <v>160</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB79" s="7">
+        <v>1829.05</v>
+      </c>
+    </row>
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B80" s="7">
+        <f>VLOOKUP(C80,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3177</v>
+      </c>
+      <c r="C80" t="s">
+        <v>541</v>
+      </c>
+      <c r="N80" s="7">
+        <v>1</v>
+      </c>
+      <c r="O80" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB80" s="7">
+        <v>2486.65</v>
+      </c>
+    </row>
+    <row r="81" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B81" s="7">
+        <f>VLOOKUP(C81,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3178</v>
+      </c>
+      <c r="C81" t="s">
+        <v>542</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" s="7">
+        <v>200</v>
+      </c>
+      <c r="AB81" s="7">
+        <v>3206.4</v>
+      </c>
+    </row>
+    <row r="82" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B82" s="7">
+        <f>VLOOKUP(C82,Sheet4!$A$1:$B$99,2,FALSE)</f>
+        <v>3179</v>
+      </c>
+      <c r="C82" t="s">
+        <v>543</v>
+      </c>
+      <c r="N82" s="7">
+        <v>1</v>
+      </c>
+      <c r="O82" s="7">
+        <v>8</v>
+      </c>
+      <c r="P82" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="7">
+        <v>15</v>
+      </c>
+      <c r="T82" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="7">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:AD2">
+    <sortState ref="B3:AD82">
+      <sortCondition ref="B2"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G114"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B1" s="18">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B2" s="18">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="18">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="18">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B5" s="18">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" s="18">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="18">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="18">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B9" s="18">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="18">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="18">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="18">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" s="18">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B14" s="18">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="18">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B16" s="18">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B17" s="18">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B18" s="18">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="18">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="18">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="18">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B22" s="18">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="18">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="18">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="18">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="18">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="79" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C79" t="s">
+      <c r="B27" s="18">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="18">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B29" s="18">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="18">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="18">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B32" s="18">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B33" s="18">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B34" s="18">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B35" s="18">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B36" s="18">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B37" s="18">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="18">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B39" s="18">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B40" s="18">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B41" s="18">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B42" s="18">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="18">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B44" s="18">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B45" s="18">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B46" s="18">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B47" s="18">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B48" s="18">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B49" s="18">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B50" s="18">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B51" s="18">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B52" s="18">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B53" s="18">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B54" s="18">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B55" s="18">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="18">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B57" s="18">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B58" s="18">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B59" s="18">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="18">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B61" s="18">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B62" s="18">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B63" s="18">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B64" s="18">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B65" s="18">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B66" s="18">
+        <v>3165</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="18">
+        <v>3166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B68" s="18">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B69" s="18">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B70" s="18">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B71" s="18">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B72" s="18">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B73" s="18">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B74" s="18">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B75" s="18">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B76" s="18">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B77" s="18">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B78" s="18">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B79" s="18">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="B80" s="18">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="84" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>587</v>
+      </c>
+      <c r="G84">
+        <v>203.25</v>
+      </c>
+    </row>
+    <row r="85" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>104</v>
+      </c>
+      <c r="G85">
+        <v>209.2</v>
+      </c>
+    </row>
+    <row r="86" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>111</v>
+      </c>
+      <c r="G86">
+        <v>218.15</v>
+      </c>
+    </row>
+    <row r="87" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="F87" t="s">
+        <v>105</v>
+      </c>
+      <c r="G87">
+        <v>230.4</v>
+      </c>
+    </row>
+    <row r="88" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>112</v>
+      </c>
+      <c r="G88">
+        <v>246.25</v>
+      </c>
+    </row>
+    <row r="89" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89" t="s">
+        <v>106</v>
+      </c>
+      <c r="G89">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="90" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>7</v>
+      </c>
+      <c r="F90" t="s">
+        <v>113</v>
+      </c>
+      <c r="G90">
+        <v>289.95</v>
+      </c>
+    </row>
+    <row r="91" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>8</v>
+      </c>
+      <c r="F91" t="s">
+        <v>146</v>
+      </c>
+      <c r="G91">
+        <v>318.39999999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>588</v>
+      </c>
+      <c r="G92">
+        <v>351.65</v>
+      </c>
+    </row>
+    <row r="93" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E93">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>589</v>
+      </c>
+      <c r="G93">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E94">
+        <v>11</v>
+      </c>
+      <c r="F94" t="s">
+        <v>590</v>
+      </c>
+      <c r="G94">
+        <v>433.75</v>
+      </c>
+    </row>
+    <row r="95" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E95">
+        <v>12</v>
+      </c>
+      <c r="F95" t="s">
+        <v>114</v>
+      </c>
+      <c r="G95">
+        <v>483.2</v>
+      </c>
+    </row>
+    <row r="96" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E96">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>107</v>
+      </c>
+      <c r="G96">
+        <v>538.65</v>
+      </c>
+    </row>
+    <row r="97" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E97">
+        <v>14</v>
+      </c>
+      <c r="F97" t="s">
+        <v>591</v>
+      </c>
+      <c r="G97">
+        <v>600.4</v>
+      </c>
+    </row>
+    <row r="98" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
+        <v>592</v>
+      </c>
+      <c r="G98">
+        <v>668.75</v>
+      </c>
+    </row>
+    <row r="99" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
+        <v>593</v>
+      </c>
+      <c r="G99">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="100" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E100">
+        <v>17</v>
+      </c>
+      <c r="F100" t="s">
+        <v>115</v>
+      </c>
+      <c r="G100">
+        <v>826.45</v>
+      </c>
+    </row>
+    <row r="101" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E101">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>108</v>
+      </c>
+      <c r="G101">
+        <v>916.40000000000009</v>
+      </c>
+    </row>
+    <row r="102" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E102">
+        <v>19</v>
+      </c>
+      <c r="F102" t="s">
+        <v>116</v>
+      </c>
+      <c r="G102">
+        <v>1014.1500000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E103">
+        <v>20</v>
+      </c>
+      <c r="F103" t="s">
+        <v>109</v>
+      </c>
+      <c r="G103">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="104" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E104">
+        <v>21</v>
+      </c>
+      <c r="F104" t="s">
+        <v>594</v>
+      </c>
+      <c r="G104">
+        <v>1234.25</v>
+      </c>
+    </row>
+    <row r="105" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E105">
+        <v>22</v>
+      </c>
+      <c r="F105" t="s">
+        <v>117</v>
+      </c>
+      <c r="G105">
+        <v>1357.1999999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E106">
+        <v>23</v>
+      </c>
+      <c r="F106" t="s">
+        <v>595</v>
+      </c>
+      <c r="G106">
+        <v>1489.15</v>
+      </c>
+    </row>
+    <row r="107" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>24</v>
+      </c>
+      <c r="F107" t="s">
+        <v>596</v>
+      </c>
+      <c r="G107">
+        <v>1630.4</v>
+      </c>
+    </row>
+    <row r="108" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>25</v>
+      </c>
+      <c r="F108" t="s">
+        <v>110</v>
+      </c>
+      <c r="G108">
+        <v>1781.25</v>
+      </c>
+    </row>
+    <row r="109" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E109">
+        <v>26</v>
+      </c>
+      <c r="F109" t="s">
+        <v>118</v>
+      </c>
+      <c r="G109">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="110" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E110">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s">
+        <v>597</v>
+      </c>
+      <c r="G110">
+        <v>2112.9499999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E111">
+        <v>28</v>
+      </c>
+      <c r="F111" t="s">
+        <v>598</v>
+      </c>
+      <c r="G111">
+        <v>2294.4</v>
+      </c>
+    </row>
+    <row r="112" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E112">
+        <v>29</v>
+      </c>
+      <c r="F112" t="s">
+        <v>119</v>
+      </c>
+      <c r="G112">
+        <v>2486.65</v>
+      </c>
+    </row>
+    <row r="113" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <v>30</v>
+      </c>
+      <c r="F113" t="s">
+        <v>599</v>
+      </c>
+      <c r="G113">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="114" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E114">
+        <v>31</v>
+      </c>
+      <c r="F114" t="s">
+        <v>600</v>
+      </c>
+      <c r="G114">
+        <v>2904.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A79">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="9" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C1" s="17" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C2" s="17">
+        <v>234.2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="17">
+        <v>255.4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C4" s="17">
+        <v>270.05</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C5" s="17">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C6" s="17">
+        <v>298.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7" s="17">
+        <v>341.84999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>533</v>
+      </c>
+      <c r="C8" s="17">
+        <v>371.84999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>540</v>
       </c>
-      <c r="N79" s="7">
-        <v>1</v>
-      </c>
-      <c r="O79" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="80" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C80" t="s">
-        <v>571</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80" s="7">
-        <v>170</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="G80" s="7">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="C81" t="s">
+      <c r="C9" s="17">
+        <v>433.75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" s="17">
+        <v>485.65</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="17">
+        <v>535.1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>537</v>
+      </c>
+      <c r="C12" s="17">
+        <v>620.34999999999991</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>521</v>
+      </c>
+      <c r="C13" s="17">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="17">
+        <v>878.35</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C15" s="17">
+        <v>912.95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>534</v>
+      </c>
+      <c r="C16" s="17">
+        <v>949.92499999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C17" s="17">
+        <v>968.30000000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>535</v>
+      </c>
+      <c r="C18" s="17">
+        <v>970.90000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>539</v>
+      </c>
+      <c r="C19" s="17">
+        <v>1014.1500000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>528</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1066.0500000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>523</v>
+      </c>
+      <c r="C21" s="17">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>529</v>
+      </c>
+      <c r="C22" s="17">
+        <v>1409.1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>536</v>
+      </c>
+      <c r="C23" s="17">
+        <v>1781.25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="17">
+        <v>1806.25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>575</v>
+      </c>
+      <c r="C25" s="17">
+        <v>1829.05</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>532</v>
+      </c>
+      <c r="C26" s="17">
+        <v>1958.4749999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>530</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1993.9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>541</v>
       </c>
-      <c r="N81" s="7">
-        <v>1</v>
-      </c>
-      <c r="O81" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="C82" t="s">
+      <c r="C28" s="17">
+        <v>2486.65</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>531</v>
+      </c>
+      <c r="C29" s="17">
+        <v>2538.5500000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
         <v>542</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="G82" s="7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="C83" t="s">
-        <v>543</v>
-      </c>
-      <c r="N83" s="7">
-        <v>1</v>
-      </c>
-      <c r="O83" s="7">
-        <v>50</v>
-      </c>
-      <c r="P83" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q83" s="7">
-        <v>50</v>
-      </c>
-      <c r="T83" s="7">
-        <v>1</v>
+      <c r="C30" s="17">
+        <v>3206.4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:C1">
+    <sortState ref="B2:C31">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory - Copy\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2274,6 +2274,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ItemData"/>
+      <sheetName val="Sheet6"/>
       <sheetName val="Sheet4"/>
       <sheetName val="Sheet13"/>
       <sheetName val="Sheet2"/>
@@ -5420,7 +5421,7 @@
         </row>
         <row r="395">
           <cell r="A395" t="str">
-            <v>鸡</v>
+            <v>母鸡</v>
           </cell>
           <cell r="B395">
             <v>3500</v>
@@ -5428,7 +5429,7 @@
         </row>
         <row r="396">
           <cell r="A396" t="str">
-            <v>鸭</v>
+            <v>鸭子</v>
           </cell>
           <cell r="B396">
             <v>3501</v>
@@ -5436,7 +5437,7 @@
         </row>
         <row r="397">
           <cell r="A397" t="str">
-            <v>家兔</v>
+            <v>兔子</v>
           </cell>
           <cell r="B397">
             <v>3502</v>
@@ -5452,7 +5453,7 @@
         </row>
         <row r="399">
           <cell r="A399" t="str">
-            <v>奶牛</v>
+            <v>猪</v>
           </cell>
           <cell r="B399">
             <v>3504</v>
@@ -5460,7 +5461,7 @@
         </row>
         <row r="400">
           <cell r="A400" t="str">
-            <v>猪</v>
+            <v>奶牛</v>
           </cell>
           <cell r="B400">
             <v>3505</v>
@@ -5476,89 +5477,113 @@
         </row>
         <row r="402">
           <cell r="A402" t="str">
-            <v>回春卷轴</v>
+            <v>山羊</v>
           </cell>
           <cell r="B402">
-            <v>5000</v>
+            <v>3507</v>
           </cell>
         </row>
         <row r="403">
           <cell r="A403" t="str">
-            <v>振奋卷轴</v>
+            <v>火鸡</v>
           </cell>
           <cell r="B403">
-            <v>5001</v>
+            <v>3508</v>
           </cell>
         </row>
         <row r="404">
           <cell r="A404" t="str">
-            <v>昏睡卷轴</v>
+            <v>羊驼</v>
           </cell>
           <cell r="B404">
-            <v>5002</v>
+            <v>3509</v>
           </cell>
         </row>
         <row r="405">
           <cell r="A405" t="str">
-            <v>感电卷轴</v>
+            <v>回春卷轴</v>
           </cell>
           <cell r="B405">
-            <v>5003</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="406">
           <cell r="A406" t="str">
-            <v>冰氛卷轴</v>
+            <v>振奋卷轴</v>
           </cell>
           <cell r="B406">
-            <v>5004</v>
+            <v>5001</v>
           </cell>
         </row>
         <row r="407">
           <cell r="A407" t="str">
-            <v>火氛卷轴</v>
+            <v>昏睡卷轴</v>
           </cell>
           <cell r="B407">
-            <v>5005</v>
+            <v>5002</v>
           </cell>
         </row>
         <row r="408">
           <cell r="A408" t="str">
-            <v>沉默卷轴</v>
+            <v>感电卷轴</v>
           </cell>
           <cell r="B408">
-            <v>5006</v>
+            <v>5003</v>
           </cell>
         </row>
         <row r="409">
           <cell r="A409" t="str">
-            <v>减速卷轴</v>
+            <v>冰氛卷轴</v>
           </cell>
           <cell r="B409">
-            <v>5007</v>
+            <v>5004</v>
           </cell>
         </row>
         <row r="410">
           <cell r="A410" t="str">
-            <v>闪避卷轴</v>
+            <v>火氛卷轴</v>
           </cell>
           <cell r="B410">
-            <v>5008</v>
+            <v>5005</v>
           </cell>
         </row>
         <row r="411">
           <cell r="A411" t="str">
-            <v>力量卷轴</v>
+            <v>沉默卷轴</v>
           </cell>
           <cell r="B411">
-            <v>5009</v>
+            <v>5006</v>
           </cell>
         </row>
         <row r="412">
           <cell r="A412" t="str">
+            <v>减速卷轴</v>
+          </cell>
+          <cell r="B412">
+            <v>5007</v>
+          </cell>
+        </row>
+        <row r="413">
+          <cell r="A413" t="str">
+            <v>闪避卷轴</v>
+          </cell>
+          <cell r="B413">
+            <v>5008</v>
+          </cell>
+        </row>
+        <row r="414">
+          <cell r="A414" t="str">
+            <v>力量卷轴</v>
+          </cell>
+          <cell r="B414">
+            <v>5009</v>
+          </cell>
+        </row>
+        <row r="415">
+          <cell r="A415" t="str">
             <v>魅惑卷轴</v>
           </cell>
-          <cell r="B412">
+          <cell r="B415">
             <v>5010</v>
           </cell>
         </row>
@@ -5576,6 +5601,7 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Datas/食物.xlsx
+++ b/Datas/食物.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="6" r:id="rId1"/>
@@ -8494,7 +8494,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T204"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8621,7 +8620,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
         <v>218</v>
       </c>
@@ -8669,7 +8668,7 @@
         <v>1001,3002</v>
       </c>
     </row>
-    <row r="6" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
         <v>219</v>
       </c>
@@ -8723,7 +8722,7 @@
         <v>1002,1005,1009,1006</v>
       </c>
     </row>
-    <row r="7" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>53</v>
       </c>
@@ -8777,7 +8776,7 @@
         <v>3112,1002,1006,1008</v>
       </c>
     </row>
-    <row r="8" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
         <v>210</v>
       </c>
@@ -8825,7 +8824,7 @@
         <v>1004,3002</v>
       </c>
     </row>
-    <row r="9" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
@@ -8882,7 +8881,7 @@
         <v>3009,3008,1003,3109</v>
       </c>
     </row>
-    <row r="10" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>52</v>
       </c>
@@ -8934,7 +8933,7 @@
         <v>3009,3007,3005</v>
       </c>
     </row>
-    <row r="11" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
@@ -8988,7 +8987,7 @@
         <v>3009,3130,1013,3008</v>
       </c>
     </row>
-    <row r="12" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
         <v>65</v>
       </c>
@@ -9035,7 +9034,7 @@
         <v>1006,3002</v>
       </c>
     </row>
-    <row r="13" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
@@ -9082,7 +9081,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="14" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
         <v>213</v>
       </c>
@@ -9129,7 +9128,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="15" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
         <v>95</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>1003,3008,1011</v>
       </c>
     </row>
-    <row r="16" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
         <v>207</v>
       </c>
@@ -9229,7 +9228,7 @@
         <v>3113,3000</v>
       </c>
     </row>
-    <row r="17" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>205</v>
       </c>
@@ -9278,7 +9277,7 @@
         <v>3009,200</v>
       </c>
     </row>
-    <row r="18" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
         <v>163</v>
       </c>
@@ -9326,7 +9325,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="19" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>195</v>
       </c>
@@ -9379,7 +9378,7 @@
         <v>1016,3008,3002</v>
       </c>
     </row>
-    <row r="20" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
         <v>16</v>
       </c>
@@ -9430,7 +9429,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
         <v>17</v>
       </c>
@@ -9482,7 +9481,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
@@ -9531,7 +9530,7 @@
         <v>1015,3011</v>
       </c>
     </row>
-    <row r="23" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
         <v>19</v>
       </c>
@@ -9585,7 +9584,7 @@
         <v>3000,4105,4115,3006</v>
       </c>
     </row>
-    <row r="24" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
         <v>20</v>
       </c>
@@ -9634,7 +9633,7 @@
         <v>1019,3011</v>
       </c>
     </row>
-    <row r="25" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
         <v>21</v>
       </c>
@@ -9685,7 +9684,7 @@
         <v>1001,1006,1004,1005</v>
       </c>
     </row>
-    <row r="26" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
         <v>79</v>
       </c>
@@ -9729,7 +9728,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
         <v>80</v>
       </c>
@@ -9774,7 +9773,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="28" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
         <v>81</v>
       </c>
@@ -9818,7 +9817,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="29" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>91</v>
       </c>
@@ -9862,7 +9861,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="30" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E30" s="7" t="s">
         <v>181</v>
       </c>
@@ -9900,7 +9899,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="31" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
         <v>26</v>
       </c>
@@ -9944,7 +9943,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="32" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
         <v>193</v>
       </c>
@@ -9988,7 +9987,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
         <v>194</v>
       </c>
@@ -10038,7 +10037,7 @@
         <v>1027,3005</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
         <v>165</v>
       </c>
@@ -10082,7 +10081,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
         <v>170</v>
@@ -10171,7 +10170,7 @@
         <v>3006,3001</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
         <v>44</v>
       </c>
@@ -10224,7 +10223,7 @@
         <v>1013,1016,1003,3002</v>
       </c>
     </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
         <v>197</v>
       </c>
@@ -10279,7 +10278,7 @@
         <v>3009,3008,1002,1003</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
         <v>63</v>
       </c>
@@ -10334,7 +10333,7 @@
         <v>1005,1018,1028,3011</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
         <v>198</v>
       </c>
@@ -10381,7 +10380,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E41" s="7" t="s">
         <v>179</v>
       </c>
@@ -10431,7 +10430,7 @@
         <v>1028,1005,1008,200</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
@@ -10484,7 +10483,7 @@
         <v>1014,3008,1009,200</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
         <v>41</v>
       </c>
@@ -10528,7 +10527,7 @@
         <v>3006,3125</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
         <v>42</v>
       </c>
@@ -10575,7 +10574,7 @@
         <v>1026,1025,3005</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
         <v>45</v>
       </c>
@@ -10621,7 +10620,7 @@
         <v>3000,4021,3113</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B46" s="7" t="s">
         <v>46</v>
       </c>
@@ -10667,7 +10666,7 @@
         <v>3010,3006,200</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B47" s="7" t="s">
         <v>69</v>
       </c>
@@ -11134,7 +11133,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B56" s="7" t="s">
         <v>131</v>
       </c>
@@ -11184,7 +11183,7 @@
         <v>4006,3002</v>
       </c>
     </row>
-    <row r="57" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B57" s="7" t="s">
         <v>132</v>
       </c>
@@ -11234,7 +11233,7 @@
         <v>4009,3002</v>
       </c>
     </row>
-    <row r="58" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B58" s="7" t="s">
         <v>133</v>
       </c>
@@ -11284,7 +11283,7 @@
         <v>4015,3002</v>
       </c>
     </row>
-    <row r="59" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B59" s="7" t="s">
         <v>146</v>
       </c>
@@ -11334,7 +11333,7 @@
         <v>4016,3003</v>
       </c>
     </row>
-    <row r="60" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B60" s="7" t="s">
         <v>134</v>
       </c>
@@ -11384,7 +11383,7 @@
         <v>4017,3002</v>
       </c>
     </row>
-    <row r="61" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B61" s="7" t="s">
         <v>136</v>
       </c>
@@ -11434,7 +11433,7 @@
         <v>4021,3002</v>
       </c>
     </row>
-    <row r="62" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B62" s="7" t="s">
         <v>123</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>4100,3003</v>
       </c>
     </row>
-    <row r="63" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B63" s="7" t="s">
         <v>124</v>
       </c>
@@ -11534,7 +11533,7 @@
         <v>4101,3003</v>
       </c>
     </row>
-    <row r="64" spans="2:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B64" s="7" t="s">
         <v>138</v>
       </c>
@@ -11584,7 +11583,7 @@
         <v>4103,3003</v>
       </c>
     </row>
-    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B65" s="7" t="s">
         <v>139</v>
       </c>
@@ -11634,7 +11633,7 @@
         <v>4106,3003</v>
       </c>
     </row>
-    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B66" s="7" t="s">
         <v>141</v>
       </c>
@@ -11684,7 +11683,7 @@
         <v>4109,3003</v>
       </c>
     </row>
-    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E67" s="7" t="s">
         <v>180</v>
       </c>
@@ -11728,7 +11727,7 @@
         <v>4111,3003</v>
       </c>
     </row>
-    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E68" s="7" t="s">
         <v>180</v>
       </c>
@@ -11773,7 +11772,7 @@
         <v>4112,3003</v>
       </c>
     </row>
-    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E69" s="7" t="s">
         <v>180</v>
       </c>
@@ -11817,7 +11816,7 @@
         <v>4113,3003</v>
       </c>
     </row>
-    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E70" s="7" t="s">
         <v>180</v>
       </c>
@@ -11861,7 +11860,7 @@
         <v>4115,3003</v>
       </c>
     </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E71" s="7" t="s">
         <v>179</v>
       </c>
@@ -11905,7 +11904,7 @@
         <v>4116,3003</v>
       </c>
     </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E72" s="7" t="s">
         <v>179</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E73" s="7" t="s">
         <v>179</v>
       </c>
@@ -12000,7 +11999,7 @@
         <v>1018,200,4100,4113</v>
       </c>
     </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E74" s="7" t="s">
         <v>178</v>
       </c>
@@ -12041,7 +12040,7 @@
         <v>3158,3000</v>
       </c>
     </row>
-    <row r="75" spans="1:20" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="7" t="s">
@@ -12094,7 +12093,7 @@
         <v>4000,1014,200,1017</v>
       </c>
     </row>
-    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="E76" s="7" t="s">
         <v>179</v>
@@ -12139,7 +12138,7 @@
         <v>4006,1027</v>
       </c>
     </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E77" s="7" t="s">
         <v>178</v>
       </c>
@@ -12177,7 +12176,7 @@
         <v>4021</v>
       </c>
     </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E78" s="7" t="s">
         <v>179</v>
       </c>
@@ -12224,7 +12223,7 @@
         <v>4105,3007,3011</v>
       </c>
     </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E79" s="7" t="s">
         <v>179</v>
       </c>
@@ -12268,7 +12267,7 @@
         <v>4111,1004</v>
       </c>
     </row>
-    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E80" s="7" t="s">
         <v>178</v>
       </c>
@@ -12305,7 +12304,7 @@
         <v>4112</v>
       </c>
     </row>
-    <row r="81" spans="5:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:20" x14ac:dyDescent="0.2">
       <c r="E81" s="7" t="s">
         <v>178</v>
       </c>
@@ -12343,7 +12342,7 @@
         <v>4109</v>
       </c>
     </row>
-    <row r="82" spans="5:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="5:20" x14ac:dyDescent="0.2">
       <c r="E82" s="7" t="s">
         <v>179</v>
       </c>
@@ -12394,7 +12393,7 @@
         <v>4113,1011,1009,1007</v>
       </c>
     </row>
-    <row r="83" spans="5:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:20" x14ac:dyDescent="0.2">
       <c r="E83" s="7" t="s">
         <v>178</v>
       </c>
@@ -12432,7 +12431,7 @@
         <v>4116</v>
       </c>
     </row>
-    <row r="84" spans="5:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="5:20" x14ac:dyDescent="0.2">
       <c r="E84" s="7" t="s">
         <v>178</v>
       </c>
@@ -12479,7 +12478,7 @@
         <v>3164,3134,1006,4015</v>
       </c>
     </row>
-    <row r="85" spans="5:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:20" x14ac:dyDescent="0.2">
       <c r="E85" s="1" t="s">
         <v>477</v>
       </c>
@@ -12996,13 +12995,7 @@
       <c r="H204" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="D4:K85">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="发酵"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="D4:K85"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
